--- a/制作進捗ボード.xlsx
+++ b/制作進捗ボード.xlsx
@@ -8,14 +8,15 @@
   </bookViews>
   <sheets>
     <sheet name="LP" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="eラーニング・動画" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="広告" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="凡例と出典" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="選択肢" sheetId="2" state="hidden" r:id="rId2"/>
+    <sheet name="eラーニング・動画" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="広告" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="凡例と出典" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'LP'!$A$5:$P$16</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'eラーニング・動画'!$A$5:$I$21</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'広告'!$A$5:$I$10</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'eラーニング・動画'!$A$5:$I$21</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'広告'!$A$5:$I$10</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -28,13 +29,22 @@
     <numFmt numFmtId="165" formatCode="0&quot;／11&quot;"/>
     <numFmt numFmtId="166" formatCode="0.0&quot;／4段&quot;"/>
   </numFmts>
-  <fonts count="16">
+  <fonts count="18">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="Meiryo"/>
+      <b val="1"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Meiryo"/>
+      <sz val="9"/>
     </font>
     <font>
       <name val="Meiryo"/>
@@ -124,7 +134,7 @@
       <sz val="12"/>
     </font>
   </fonts>
-  <fills count="5">
+  <fills count="6">
     <fill>
       <patternFill/>
     </fill>
@@ -144,6 +154,11 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00FAF8F3"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00EAF1F6"/>
       </patternFill>
     </fill>
   </fills>
@@ -178,109 +193,123 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="39">
+  <cellXfs count="45">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="8" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="164" fontId="8" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="164" fontId="8" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="165" fontId="11" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="165" fontId="13" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="166" fontId="11" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="166" fontId="13" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="9" fontId="6" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="9" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="9" fontId="8" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="9" fontId="11" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="11" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="13" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
-  <dxfs count="4">
+  <dxfs count="3">
     <dxf>
       <font>
         <name val="Meiryo"/>
@@ -302,13 +331,6 @@
         <name val="Meiryo"/>
         <b val="1"/>
         <color rgb="001C6647"/>
-        <sz val="9"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <name val="Meiryo"/>
-        <color rgb="006E747D"/>
         <sz val="9"/>
       </font>
     </dxf>
@@ -882,117 +904,117 @@
           <t>△</t>
         </is>
       </c>
-      <c r="H6" s="7">
+      <c r="H6" s="8">
         <f>IF(J6="","×","○")</f>
         <v/>
       </c>
-      <c r="I6" s="8">
+      <c r="I6" s="9">
         <f>COUNTIF(E6:H6,"○")+COUNTIF(E6:H6,"△")</f>
         <v/>
       </c>
-      <c r="J6" s="9" t="n"/>
+      <c r="J6" s="10" t="n"/>
       <c r="K6" s="5" t="inlineStr">
         <is>
           <t>送信ボタンがメーラーを開くだけ。受付フォームの実装が必要／会社概要ページが未作成／本番ドメインへの公開</t>
         </is>
       </c>
-      <c r="L6" s="10" t="inlineStr">
+      <c r="L6" s="11" t="inlineStr">
         <is>
           <t>資料請求を開く</t>
         </is>
       </c>
-      <c r="M6" s="11" t="inlineStr">
+      <c r="M6" s="12" t="inlineStr">
         <is>
           <t>未作成</t>
         </is>
       </c>
-      <c r="N6" s="10" t="inlineStr">
+      <c r="N6" s="11" t="inlineStr">
         <is>
           <t>LPを開く</t>
         </is>
       </c>
-      <c r="O6" s="12" t="inlineStr">
+      <c r="O6" s="13" t="inlineStr">
         <is>
           <t>08b479a1</t>
         </is>
       </c>
-      <c r="P6" s="7" t="inlineStr">
+      <c r="P6" s="8" t="inlineStr">
         <is>
           <t>2026-09-03</t>
         </is>
       </c>
     </row>
     <row r="7" ht="46" customHeight="1">
-      <c r="A7" s="13" t="inlineStr">
+      <c r="A7" s="14" t="inlineStr">
         <is>
           <t>REALIZE CLUB（法人向け）</t>
         </is>
       </c>
-      <c r="B7" s="14" t="inlineStr">
+      <c r="B7" s="15" t="inlineStr">
         <is>
           <t>別案</t>
         </is>
       </c>
-      <c r="C7" s="13" t="inlineStr">
+      <c r="C7" s="14" t="inlineStr">
         <is>
           <t>会社が社員の人生を支える時代へ</t>
         </is>
       </c>
-      <c r="D7" s="13" t="inlineStr">
+      <c r="D7" s="14" t="inlineStr">
         <is>
           <t>星空タウン／クリーム × 濃紺のイラスト</t>
         </is>
       </c>
-      <c r="E7" s="15" t="inlineStr">
+      <c r="E7" s="7" t="inlineStr">
         <is>
           <t>○</t>
         </is>
       </c>
-      <c r="F7" s="15" t="inlineStr">
+      <c r="F7" s="7" t="inlineStr">
         <is>
           <t>○</t>
         </is>
       </c>
-      <c r="G7" s="15" t="inlineStr">
+      <c r="G7" s="7" t="inlineStr">
         <is>
           <t>△</t>
         </is>
       </c>
-      <c r="H7" s="15">
+      <c r="H7" s="16">
         <f>IF(J7="","×","○")</f>
         <v/>
       </c>
-      <c r="I7" s="16">
+      <c r="I7" s="17">
         <f>COUNTIF(E7:H7,"○")+COUNTIF(E7:H7,"△")</f>
         <v/>
       </c>
-      <c r="J7" s="9" t="n"/>
-      <c r="K7" s="13" t="inlineStr">
+      <c r="J7" s="10" t="n"/>
+      <c r="K7" s="14" t="inlineStr">
         <is>
           <t>RC案で唯一3ページ揃い。採用するかの判断／送信はメーラー起動のみ</t>
         </is>
       </c>
-      <c r="L7" s="17" t="inlineStr">
+      <c r="L7" s="18" t="inlineStr">
         <is>
           <t>資料請求を開く</t>
         </is>
       </c>
-      <c r="M7" s="17" t="inlineStr">
+      <c r="M7" s="18" t="inlineStr">
         <is>
           <t>会社概要を開く</t>
         </is>
       </c>
-      <c r="N7" s="17" t="inlineStr">
+      <c r="N7" s="18" t="inlineStr">
         <is>
           <t>LPを開く</t>
         </is>
       </c>
-      <c r="O7" s="18" t="inlineStr">
+      <c r="O7" s="19" t="inlineStr">
         <is>
           <t>7355f424</t>
         </is>
       </c>
-      <c r="P7" s="15" t="inlineStr">
+      <c r="P7" s="16" t="inlineStr">
         <is>
           <t>2026-08-31</t>
         </is>
@@ -1004,7 +1026,7 @@
           <t>REALIZE CLUB（法人向け）</t>
         </is>
       </c>
-      <c r="B8" s="19" t="inlineStr">
+      <c r="B8" s="20" t="inlineStr">
         <is>
           <t>別案</t>
         </is>
@@ -1034,117 +1056,117 @@
           <t>×</t>
         </is>
       </c>
-      <c r="H8" s="7">
+      <c r="H8" s="8">
         <f>IF(J8="","×","○")</f>
         <v/>
       </c>
-      <c r="I8" s="8">
+      <c r="I8" s="9">
         <f>COUNTIF(E8:H8,"○")+COUNTIF(E8:H8,"△")</f>
         <v/>
       </c>
-      <c r="J8" s="9" t="n"/>
+      <c r="J8" s="10" t="n"/>
       <c r="K8" s="5" t="inlineStr">
         <is>
           <t>kaisha.html ほかへの相対リンクが残り、単体では飛べない／会社概要ページの作成</t>
         </is>
       </c>
-      <c r="L8" s="11" t="inlineStr">
+      <c r="L8" s="12" t="inlineStr">
         <is>
           <t>（同ファイル内）</t>
         </is>
       </c>
-      <c r="M8" s="11" t="inlineStr">
+      <c r="M8" s="12" t="inlineStr">
         <is>
           <t>未作成</t>
         </is>
       </c>
-      <c r="N8" s="10" t="inlineStr">
+      <c r="N8" s="11" t="inlineStr">
         <is>
           <t>LPを開く</t>
         </is>
       </c>
-      <c r="O8" s="12" t="inlineStr">
+      <c r="O8" s="13" t="inlineStr">
         <is>
           <t>ded9a489</t>
         </is>
       </c>
-      <c r="P8" s="7" t="inlineStr">
+      <c r="P8" s="8" t="inlineStr">
         <is>
           <t>2026-08-31</t>
         </is>
       </c>
     </row>
     <row r="9" ht="46" customHeight="1">
-      <c r="A9" s="13" t="inlineStr">
+      <c r="A9" s="14" t="inlineStr">
         <is>
           <t>REALIZE CLUB（法人向け）</t>
         </is>
       </c>
-      <c r="B9" s="14" t="inlineStr">
+      <c r="B9" s="15" t="inlineStr">
         <is>
           <t>別案</t>
         </is>
       </c>
-      <c r="C9" s="13" t="inlineStr">
+      <c r="C9" s="14" t="inlineStr">
         <is>
           <t>その安心、今がお得。</t>
         </is>
       </c>
-      <c r="D9" s="13" t="inlineStr">
+      <c r="D9" s="14" t="inlineStr">
         <is>
           <t>スーパーの特売ポップ／白地に赤と黄</t>
         </is>
       </c>
-      <c r="E9" s="15" t="inlineStr">
+      <c r="E9" s="7" t="inlineStr">
         <is>
           <t>○</t>
         </is>
       </c>
-      <c r="F9" s="15" t="inlineStr">
+      <c r="F9" s="7" t="inlineStr">
         <is>
           <t>△</t>
         </is>
       </c>
-      <c r="G9" s="15" t="inlineStr">
+      <c r="G9" s="7" t="inlineStr">
         <is>
           <t>×</t>
         </is>
       </c>
-      <c r="H9" s="15">
+      <c r="H9" s="16">
         <f>IF(J9="","×","○")</f>
         <v/>
       </c>
-      <c r="I9" s="16">
+      <c r="I9" s="17">
         <f>COUNTIF(E9:H9,"○")+COUNTIF(E9:H9,"△")</f>
         <v/>
       </c>
-      <c r="J9" s="9" t="n"/>
-      <c r="K9" s="13" t="inlineStr">
+      <c r="J9" s="10" t="n"/>
+      <c r="K9" s="14" t="inlineStr">
         <is>
           <t>リンクがすべてページ内アンカー。外部への導線が1本もない／会社概要ページ、送信先の設定</t>
         </is>
       </c>
-      <c r="L9" s="20" t="inlineStr">
+      <c r="L9" s="21" t="inlineStr">
         <is>
           <t>（同ページ内フォーム）</t>
         </is>
       </c>
-      <c r="M9" s="20" t="inlineStr">
+      <c r="M9" s="21" t="inlineStr">
         <is>
           <t>未作成</t>
         </is>
       </c>
-      <c r="N9" s="17" t="inlineStr">
+      <c r="N9" s="18" t="inlineStr">
         <is>
           <t>LPを開く</t>
         </is>
       </c>
-      <c r="O9" s="18" t="inlineStr">
+      <c r="O9" s="19" t="inlineStr">
         <is>
           <t>4ce48691</t>
         </is>
       </c>
-      <c r="P9" s="15" t="inlineStr">
+      <c r="P9" s="16" t="inlineStr">
         <is>
           <t>2026-08-31</t>
         </is>
@@ -1156,7 +1178,7 @@
           <t>REALIZE CLUB（法人向け）</t>
         </is>
       </c>
-      <c r="B10" s="19" t="inlineStr">
+      <c r="B10" s="20" t="inlineStr">
         <is>
           <t>別案</t>
         </is>
@@ -1186,117 +1208,117 @@
           <t>×</t>
         </is>
       </c>
-      <c r="H10" s="7">
+      <c r="H10" s="8">
         <f>IF(J10="","×","○")</f>
         <v/>
       </c>
-      <c r="I10" s="8">
+      <c r="I10" s="9">
         <f>COUNTIF(E10:H10,"○")+COUNTIF(E10:H10,"△")</f>
         <v/>
       </c>
-      <c r="J10" s="9" t="n"/>
+      <c r="J10" s="10" t="n"/>
       <c r="K10" s="5" t="inlineStr">
         <is>
           <t>会社概要ページが未作成／送信はメーラー起動のみ</t>
         </is>
       </c>
-      <c r="L10" s="10" t="inlineStr">
+      <c r="L10" s="11" t="inlineStr">
         <is>
           <t>資料請求を開く</t>
         </is>
       </c>
-      <c r="M10" s="11" t="inlineStr">
+      <c r="M10" s="12" t="inlineStr">
         <is>
           <t>未作成</t>
         </is>
       </c>
-      <c r="N10" s="10" t="inlineStr">
+      <c r="N10" s="11" t="inlineStr">
         <is>
           <t>LPを開く</t>
         </is>
       </c>
-      <c r="O10" s="12" t="inlineStr">
+      <c r="O10" s="13" t="inlineStr">
         <is>
           <t>b0f16478</t>
         </is>
       </c>
-      <c r="P10" s="7" t="inlineStr">
+      <c r="P10" s="8" t="inlineStr">
         <is>
           <t>2026-08-28</t>
         </is>
       </c>
     </row>
     <row r="11" ht="46" customHeight="1">
-      <c r="A11" s="13" t="inlineStr">
+      <c r="A11" s="14" t="inlineStr">
         <is>
           <t>LIFE MAKE PARTNERS（加盟店募集）</t>
         </is>
       </c>
-      <c r="B11" s="21" t="inlineStr">
+      <c r="B11" s="22" t="inlineStr">
         <is>
           <t>現行</t>
         </is>
       </c>
-      <c r="C11" s="13" t="inlineStr">
+      <c r="C11" s="14" t="inlineStr">
         <is>
           <t>家より先に、人生の話を。</t>
         </is>
       </c>
-      <c r="D11" s="13" t="inlineStr">
+      <c r="D11" s="14" t="inlineStr">
         <is>
           <t>韓国料理店の看板／木の壁 × 生成りの横断幕</t>
         </is>
       </c>
-      <c r="E11" s="15" t="inlineStr">
+      <c r="E11" s="7" t="inlineStr">
         <is>
           <t>○</t>
         </is>
       </c>
-      <c r="F11" s="15" t="inlineStr">
+      <c r="F11" s="7" t="inlineStr">
         <is>
           <t>○</t>
         </is>
       </c>
-      <c r="G11" s="15" t="inlineStr">
+      <c r="G11" s="7" t="inlineStr">
         <is>
           <t>○</t>
         </is>
       </c>
-      <c r="H11" s="15">
+      <c r="H11" s="16">
         <f>IF(J11="","×","○")</f>
         <v/>
       </c>
-      <c r="I11" s="16">
+      <c r="I11" s="17">
         <f>COUNTIF(E11:H11,"○")+COUNTIF(E11:H11,"△")</f>
         <v/>
       </c>
-      <c r="J11" s="9" t="n"/>
-      <c r="K11" s="13" t="inlineStr">
+      <c r="J11" s="10" t="n"/>
+      <c r="K11" s="14" t="inlineStr">
         <is>
           <t>本番ドメインへの公開だけが残り。問い合わせはLINE公式（lin.ee/WHYApuM）に集約済み</t>
         </is>
       </c>
-      <c r="L11" s="17" t="inlineStr">
+      <c r="L11" s="18" t="inlineStr">
         <is>
           <t>資料請求を開く</t>
         </is>
       </c>
-      <c r="M11" s="17" t="inlineStr">
+      <c r="M11" s="18" t="inlineStr">
         <is>
           <t>会社概要を開く</t>
         </is>
       </c>
-      <c r="N11" s="17" t="inlineStr">
+      <c r="N11" s="18" t="inlineStr">
         <is>
           <t>LPを開く</t>
         </is>
       </c>
-      <c r="O11" s="18" t="inlineStr">
+      <c r="O11" s="19" t="inlineStr">
         <is>
           <t>7f212d2f</t>
         </is>
       </c>
-      <c r="P11" s="15" t="inlineStr">
+      <c r="P11" s="16" t="inlineStr">
         <is>
           <t>2026-09-03</t>
         </is>
@@ -1308,7 +1330,7 @@
           <t>LIFE MAKE PARTNERS（加盟店募集）</t>
         </is>
       </c>
-      <c r="B12" s="19" t="inlineStr">
+      <c r="B12" s="20" t="inlineStr">
         <is>
           <t>別案</t>
         </is>
@@ -1338,117 +1360,117 @@
           <t>×</t>
         </is>
       </c>
-      <c r="H12" s="7">
+      <c r="H12" s="8">
         <f>IF(J12="","×","○")</f>
         <v/>
       </c>
-      <c r="I12" s="8">
+      <c r="I12" s="9">
         <f>COUNTIF(E12:H12,"○")+COUNTIF(E12:H12,"△")</f>
         <v/>
       </c>
-      <c r="J12" s="9" t="n"/>
+      <c r="J12" s="10" t="n"/>
       <c r="K12" s="5" t="inlineStr">
         <is>
           <t>kaisha-katsu.html ほかへの相対リンクが残り飛べない／行き先が「#」のままのボタンが2つ</t>
         </is>
       </c>
-      <c r="L12" s="11" t="inlineStr">
+      <c r="L12" s="12" t="inlineStr">
         <is>
           <t>（同ページ内フォーム）</t>
         </is>
       </c>
-      <c r="M12" s="11" t="inlineStr">
+      <c r="M12" s="12" t="inlineStr">
         <is>
           <t>未作成</t>
         </is>
       </c>
-      <c r="N12" s="10" t="inlineStr">
+      <c r="N12" s="11" t="inlineStr">
         <is>
           <t>LPを開く</t>
         </is>
       </c>
-      <c r="O12" s="12" t="inlineStr">
+      <c r="O12" s="13" t="inlineStr">
         <is>
           <t>db82fc95</t>
         </is>
       </c>
-      <c r="P12" s="7" t="inlineStr">
+      <c r="P12" s="8" t="inlineStr">
         <is>
           <t>2026-08-28</t>
         </is>
       </c>
     </row>
     <row r="13" ht="46" customHeight="1">
-      <c r="A13" s="13" t="inlineStr">
+      <c r="A13" s="14" t="inlineStr">
         <is>
           <t>LIFE MAKE PARTNERS（加盟店募集）</t>
         </is>
       </c>
-      <c r="B13" s="14" t="inlineStr">
+      <c r="B13" s="15" t="inlineStr">
         <is>
           <t>別案</t>
         </is>
       </c>
-      <c r="C13" s="13" t="inlineStr">
+      <c r="C13" s="14" t="inlineStr">
         <is>
           <t>加盟資格は、人生への愛。ただそれだけ。</t>
         </is>
       </c>
-      <c r="D13" s="13" t="inlineStr">
+      <c r="D13" s="14" t="inlineStr">
         <is>
           <t>星空タウン／RC星空案と同じ世界観</t>
         </is>
       </c>
-      <c r="E13" s="15" t="inlineStr">
+      <c r="E13" s="7" t="inlineStr">
         <is>
           <t>○</t>
         </is>
       </c>
-      <c r="F13" s="15" t="inlineStr">
+      <c r="F13" s="7" t="inlineStr">
         <is>
           <t>○</t>
         </is>
       </c>
-      <c r="G13" s="15" t="inlineStr">
+      <c r="G13" s="7" t="inlineStr">
         <is>
           <t>△</t>
         </is>
       </c>
-      <c r="H13" s="15">
+      <c r="H13" s="16">
         <f>IF(J13="","×","○")</f>
         <v/>
       </c>
-      <c r="I13" s="16">
+      <c r="I13" s="17">
         <f>COUNTIF(E13:H13,"○")+COUNTIF(E13:H13,"△")</f>
         <v/>
       </c>
-      <c r="J13" s="9" t="n"/>
-      <c r="K13" s="13" t="inlineStr">
+      <c r="J13" s="10" t="n"/>
+      <c r="K13" s="14" t="inlineStr">
         <is>
           <t>行き先が「#」のままのボタンが2つ／現行案との統廃合の判断</t>
         </is>
       </c>
-      <c r="L13" s="17" t="inlineStr">
+      <c r="L13" s="18" t="inlineStr">
         <is>
           <t>資料請求を開く</t>
         </is>
       </c>
-      <c r="M13" s="17" t="inlineStr">
+      <c r="M13" s="18" t="inlineStr">
         <is>
           <t>会社概要を開く</t>
         </is>
       </c>
-      <c r="N13" s="17" t="inlineStr">
+      <c r="N13" s="18" t="inlineStr">
         <is>
           <t>LPを開く</t>
         </is>
       </c>
-      <c r="O13" s="18" t="inlineStr">
+      <c r="O13" s="19" t="inlineStr">
         <is>
           <t>65b43069</t>
         </is>
       </c>
-      <c r="P13" s="15" t="inlineStr">
+      <c r="P13" s="16" t="inlineStr">
         <is>
           <t>2026-08-24</t>
         </is>
@@ -1490,117 +1512,117 @@
           <t>△</t>
         </is>
       </c>
-      <c r="H14" s="7">
+      <c r="H14" s="8">
         <f>IF(J14="","×","○")</f>
         <v/>
       </c>
-      <c r="I14" s="8">
+      <c r="I14" s="9">
         <f>COUNTIF(E14:H14,"○")+COUNTIF(E14:H14,"△")</f>
         <v/>
       </c>
-      <c r="J14" s="9" t="n"/>
+      <c r="J14" s="10" t="n"/>
       <c r="K14" s="5" t="inlineStr">
         <is>
           <t>行き先が「#」のままのリンクが2つ残っている／本番ドメインへの公開</t>
         </is>
       </c>
-      <c r="L14" s="10" t="inlineStr">
+      <c r="L14" s="11" t="inlineStr">
         <is>
           <t>資料請求を開く</t>
         </is>
       </c>
-      <c r="M14" s="10" t="inlineStr">
+      <c r="M14" s="11" t="inlineStr">
         <is>
           <t>会社概要を開く</t>
         </is>
       </c>
-      <c r="N14" s="10" t="inlineStr">
+      <c r="N14" s="11" t="inlineStr">
         <is>
           <t>LPを開く</t>
         </is>
       </c>
-      <c r="O14" s="12" t="inlineStr">
+      <c r="O14" s="13" t="inlineStr">
         <is>
           <t>1a259364</t>
         </is>
       </c>
-      <c r="P14" s="7" t="inlineStr">
+      <c r="P14" s="8" t="inlineStr">
         <is>
           <t>2026-09-03</t>
         </is>
       </c>
     </row>
     <row r="15" ht="46" customHeight="1">
-      <c r="A15" s="13" t="inlineStr">
+      <c r="A15" s="14" t="inlineStr">
         <is>
           <t>まちの相談窓口</t>
         </is>
       </c>
-      <c r="B15" s="22" t="inlineStr">
+      <c r="B15" s="23" t="inlineStr">
         <is>
           <t>旧版</t>
         </is>
       </c>
-      <c r="C15" s="13" t="inlineStr">
+      <c r="C15" s="14" t="inlineStr">
         <is>
           <t>まちの相談窓口（フォーム版）</t>
         </is>
       </c>
-      <c r="D15" s="13" t="inlineStr">
+      <c r="D15" s="14" t="inlineStr">
         <is>
           <t>銭湯ポスター／申込フォーム内蔵</t>
         </is>
       </c>
-      <c r="E15" s="15" t="inlineStr">
+      <c r="E15" s="7" t="inlineStr">
         <is>
           <t>○</t>
         </is>
       </c>
-      <c r="F15" s="15" t="inlineStr">
+      <c r="F15" s="7" t="inlineStr">
         <is>
           <t>○</t>
         </is>
       </c>
-      <c r="G15" s="15" t="inlineStr">
+      <c r="G15" s="7" t="inlineStr">
         <is>
           <t>△</t>
         </is>
       </c>
-      <c r="H15" s="15">
+      <c r="H15" s="16">
         <f>IF(J15="","×","○")</f>
         <v/>
       </c>
-      <c r="I15" s="16">
+      <c r="I15" s="17">
         <f>COUNTIF(E15:H15,"○")+COUNTIF(E15:H15,"△")</f>
         <v/>
       </c>
-      <c r="J15" s="9" t="n"/>
-      <c r="K15" s="13" t="inlineStr">
+      <c r="J15" s="10" t="n"/>
+      <c r="K15" s="14" t="inlineStr">
         <is>
           <t>現行のLINE誘導版に置き換わっている。残すか消すかの判断</t>
         </is>
       </c>
-      <c r="L15" s="17" t="inlineStr">
+      <c r="L15" s="18" t="inlineStr">
         <is>
           <t>資料請求を開く</t>
         </is>
       </c>
-      <c r="M15" s="17" t="inlineStr">
+      <c r="M15" s="18" t="inlineStr">
         <is>
           <t>会社概要を開く</t>
         </is>
       </c>
-      <c r="N15" s="17" t="inlineStr">
+      <c r="N15" s="18" t="inlineStr">
         <is>
           <t>LPを開く</t>
         </is>
       </c>
-      <c r="O15" s="18" t="inlineStr">
+      <c r="O15" s="19" t="inlineStr">
         <is>
           <t>39f0d878</t>
         </is>
       </c>
-      <c r="P15" s="15" t="inlineStr">
+      <c r="P15" s="16" t="inlineStr">
         <is>
           <t>2026-08-20</t>
         </is>
@@ -1612,7 +1634,7 @@
           <t>不動産FC加盟</t>
         </is>
       </c>
-      <c r="B16" s="23" t="inlineStr">
+      <c r="B16" s="24" t="inlineStr">
         <is>
           <t>単発</t>
         </is>
@@ -1642,73 +1664,73 @@
           <t>×</t>
         </is>
       </c>
-      <c r="H16" s="7">
+      <c r="H16" s="8">
         <f>IF(J16="","×","○")</f>
         <v/>
       </c>
-      <c r="I16" s="8">
+      <c r="I16" s="9">
         <f>COUNTIF(E16:H16,"○")+COUNTIF(E16:H16,"△")</f>
         <v/>
       </c>
-      <c r="J16" s="9" t="n"/>
+      <c r="J16" s="10" t="n"/>
       <c r="K16" s="5" t="inlineStr">
         <is>
           <t>ページのタイトルタグが空。共有すると名前なしで出る／資料請求・会社概要ページ、送信先の設定</t>
         </is>
       </c>
-      <c r="L16" s="11" t="inlineStr">
+      <c r="L16" s="12" t="inlineStr">
         <is>
           <t>（同ページ内フォーム）</t>
         </is>
       </c>
-      <c r="M16" s="11" t="inlineStr">
+      <c r="M16" s="12" t="inlineStr">
         <is>
           <t>未作成</t>
         </is>
       </c>
-      <c r="N16" s="10" t="inlineStr">
+      <c r="N16" s="11" t="inlineStr">
         <is>
           <t>LPを開く</t>
         </is>
       </c>
-      <c r="O16" s="12" t="inlineStr">
+      <c r="O16" s="13" t="inlineStr">
         <is>
           <t>d5160792</t>
         </is>
       </c>
-      <c r="P16" s="7" t="inlineStr">
+      <c r="P16" s="8" t="inlineStr">
         <is>
           <t>2026-08-19</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="D17" s="24" t="inlineStr">
+      <c r="D17" s="25" t="inlineStr">
         <is>
           <t>合計 / 平均</t>
         </is>
       </c>
-      <c r="E17" s="25">
+      <c r="E17" s="26">
         <f>COUNTIF(E6:E16,"○")</f>
         <v/>
       </c>
-      <c r="F17" s="25">
+      <c r="F17" s="26">
         <f>COUNTIF(F6:F16,"○")</f>
         <v/>
       </c>
-      <c r="G17" s="25">
+      <c r="G17" s="26">
         <f>COUNTIF(G6:G16,"○")</f>
         <v/>
       </c>
-      <c r="H17" s="25">
+      <c r="H17" s="26">
         <f>COUNTIF(H6:H16,"○")</f>
         <v/>
       </c>
-      <c r="I17" s="26">
+      <c r="I17" s="27">
         <f>AVERAGE(I6:I16)</f>
         <v/>
       </c>
-      <c r="J17" s="27">
+      <c r="J17" s="28">
         <f>COUNTA(J6:J16)&amp;" 本 公開済み"</f>
         <v/>
       </c>
@@ -1726,8 +1748,17 @@
       <formula>"○"</formula>
     </cfRule>
   </conditionalFormatting>
+  <conditionalFormatting sqref="I6:I16">
+    <cfRule type="dataBar" priority="4">
+      <dataBar showValue="1">
+        <cfvo type="num" val="0"/>
+        <cfvo type="num" val="4"/>
+        <color rgb="001F4E6B"/>
+      </dataBar>
+    </cfRule>
+  </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation sqref="E6:G16" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list">
+    <dataValidation sqref="E6:G16" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" promptTitle="選んでください" prompt="○＝できている／△＝仮づけ／×＝手つかず" type="list">
       <formula1>"○,△,×"</formula1>
     </dataValidation>
   </dataValidations>
@@ -1767,6 +1798,132 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:A22"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="29" t="inlineStr">
+        <is>
+          <t>進捗</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="30" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="30" t="n">
+        <v>0.05</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="30" t="n">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="30" t="n">
+        <v>0.15</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="30" t="n">
+        <v>0.2</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="30" t="n">
+        <v>0.25</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="30" t="n">
+        <v>0.3</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="30" t="n">
+        <v>0.35</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="30" t="n">
+        <v>0.4</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="30" t="n">
+        <v>0.45</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="30" t="n">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="30" t="n">
+        <v>0.55</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="30" t="n">
+        <v>0.6000000000000001</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="30" t="n">
+        <v>0.65</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="30" t="n">
+        <v>0.7000000000000001</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="30" t="n">
+        <v>0.75</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="30" t="n">
+        <v>0.8</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="30" t="n">
+        <v>0.8500000000000001</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="30" t="n">
+        <v>0.9</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="30" t="n">
+        <v>0.9500000000000001</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="30" t="n">
+        <v>1</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:I28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
@@ -1850,12 +2007,12 @@
       </c>
     </row>
     <row r="6" ht="32" customHeight="1">
-      <c r="A6" s="12" t="inlineStr">
+      <c r="A6" s="13" t="inlineStr">
         <is>
           <t>教材・ツール</t>
         </is>
       </c>
-      <c r="B6" s="7" t="inlineStr">
+      <c r="B6" s="8" t="inlineStr">
         <is>
           <t>P2</t>
         </is>
@@ -1870,20 +2027,20 @@
           <t>LMP事業 · Web・ツール・システム</t>
         </is>
       </c>
-      <c r="E6" s="12" t="inlineStr">
+      <c r="E6" s="13" t="inlineStr">
         <is>
           <t>社長・白石・片山</t>
         </is>
       </c>
-      <c r="F6" s="28" t="n">
+      <c r="F6" s="31" t="n">
         <v>0.5</v>
       </c>
-      <c r="G6" s="19" t="inlineStr">
+      <c r="G6" s="32" t="inlineStr">
         <is>
           <t>進行中</t>
         </is>
       </c>
-      <c r="H6" s="29" t="n"/>
+      <c r="H6" s="33" t="n"/>
       <c r="I6" s="5" t="inlineStr">
         <is>
           <t>加盟店が学ぶ画面そのもの</t>
@@ -1891,12 +2048,12 @@
       </c>
     </row>
     <row r="7" ht="32" customHeight="1">
-      <c r="A7" s="12" t="inlineStr">
+      <c r="A7" s="13" t="inlineStr">
         <is>
           <t>教材・ツール</t>
         </is>
       </c>
-      <c r="B7" s="7" t="inlineStr">
+      <c r="B7" s="8" t="inlineStr">
         <is>
           <t>P2</t>
         </is>
@@ -1911,20 +2068,20 @@
           <t>LMP事業 · Web・ツール・システム</t>
         </is>
       </c>
-      <c r="E7" s="30" t="inlineStr">
+      <c r="E7" s="34" t="inlineStr">
         <is>
           <t>未定</t>
         </is>
       </c>
-      <c r="F7" s="28" t="n">
+      <c r="F7" s="31" t="n">
         <v>0.2</v>
       </c>
-      <c r="G7" s="19" t="inlineStr">
+      <c r="G7" s="32" t="inlineStr">
         <is>
           <t>進行中</t>
         </is>
       </c>
-      <c r="H7" s="29" t="n"/>
+      <c r="H7" s="33" t="n"/>
       <c r="I7" s="5" t="inlineStr">
         <is>
           <t>教材の中で流す動画。担当が決まっていない</t>
@@ -1932,12 +2089,12 @@
       </c>
     </row>
     <row r="8" ht="32" customHeight="1">
-      <c r="A8" s="12" t="inlineStr">
+      <c r="A8" s="13" t="inlineStr">
         <is>
           <t>教材・ツール</t>
         </is>
       </c>
-      <c r="B8" s="7" t="inlineStr">
+      <c r="B8" s="8" t="inlineStr">
         <is>
           <t>P2</t>
         </is>
@@ -1952,20 +2109,20 @@
           <t>RC事業 · Web・ツール・システム</t>
         </is>
       </c>
-      <c r="E8" s="12" t="inlineStr">
+      <c r="E8" s="13" t="inlineStr">
         <is>
           <t>白石</t>
         </is>
       </c>
-      <c r="F8" s="28" t="n">
+      <c r="F8" s="31" t="n">
         <v>0.8</v>
       </c>
-      <c r="G8" s="19" t="inlineStr">
+      <c r="G8" s="32" t="inlineStr">
         <is>
           <t>進行中</t>
         </is>
       </c>
-      <c r="H8" s="29" t="n"/>
+      <c r="H8" s="33" t="n"/>
       <c r="I8" s="5" t="inlineStr">
         <is>
           <t>学ぶ前に現在地をはかる</t>
@@ -1973,12 +2130,12 @@
       </c>
     </row>
     <row r="9" ht="32" customHeight="1">
-      <c r="A9" s="12" t="inlineStr">
+      <c r="A9" s="13" t="inlineStr">
         <is>
           <t>教材・ツール</t>
         </is>
       </c>
-      <c r="B9" s="7" t="inlineStr">
+      <c r="B9" s="8" t="inlineStr">
         <is>
           <t>P2</t>
         </is>
@@ -1993,20 +2150,20 @@
           <t>RC事業 · 動画・コンテンツ</t>
         </is>
       </c>
-      <c r="E9" s="12" t="inlineStr">
+      <c r="E9" s="13" t="inlineStr">
         <is>
           <t>白石</t>
         </is>
       </c>
-      <c r="F9" s="28" t="n">
+      <c r="F9" s="31" t="n">
         <v>0.6</v>
       </c>
-      <c r="G9" s="19" t="inlineStr">
+      <c r="G9" s="32" t="inlineStr">
         <is>
           <t>進行中</t>
         </is>
       </c>
-      <c r="H9" s="29" t="n"/>
+      <c r="H9" s="33" t="n"/>
       <c r="I9" s="5" t="inlineStr">
         <is>
           <t>教材のもとになる原稿</t>
@@ -2014,12 +2171,12 @@
       </c>
     </row>
     <row r="10" ht="32" customHeight="1">
-      <c r="A10" s="12" t="inlineStr">
+      <c r="A10" s="13" t="inlineStr">
         <is>
           <t>教材・ツール</t>
         </is>
       </c>
-      <c r="B10" s="7" t="inlineStr">
+      <c r="B10" s="8" t="inlineStr">
         <is>
           <t>P2</t>
         </is>
@@ -2034,20 +2191,20 @@
           <t>LMP事業 · 営業・資料</t>
         </is>
       </c>
-      <c r="E10" s="30" t="inlineStr">
+      <c r="E10" s="34" t="inlineStr">
         <is>
           <t>未定</t>
         </is>
       </c>
-      <c r="F10" s="28" t="n">
+      <c r="F10" s="31" t="n">
         <v>0</v>
       </c>
-      <c r="G10" s="23" t="inlineStr">
+      <c r="G10" s="35" t="inlineStr">
         <is>
           <t>未着手</t>
         </is>
       </c>
-      <c r="H10" s="29" t="n"/>
+      <c r="H10" s="33" t="n"/>
       <c r="I10" s="5" t="inlineStr">
         <is>
           <t>担当が決まっていない</t>
@@ -2055,12 +2212,12 @@
       </c>
     </row>
     <row r="11" ht="32" customHeight="1">
-      <c r="A11" s="12" t="inlineStr">
+      <c r="A11" s="13" t="inlineStr">
         <is>
           <t>教材・ツール</t>
         </is>
       </c>
-      <c r="B11" s="7" t="inlineStr">
+      <c r="B11" s="8" t="inlineStr">
         <is>
           <t>P2</t>
         </is>
@@ -2075,29 +2232,29 @@
           <t>LMP事業 · 加盟開発</t>
         </is>
       </c>
-      <c r="E11" s="12" t="inlineStr">
+      <c r="E11" s="13" t="inlineStr">
         <is>
           <t>白石・池之上・大熊</t>
         </is>
       </c>
-      <c r="F11" s="28" t="n">
+      <c r="F11" s="31" t="n">
         <v>0</v>
       </c>
-      <c r="G11" s="23" t="inlineStr">
+      <c r="G11" s="35" t="inlineStr">
         <is>
           <t>未着手</t>
         </is>
       </c>
-      <c r="H11" s="29" t="n"/>
+      <c r="H11" s="33" t="n"/>
       <c r="I11" s="5" t="inlineStr"/>
     </row>
     <row r="12" ht="32" customHeight="1">
-      <c r="A12" s="12" t="inlineStr">
+      <c r="A12" s="13" t="inlineStr">
         <is>
           <t>教材・ツール</t>
         </is>
       </c>
-      <c r="B12" s="7" t="inlineStr">
+      <c r="B12" s="8" t="inlineStr">
         <is>
           <t>P2</t>
         </is>
@@ -2112,29 +2269,29 @@
           <t>RCP事業 · Web・ツール・システム</t>
         </is>
       </c>
-      <c r="E12" s="12" t="inlineStr">
+      <c r="E12" s="13" t="inlineStr">
         <is>
           <t>白石</t>
         </is>
       </c>
-      <c r="F12" s="28" t="n">
+      <c r="F12" s="31" t="n">
         <v>0</v>
       </c>
-      <c r="G12" s="23" t="inlineStr">
+      <c r="G12" s="35" t="inlineStr">
         <is>
           <t>未着手</t>
         </is>
       </c>
-      <c r="H12" s="29" t="n"/>
+      <c r="H12" s="33" t="n"/>
       <c r="I12" s="5" t="inlineStr"/>
     </row>
     <row r="13" ht="32" customHeight="1">
-      <c r="A13" s="12" t="inlineStr">
+      <c r="A13" s="13" t="inlineStr">
         <is>
           <t>教材・ツール</t>
         </is>
       </c>
-      <c r="B13" s="7" t="inlineStr">
+      <c r="B13" s="8" t="inlineStr">
         <is>
           <t>P2</t>
         </is>
@@ -2149,20 +2306,20 @@
           <t>AIアオ先生 · 営業コーチ</t>
         </is>
       </c>
-      <c r="E13" s="12" t="inlineStr">
+      <c r="E13" s="13" t="inlineStr">
         <is>
           <t>池之上</t>
         </is>
       </c>
-      <c r="F13" s="28" t="n">
+      <c r="F13" s="31" t="n">
         <v>0.9</v>
       </c>
-      <c r="G13" s="6" t="inlineStr">
+      <c r="G13" s="36" t="inlineStr">
         <is>
           <t>確認待ち</t>
         </is>
       </c>
-      <c r="H13" s="29" t="n"/>
+      <c r="H13" s="33" t="n"/>
       <c r="I13" s="5" t="inlineStr">
         <is>
           <t>制作MASTERのみに記載</t>
@@ -2170,12 +2327,12 @@
       </c>
     </row>
     <row r="14" ht="32" customHeight="1">
-      <c r="A14" s="12" t="inlineStr">
+      <c r="A14" s="13" t="inlineStr">
         <is>
           <t>動画</t>
         </is>
       </c>
-      <c r="B14" s="7" t="inlineStr">
+      <c r="B14" s="8" t="inlineStr">
         <is>
           <t>P2</t>
         </is>
@@ -2190,20 +2347,20 @@
           <t>RC事業 · 動画・コンテンツ</t>
         </is>
       </c>
-      <c r="E14" s="12" t="inlineStr">
+      <c r="E14" s="13" t="inlineStr">
         <is>
           <t>白石</t>
         </is>
       </c>
-      <c r="F14" s="28" t="n">
+      <c r="F14" s="31" t="n">
         <v>0.7</v>
       </c>
-      <c r="G14" s="19" t="inlineStr">
+      <c r="G14" s="32" t="inlineStr">
         <is>
           <t>進行中</t>
         </is>
       </c>
-      <c r="H14" s="29" t="n"/>
+      <c r="H14" s="33" t="n"/>
       <c r="I14" s="5" t="inlineStr">
         <is>
           <t>動画で唯一動いている1本</t>
@@ -2211,12 +2368,12 @@
       </c>
     </row>
     <row r="15" ht="32" customHeight="1">
-      <c r="A15" s="12" t="inlineStr">
+      <c r="A15" s="13" t="inlineStr">
         <is>
           <t>動画</t>
         </is>
       </c>
-      <c r="B15" s="7" t="inlineStr">
+      <c r="B15" s="8" t="inlineStr">
         <is>
           <t>P2</t>
         </is>
@@ -2231,29 +2388,29 @@
           <t>RC事業 · 動画・コンテンツ</t>
         </is>
       </c>
-      <c r="E15" s="12" t="inlineStr">
+      <c r="E15" s="13" t="inlineStr">
         <is>
           <t>白石</t>
         </is>
       </c>
-      <c r="F15" s="28" t="n">
+      <c r="F15" s="31" t="n">
         <v>0</v>
       </c>
-      <c r="G15" s="23" t="inlineStr">
+      <c r="G15" s="35" t="inlineStr">
         <is>
           <t>未着手</t>
         </is>
       </c>
-      <c r="H15" s="29" t="n"/>
+      <c r="H15" s="33" t="n"/>
       <c r="I15" s="5" t="inlineStr"/>
     </row>
     <row r="16" ht="32" customHeight="1">
-      <c r="A16" s="12" t="inlineStr">
+      <c r="A16" s="13" t="inlineStr">
         <is>
           <t>動画</t>
         </is>
       </c>
-      <c r="B16" s="7" t="inlineStr">
+      <c r="B16" s="8" t="inlineStr">
         <is>
           <t>P2</t>
         </is>
@@ -2268,29 +2425,29 @@
           <t>RC事業 · 動画・コンテンツ</t>
         </is>
       </c>
-      <c r="E16" s="12" t="inlineStr">
+      <c r="E16" s="13" t="inlineStr">
         <is>
           <t>白石</t>
         </is>
       </c>
-      <c r="F16" s="28" t="n">
+      <c r="F16" s="31" t="n">
         <v>0</v>
       </c>
-      <c r="G16" s="23" t="inlineStr">
+      <c r="G16" s="35" t="inlineStr">
         <is>
           <t>未着手</t>
         </is>
       </c>
-      <c r="H16" s="29" t="n"/>
+      <c r="H16" s="33" t="n"/>
       <c r="I16" s="5" t="inlineStr"/>
     </row>
     <row r="17" ht="32" customHeight="1">
-      <c r="A17" s="12" t="inlineStr">
+      <c r="A17" s="13" t="inlineStr">
         <is>
           <t>動画</t>
         </is>
       </c>
-      <c r="B17" s="7" t="inlineStr">
+      <c r="B17" s="8" t="inlineStr">
         <is>
           <t>P2</t>
         </is>
@@ -2305,29 +2462,29 @@
           <t>RCP事業 · 動画・コンテンツ</t>
         </is>
       </c>
-      <c r="E17" s="12" t="inlineStr">
+      <c r="E17" s="13" t="inlineStr">
         <is>
           <t>白石</t>
         </is>
       </c>
-      <c r="F17" s="28" t="n">
+      <c r="F17" s="31" t="n">
         <v>0</v>
       </c>
-      <c r="G17" s="23" t="inlineStr">
+      <c r="G17" s="35" t="inlineStr">
         <is>
           <t>未着手</t>
         </is>
       </c>
-      <c r="H17" s="29" t="n"/>
+      <c r="H17" s="33" t="n"/>
       <c r="I17" s="5" t="inlineStr"/>
     </row>
     <row r="18" ht="32" customHeight="1">
-      <c r="A18" s="12" t="inlineStr">
+      <c r="A18" s="13" t="inlineStr">
         <is>
           <t>動画</t>
         </is>
       </c>
-      <c r="B18" s="7" t="inlineStr">
+      <c r="B18" s="8" t="inlineStr">
         <is>
           <t>P2</t>
         </is>
@@ -2342,29 +2499,29 @@
           <t>RCP事業 · 動画・コンテンツ</t>
         </is>
       </c>
-      <c r="E18" s="12" t="inlineStr">
+      <c r="E18" s="13" t="inlineStr">
         <is>
           <t>白石</t>
         </is>
       </c>
-      <c r="F18" s="28" t="n">
+      <c r="F18" s="31" t="n">
         <v>0</v>
       </c>
-      <c r="G18" s="23" t="inlineStr">
+      <c r="G18" s="35" t="inlineStr">
         <is>
           <t>未着手</t>
         </is>
       </c>
-      <c r="H18" s="29" t="n"/>
+      <c r="H18" s="33" t="n"/>
       <c r="I18" s="5" t="inlineStr"/>
     </row>
     <row r="19" ht="32" customHeight="1">
-      <c r="A19" s="12" t="inlineStr">
+      <c r="A19" s="13" t="inlineStr">
         <is>
           <t>動画</t>
         </is>
       </c>
-      <c r="B19" s="7" t="inlineStr">
+      <c r="B19" s="8" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -2379,20 +2536,20 @@
           <t>RCP PPモデル · OEM</t>
         </is>
       </c>
-      <c r="E19" s="12" t="inlineStr">
+      <c r="E19" s="13" t="inlineStr">
         <is>
           <t>白石</t>
         </is>
       </c>
-      <c r="F19" s="28" t="n">
+      <c r="F19" s="31" t="n">
         <v>0</v>
       </c>
-      <c r="G19" s="23" t="inlineStr">
+      <c r="G19" s="35" t="inlineStr">
         <is>
           <t>未着手</t>
         </is>
       </c>
-      <c r="H19" s="29" t="n"/>
+      <c r="H19" s="33" t="n"/>
       <c r="I19" s="5" t="inlineStr">
         <is>
           <t>AKさん・大橋会長・木原さん・水谷先生・藤田先生</t>
@@ -2400,12 +2557,12 @@
       </c>
     </row>
     <row r="20" ht="32" customHeight="1">
-      <c r="A20" s="12" t="inlineStr">
+      <c r="A20" s="13" t="inlineStr">
         <is>
           <t>動画</t>
         </is>
       </c>
-      <c r="B20" s="7" t="inlineStr">
+      <c r="B20" s="8" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -2420,29 +2577,29 @@
           <t>RC／RCP／HI／PP · REALIZE QUEST</t>
         </is>
       </c>
-      <c r="E20" s="12" t="inlineStr">
+      <c r="E20" s="13" t="inlineStr">
         <is>
           <t>白石・片山</t>
         </is>
       </c>
-      <c r="F20" s="28" t="n">
+      <c r="F20" s="31" t="n">
         <v>0</v>
       </c>
-      <c r="G20" s="23" t="inlineStr">
+      <c r="G20" s="35" t="inlineStr">
         <is>
           <t>未着手</t>
         </is>
       </c>
-      <c r="H20" s="29" t="n"/>
+      <c r="H20" s="33" t="n"/>
       <c r="I20" s="5" t="inlineStr"/>
     </row>
     <row r="21" ht="32" customHeight="1">
-      <c r="A21" s="12" t="inlineStr">
+      <c r="A21" s="13" t="inlineStr">
         <is>
           <t>動画</t>
         </is>
       </c>
-      <c r="B21" s="7" t="inlineStr">
+      <c r="B21" s="8" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -2457,20 +2614,20 @@
           <t>採用 · 学生募集</t>
         </is>
       </c>
-      <c r="E21" s="12" t="inlineStr">
+      <c r="E21" s="13" t="inlineStr">
         <is>
           <t>白石・片山</t>
         </is>
       </c>
-      <c r="F21" s="28" t="n">
+      <c r="F21" s="31" t="n">
         <v>0</v>
       </c>
-      <c r="G21" s="23" t="inlineStr">
+      <c r="G21" s="35" t="inlineStr">
         <is>
           <t>未着手</t>
         </is>
       </c>
-      <c r="H21" s="29" t="n"/>
+      <c r="H21" s="33" t="n"/>
       <c r="I21" s="5" t="inlineStr">
         <is>
           <t>PR動画・SNS採用募集動画</t>
@@ -2478,33 +2635,33 @@
       </c>
     </row>
     <row r="22">
-      <c r="E22" s="24" t="inlineStr">
+      <c r="E22" s="25" t="inlineStr">
         <is>
           <t>平均</t>
         </is>
       </c>
-      <c r="F22" s="31">
+      <c r="F22" s="37">
         <f>AVERAGE(F6:F21)</f>
         <v/>
       </c>
-      <c r="G22" s="27">
+      <c r="G22" s="28">
         <f>COUNTIF(G6:G21,"未着手")&amp;" 件未着手"</f>
         <v/>
       </c>
-      <c r="H22" s="27">
+      <c r="H22" s="28">
         <f>COUNTA(H6:H21)&amp;" 件 登録済み"</f>
         <v/>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="32" t="inlineStr">
+      <c r="A24" s="38" t="inlineStr">
         <is>
           <t>できている設計書・ガイド</t>
         </is>
       </c>
     </row>
     <row r="25">
-      <c r="C25" s="33" t="inlineStr">
+      <c r="C25" s="39" t="inlineStr">
         <is>
           <t>LIFE CHECK42 Eラーニング画面設計書</t>
         </is>
@@ -2519,14 +2676,14 @@
           <t>2026-08-31</t>
         </is>
       </c>
-      <c r="I25" s="34" t="inlineStr">
+      <c r="I25" s="40" t="inlineStr">
         <is>
           <t>開く</t>
         </is>
       </c>
     </row>
     <row r="26">
-      <c r="C26" s="33" t="inlineStr">
+      <c r="C26" s="39" t="inlineStr">
         <is>
           <t>RCP ノーマル版 eラーニング｜UI提案 v1</t>
         </is>
@@ -2541,14 +2698,14 @@
           <t>2026-08-05</t>
         </is>
       </c>
-      <c r="I26" s="34" t="inlineStr">
+      <c r="I26" s="40" t="inlineStr">
         <is>
           <t>開く</t>
         </is>
       </c>
     </row>
     <row r="27">
-      <c r="C27" s="33" t="inlineStr">
+      <c r="C27" s="39" t="inlineStr">
         <is>
           <t>AIロープレ 操作ガイド</t>
         </is>
@@ -2563,14 +2720,14 @@
           <t>2026-08-31</t>
         </is>
       </c>
-      <c r="I27" s="34" t="inlineStr">
+      <c r="I27" s="40" t="inlineStr">
         <is>
           <t>開く</t>
         </is>
       </c>
     </row>
     <row r="28">
-      <c r="C28" s="33" t="inlineStr">
+      <c r="C28" s="39" t="inlineStr">
         <is>
           <t>生成AI動画講座 比較検討</t>
         </is>
@@ -2585,7 +2742,7 @@
           <t>2026-08-21</t>
         </is>
       </c>
-      <c r="I28" s="34" t="inlineStr">
+      <c r="I28" s="40" t="inlineStr">
         <is>
           <t>開く</t>
         </is>
@@ -2594,10 +2751,22 @@
   </sheetData>
   <autoFilter ref="A5:I21"/>
   <conditionalFormatting sqref="F6:F21">
-    <cfRule type="cellIs" priority="1" operator="equal" dxfId="3">
-      <formula>0</formula>
+    <cfRule type="dataBar" priority="1">
+      <dataBar showValue="1">
+        <cfvo type="num" val="0"/>
+        <cfvo type="num" val="1"/>
+        <color rgb="001F4E6B"/>
+      </dataBar>
     </cfRule>
   </conditionalFormatting>
+  <dataValidations count="2">
+    <dataValidation sqref="F6:F21" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" promptTitle="進捗を選ぶ" prompt="5%きざみで選べます。直接入力もできます。" type="list">
+      <formula1>'選択肢'!$A$2:$A$22</formula1>
+    </dataValidation>
+    <dataValidation sqref="G6:G21" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" promptTitle="状態を選ぶ" prompt="未着手／進行中／確認待ち" type="list">
+      <formula1>"未着手,進行中,確認待ち"</formula1>
+    </dataValidation>
+  </dataValidations>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I25" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I26" r:id="rId2"/>
@@ -2609,7 +2778,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -2698,12 +2867,12 @@
       </c>
     </row>
     <row r="6" ht="32" customHeight="1">
-      <c r="A6" s="12" t="inlineStr">
+      <c r="A6" s="13" t="inlineStr">
         <is>
           <t>広告</t>
         </is>
       </c>
-      <c r="B6" s="7" t="inlineStr">
+      <c r="B6" s="8" t="inlineStr">
         <is>
           <t>P2</t>
         </is>
@@ -2718,20 +2887,20 @@
           <t>RC法人開拓 · 地域企業への入口</t>
         </is>
       </c>
-      <c r="E6" s="12" t="inlineStr">
+      <c r="E6" s="13" t="inlineStr">
         <is>
           <t>大熊・片山</t>
         </is>
       </c>
-      <c r="F6" s="28" t="n">
+      <c r="F6" s="31" t="n">
         <v>0</v>
       </c>
-      <c r="G6" s="23" t="inlineStr">
+      <c r="G6" s="35" t="inlineStr">
         <is>
           <t>未着手</t>
         </is>
       </c>
-      <c r="H6" s="29" t="n"/>
+      <c r="H6" s="33" t="n"/>
       <c r="I6" s="5" t="inlineStr">
         <is>
           <t>バナー・原稿などのクリエイティブ</t>
@@ -2739,12 +2908,12 @@
       </c>
     </row>
     <row r="7" ht="32" customHeight="1">
-      <c r="A7" s="12" t="inlineStr">
+      <c r="A7" s="13" t="inlineStr">
         <is>
           <t>広告</t>
         </is>
       </c>
-      <c r="B7" s="7" t="inlineStr">
+      <c r="B7" s="8" t="inlineStr">
         <is>
           <t>P2</t>
         </is>
@@ -2759,20 +2928,20 @@
           <t>RC法人開拓／LMP加盟開発</t>
         </is>
       </c>
-      <c r="E7" s="12" t="inlineStr">
+      <c r="E7" s="13" t="inlineStr">
         <is>
           <t>池之上・片山</t>
         </is>
       </c>
-      <c r="F7" s="28" t="n">
+      <c r="F7" s="31" t="n">
         <v>0</v>
       </c>
-      <c r="G7" s="23" t="inlineStr">
+      <c r="G7" s="35" t="inlineStr">
         <is>
           <t>未着手</t>
         </is>
       </c>
-      <c r="H7" s="29" t="n"/>
+      <c r="H7" s="33" t="n"/>
       <c r="I7" s="5" t="inlineStr">
         <is>
           <t>出稿・予算・改善</t>
@@ -2780,12 +2949,12 @@
       </c>
     </row>
     <row r="8" ht="32" customHeight="1">
-      <c r="A8" s="12" t="inlineStr">
+      <c r="A8" s="13" t="inlineStr">
         <is>
           <t>広告</t>
         </is>
       </c>
-      <c r="B8" s="7" t="inlineStr">
+      <c r="B8" s="8" t="inlineStr">
         <is>
           <t>P2</t>
         </is>
@@ -2800,20 +2969,20 @@
           <t>LMP事業 · 全体品質確認</t>
         </is>
       </c>
-      <c r="E8" s="12" t="inlineStr">
+      <c r="E8" s="13" t="inlineStr">
         <is>
           <t>白石</t>
         </is>
       </c>
-      <c r="F8" s="28" t="n">
+      <c r="F8" s="31" t="n">
         <v>0</v>
       </c>
-      <c r="G8" s="23" t="inlineStr">
+      <c r="G8" s="35" t="inlineStr">
         <is>
           <t>未着手</t>
         </is>
       </c>
-      <c r="H8" s="29" t="n"/>
+      <c r="H8" s="33" t="n"/>
       <c r="I8" s="5" t="inlineStr">
         <is>
           <t>出す前の品質確認</t>
@@ -2821,12 +2990,12 @@
       </c>
     </row>
     <row r="9" ht="32" customHeight="1">
-      <c r="A9" s="12" t="inlineStr">
+      <c r="A9" s="13" t="inlineStr">
         <is>
           <t>広告</t>
         </is>
       </c>
-      <c r="B9" s="7" t="inlineStr">
+      <c r="B9" s="8" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -2841,20 +3010,20 @@
           <t>社内業務 · 法務・業法</t>
         </is>
       </c>
-      <c r="E9" s="12" t="inlineStr">
+      <c r="E9" s="13" t="inlineStr">
         <is>
           <t>社長・寺井・池之上・弁護士</t>
         </is>
       </c>
-      <c r="F9" s="28" t="n">
+      <c r="F9" s="31" t="n">
         <v>0</v>
       </c>
-      <c r="G9" s="23" t="inlineStr">
+      <c r="G9" s="35" t="inlineStr">
         <is>
           <t>未着手</t>
         </is>
       </c>
-      <c r="H9" s="29" t="n"/>
+      <c r="H9" s="33" t="n"/>
       <c r="I9" s="5" t="inlineStr">
         <is>
           <t>言い切り表現・実績表示の法務確認</t>
@@ -2862,12 +3031,12 @@
       </c>
     </row>
     <row r="10" ht="32" customHeight="1">
-      <c r="A10" s="12" t="inlineStr">
+      <c r="A10" s="13" t="inlineStr">
         <is>
           <t>広告</t>
         </is>
       </c>
-      <c r="B10" s="7" t="inlineStr">
+      <c r="B10" s="8" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -2882,37 +3051,37 @@
           <t>RC／RCP／HI／PP · REALIZE QUEST</t>
         </is>
       </c>
-      <c r="E10" s="12" t="inlineStr">
+      <c r="E10" s="13" t="inlineStr">
         <is>
           <t>白石</t>
         </is>
       </c>
-      <c r="F10" s="28" t="n">
+      <c r="F10" s="31" t="n">
         <v>0</v>
       </c>
-      <c r="G10" s="23" t="inlineStr">
+      <c r="G10" s="35" t="inlineStr">
         <is>
           <t>未着手</t>
         </is>
       </c>
-      <c r="H10" s="29" t="n"/>
+      <c r="H10" s="33" t="n"/>
       <c r="I10" s="5" t="inlineStr"/>
     </row>
     <row r="11">
-      <c r="E11" s="24" t="inlineStr">
+      <c r="E11" s="25" t="inlineStr">
         <is>
           <t>平均</t>
         </is>
       </c>
-      <c r="F11" s="31">
+      <c r="F11" s="37">
         <f>AVERAGE(F6:F10)</f>
         <v/>
       </c>
-      <c r="G11" s="27">
+      <c r="G11" s="28">
         <f>COUNTIF(G6:G10,"未着手")&amp;" 件未着手"</f>
         <v/>
       </c>
-      <c r="H11" s="27">
+      <c r="H11" s="28">
         <f>COUNTA(H6:H10)&amp;" 件 登録済み"</f>
         <v/>
       </c>
@@ -2920,22 +3089,34 @@
   </sheetData>
   <autoFilter ref="A5:I10"/>
   <conditionalFormatting sqref="F6:F10">
-    <cfRule type="cellIs" priority="1" operator="equal" dxfId="3">
-      <formula>0</formula>
+    <cfRule type="dataBar" priority="1">
+      <dataBar showValue="1">
+        <cfvo type="num" val="0"/>
+        <cfvo type="num" val="1"/>
+        <color rgb="001F4E6B"/>
+      </dataBar>
     </cfRule>
   </conditionalFormatting>
+  <dataValidations count="2">
+    <dataValidation sqref="F6:F10" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" promptTitle="進捗を選ぶ" prompt="5%きざみで選べます。直接入力もできます。" type="list">
+      <formula1>'選択肢'!$A$2:$A$22</formula1>
+    </dataValidation>
+    <dataValidation sqref="G6:G10" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" promptTitle="状態を選ぶ" prompt="未着手／進行中／確認待ち" type="list">
+      <formula1>"未着手,進行中,確認待ち"</formula1>
+    </dataValidation>
+  </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="anysvml"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B30"/>
+  <dimension ref="A1:B34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -2943,270 +3124,318 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="35" t="inlineStr">
+      <c r="A1" s="41" t="inlineStr">
         <is>
           <t>凡例と出典</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="36" t="inlineStr">
+      <c r="A3" s="42" t="inlineStr">
         <is>
           <t>LPシートの4段</t>
         </is>
       </c>
     </row>
     <row r="4" ht="36" customHeight="1">
-      <c r="A4" s="37" t="inlineStr">
+      <c r="A4" s="43" t="inlineStr">
         <is>
           <t>①原稿・デザイン</t>
         </is>
       </c>
-      <c r="B4" s="38" t="inlineStr">
+      <c r="B4" s="44" t="inlineStr">
         <is>
           <t>本編の文章とデザインが最後まで通っている</t>
         </is>
       </c>
     </row>
     <row r="5" ht="36" customHeight="1">
-      <c r="A5" s="37" t="inlineStr">
+      <c r="A5" s="43" t="inlineStr">
         <is>
           <t>②付随ページ</t>
         </is>
       </c>
-      <c r="B5" s="38" t="inlineStr">
+      <c r="B5" s="44" t="inlineStr">
         <is>
           <t>資料請求・会社概要など、必要な付随ページが揃っている</t>
         </is>
       </c>
     </row>
     <row r="6" ht="36" customHeight="1">
-      <c r="A6" s="37" t="inlineStr">
+      <c r="A6" s="43" t="inlineStr">
         <is>
           <t>③問い合わせ導線</t>
         </is>
       </c>
-      <c r="B6" s="38" t="inlineStr">
+      <c r="B6" s="44" t="inlineStr">
         <is>
           <t>ボタンの行き先が実在し、問い合わせが届く先につながっている</t>
         </is>
       </c>
     </row>
     <row r="7" ht="36" customHeight="1">
-      <c r="A7" s="37" t="inlineStr">
+      <c r="A7" s="43" t="inlineStr">
         <is>
           <t>④本番公開</t>
         </is>
       </c>
-      <c r="B7" s="38" t="inlineStr">
+      <c r="B7" s="44" t="inlineStr">
         <is>
           <t>独自ドメインで公開され、J列に本番URLが入っている（自動判定）</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="36" t="inlineStr">
+      <c r="A9" s="42" t="inlineStr">
         <is>
           <t>記号</t>
         </is>
       </c>
     </row>
     <row r="10" ht="36" customHeight="1">
-      <c r="A10" s="37" t="inlineStr">
+      <c r="A10" s="43" t="inlineStr">
         <is>
           <t>○</t>
         </is>
       </c>
-      <c r="B10" s="38" t="inlineStr">
+      <c r="B10" s="44" t="inlineStr">
         <is>
           <t>できている</t>
         </is>
       </c>
     </row>
     <row r="11" ht="36" customHeight="1">
-      <c r="A11" s="37" t="inlineStr">
+      <c r="A11" s="43" t="inlineStr">
         <is>
           <t>△</t>
         </is>
       </c>
-      <c r="B11" s="38" t="inlineStr">
+      <c r="B11" s="44" t="inlineStr">
         <is>
           <t>仮づけ。メーラーを開くだけ、または行き先が「#」のまま</t>
         </is>
       </c>
     </row>
     <row r="12" ht="36" customHeight="1">
-      <c r="A12" s="37" t="inlineStr">
+      <c r="A12" s="43" t="inlineStr">
         <is>
           <t>×</t>
         </is>
       </c>
-      <c r="B12" s="38" t="inlineStr">
+      <c r="B12" s="44" t="inlineStr">
         <is>
           <t>手つかず／ページが存在しない</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="36" t="inlineStr">
+      <c r="A14" s="42" t="inlineStr">
         <is>
           <t>状態（eラーニング・動画／広告シート）</t>
         </is>
       </c>
     </row>
     <row r="15" ht="36" customHeight="1">
-      <c r="A15" s="37" t="inlineStr">
+      <c r="A15" s="43" t="inlineStr">
         <is>
           <t>確認待ち</t>
         </is>
       </c>
-      <c r="B15" s="38" t="inlineStr">
+      <c r="B15" s="44" t="inlineStr">
         <is>
           <t>作業は終わり、誰かの確認を待っている</t>
         </is>
       </c>
     </row>
     <row r="16" ht="36" customHeight="1">
-      <c r="A16" s="37" t="inlineStr">
+      <c r="A16" s="43" t="inlineStr">
         <is>
           <t>進行中</t>
         </is>
       </c>
-      <c r="B16" s="38" t="inlineStr">
+      <c r="B16" s="44" t="inlineStr">
         <is>
           <t>いま手が動いている</t>
         </is>
       </c>
     </row>
     <row r="17" ht="36" customHeight="1">
-      <c r="A17" s="37" t="inlineStr">
+      <c r="A17" s="43" t="inlineStr">
         <is>
           <t>未着手</t>
         </is>
       </c>
-      <c r="B17" s="38" t="inlineStr">
+      <c r="B17" s="44" t="inlineStr">
         <is>
           <t>まだ始まっていない</t>
         </is>
       </c>
     </row>
     <row r="18" ht="36" customHeight="1">
-      <c r="A18" s="37" t="inlineStr">
+      <c r="A18" s="43" t="inlineStr">
         <is>
           <t>P2／P3</t>
         </is>
       </c>
-      <c r="B18" s="38" t="inlineStr">
+      <c r="B18" s="44" t="inlineStr">
         <is>
           <t>工程表の優先度。P3は「中核が回り出してから戻ってくる」もの</t>
         </is>
       </c>
     </row>
     <row r="19" ht="36" customHeight="1">
-      <c r="A19" s="37" t="inlineStr">
+      <c r="A19" s="43" t="inlineStr">
         <is>
           <t>赤い担当名</t>
         </is>
       </c>
-      <c r="B19" s="38" t="inlineStr">
+      <c r="B19" s="44" t="inlineStr">
         <is>
           <t>担当が「未定」の仕事。誰かを決めないと進みません</t>
         </is>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="36" t="inlineStr">
+      <c r="A21" s="42" t="inlineStr">
         <is>
           <t>使い方</t>
         </is>
       </c>
     </row>
     <row r="22" ht="36" customHeight="1">
-      <c r="A22" s="37" t="inlineStr">
+      <c r="A22" s="43" t="inlineStr">
+        <is>
+          <t>進捗のセル（水色）</t>
+        </is>
+      </c>
+      <c r="B22" s="44" t="inlineStr">
+        <is>
+          <t>クリックすると右に▼が出ます。0%〜100%を5%きざみで選べます（直接入力も可）。選ぶとセルの中のバーがその長さに変わります。</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="36" customHeight="1">
+      <c r="A23" s="43" t="inlineStr">
+        <is>
+          <t>状態のセル（水色）</t>
+        </is>
+      </c>
+      <c r="B23" s="44" t="inlineStr">
+        <is>
+          <t>クリックして 未着手／進行中／確認待ち を選びます。</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="36" customHeight="1">
+      <c r="A24" s="43" t="inlineStr">
+        <is>
+          <t>LPの○△×（水色）</t>
+        </is>
+      </c>
+      <c r="B24" s="44" t="inlineStr">
+        <is>
+          <t>E〜G列。クリックして選び直せます。H列の④本番公開はJ列のURL有無から自動で決まります。</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="36" customHeight="1">
+      <c r="A25" s="43" t="inlineStr">
+        <is>
+          <t>列見出しの▼</t>
+        </is>
+      </c>
+      <c r="B25" s="44" t="inlineStr">
+        <is>
+          <t>各シートの見出し行にオートフィルタが付いています。▼から値を選ぶと、その行だけ表示されます。複数の列を組み合わせられます。</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="36" customHeight="1">
+      <c r="A26" s="43" t="inlineStr">
         <is>
           <t>黄色の記入欄</t>
         </is>
       </c>
-      <c r="B22" s="38" t="inlineStr">
-        <is>
-          <t>公開したURL・動画URL・広告の入稿先を貼ります。ここだけが記入欄です。</t>
-        </is>
-      </c>
-    </row>
-    <row r="23" ht="36" customHeight="1">
-      <c r="A23" s="37" t="inlineStr">
+      <c r="B26" s="44" t="inlineStr">
+        <is>
+          <t>公開したURL・動画URL・広告の入稿先を貼ります。</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="36" customHeight="1">
+      <c r="A27" s="43" t="inlineStr">
         <is>
           <t>自動で動く数字</t>
         </is>
       </c>
-      <c r="B23" s="38" t="inlineStr">
+      <c r="B27" s="44" t="inlineStr">
         <is>
           <t>LPシートは④と到達度、各シートの最下段の平均・件数が数式です。手で書き換えないでください。</t>
         </is>
       </c>
     </row>
-    <row r="25">
-      <c r="A25" s="36" t="inlineStr">
+    <row r="29">
+      <c r="A29" s="42" t="inlineStr">
         <is>
           <t>出典</t>
         </is>
       </c>
     </row>
-    <row r="26" ht="36" customHeight="1">
-      <c r="A26" s="37" t="inlineStr">
+    <row r="30" ht="36" customHeight="1">
+      <c r="A30" s="43" t="inlineStr">
         <is>
           <t>LPシート</t>
         </is>
       </c>
-      <c r="B26" s="38" t="inlineStr">
+      <c r="B30" s="44" t="inlineStr">
         <is>
           <t>公開済みアーティファクト43件のうちLPに該当する22ページ（本編11＋付随11）を、1ページずつHTMLを読んで確認。ボタンの行き先・フォームの送信方法・付随ページの有無は実物ベースです。</t>
         </is>
       </c>
     </row>
-    <row r="27" ht="36" customHeight="1">
-      <c r="A27" s="37" t="inlineStr">
+    <row r="31" ht="36" customHeight="1">
+      <c r="A31" s="43" t="inlineStr">
         <is>
           <t>進捗％と担当</t>
         </is>
       </c>
-      <c r="B27" s="38" t="inlineStr">
+      <c r="B31" s="44" t="inlineStr">
         <is>
           <t>社内の「REALIZE OS 制作MASTER」(2026-09-03) と「仕事の棚卸し」(2026-09-02) の数値をそのまま引いています。</t>
         </is>
       </c>
     </row>
-    <row r="28" ht="36" customHeight="1">
-      <c r="A28" s="37" t="inlineStr">
+    <row r="32" ht="36" customHeight="1">
+      <c r="A32" s="43" t="inlineStr">
         <is>
           <t>担当の食い違い</t>
         </is>
       </c>
-      <c r="B28" s="38" t="inlineStr">
+      <c r="B32" s="44" t="inlineStr">
         <is>
           <t>広告運用の担当は2資料で記載が違います（制作MASTER＝大熊・片山／棚卸し＝池之上・片山）。広告制作は大熊・片山、広告運用は池之上・片山としています。</t>
         </is>
       </c>
     </row>
-    <row r="29" ht="36" customHeight="1">
-      <c r="A29" s="37" t="inlineStr">
+    <row r="33" ht="36" customHeight="1">
+      <c r="A33" s="43" t="inlineStr">
         <is>
           <t>未確認</t>
         </is>
       </c>
-      <c r="B29" s="38" t="inlineStr">
+      <c r="B33" s="44" t="inlineStr">
         <is>
           <t>LP付随ページ4本（RC星空案の会社概要、RCアイス案の資料請求、LMP星空案の資料請求と会社概要）は、親LPからのリンクで存在を確認しただけで中身は開いていません。</t>
         </is>
       </c>
     </row>
-    <row r="30" ht="36" customHeight="1">
-      <c r="A30" s="37" t="inlineStr">
+    <row r="34" ht="36" customHeight="1">
+      <c r="A34" s="43" t="inlineStr">
         <is>
           <t>調査日</t>
         </is>
       </c>
-      <c r="B30" s="38" t="inlineStr">
+      <c r="B34" s="44" t="inlineStr">
         <is>
           <t>2026-09-03</t>
         </is>

--- a/制作進捗ボード.xlsx
+++ b/制作進捗ボード.xlsx
@@ -193,7 +193,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="45">
+  <cellXfs count="42">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -201,11 +201,14 @@
     <xf numFmtId="0" fontId="6" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="8" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -228,11 +231,11 @@
     <xf numFmtId="0" fontId="8" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="8" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -246,19 +249,10 @@
     <xf numFmtId="0" fontId="8" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="11" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -273,10 +267,11 @@
     <xf numFmtId="0" fontId="13" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="9" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="8" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="9" fontId="8" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -284,12 +279,6 @@
     </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="9" fontId="13" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
@@ -879,73 +868,73 @@
           <t>現行</t>
         </is>
       </c>
-      <c r="C6" s="5" t="inlineStr">
+      <c r="C6" s="7" t="inlineStr">
         <is>
           <t>会社が、社員の人生を守る時代へ。</t>
         </is>
       </c>
-      <c r="D6" s="5" t="inlineStr">
+      <c r="D6" s="7" t="inlineStr">
         <is>
           <t>深緑 × 和モダン／昭和と令和の対比</t>
         </is>
       </c>
-      <c r="E6" s="7" t="inlineStr">
+      <c r="E6" s="8" t="inlineStr">
         <is>
           <t>○</t>
         </is>
       </c>
-      <c r="F6" s="7" t="inlineStr">
+      <c r="F6" s="8" t="inlineStr">
         <is>
           <t>○</t>
         </is>
       </c>
-      <c r="G6" s="7" t="inlineStr">
+      <c r="G6" s="8" t="inlineStr">
         <is>
           <t>△</t>
         </is>
       </c>
-      <c r="H6" s="8">
+      <c r="H6" s="9">
         <f>IF(J6="","×","○")</f>
         <v/>
       </c>
-      <c r="I6" s="9">
+      <c r="I6" s="10">
         <f>COUNTIF(E6:H6,"○")+COUNTIF(E6:H6,"△")</f>
         <v/>
       </c>
-      <c r="J6" s="10" t="n"/>
-      <c r="K6" s="5" t="inlineStr">
+      <c r="J6" s="11" t="n"/>
+      <c r="K6" s="7" t="inlineStr">
         <is>
           <t>送信ボタンがメーラーを開くだけ。受付フォームの実装が必要／会社概要ページが未作成／本番ドメインへの公開</t>
         </is>
       </c>
-      <c r="L6" s="11" t="inlineStr">
+      <c r="L6" s="12" t="inlineStr">
         <is>
           <t>資料請求を開く</t>
         </is>
       </c>
-      <c r="M6" s="12" t="inlineStr">
+      <c r="M6" s="13" t="inlineStr">
         <is>
           <t>未作成</t>
         </is>
       </c>
-      <c r="N6" s="11" t="inlineStr">
+      <c r="N6" s="12" t="inlineStr">
         <is>
           <t>LPを開く</t>
         </is>
       </c>
-      <c r="O6" s="13" t="inlineStr">
+      <c r="O6" s="14" t="inlineStr">
         <is>
           <t>08b479a1</t>
         </is>
       </c>
-      <c r="P6" s="8" t="inlineStr">
+      <c r="P6" s="9" t="inlineStr">
         <is>
           <t>2026-09-03</t>
         </is>
       </c>
     </row>
     <row r="7" ht="46" customHeight="1">
-      <c r="A7" s="14" t="inlineStr">
+      <c r="A7" s="5" t="inlineStr">
         <is>
           <t>REALIZE CLUB（法人向け）</t>
         </is>
@@ -955,66 +944,66 @@
           <t>別案</t>
         </is>
       </c>
-      <c r="C7" s="14" t="inlineStr">
+      <c r="C7" s="16" t="inlineStr">
         <is>
           <t>会社が社員の人生を支える時代へ</t>
         </is>
       </c>
-      <c r="D7" s="14" t="inlineStr">
+      <c r="D7" s="16" t="inlineStr">
         <is>
           <t>星空タウン／クリーム × 濃紺のイラスト</t>
         </is>
       </c>
-      <c r="E7" s="7" t="inlineStr">
+      <c r="E7" s="8" t="inlineStr">
         <is>
           <t>○</t>
         </is>
       </c>
-      <c r="F7" s="7" t="inlineStr">
+      <c r="F7" s="8" t="inlineStr">
         <is>
           <t>○</t>
         </is>
       </c>
-      <c r="G7" s="7" t="inlineStr">
+      <c r="G7" s="8" t="inlineStr">
         <is>
           <t>△</t>
         </is>
       </c>
-      <c r="H7" s="16">
+      <c r="H7" s="17">
         <f>IF(J7="","×","○")</f>
         <v/>
       </c>
-      <c r="I7" s="17">
+      <c r="I7" s="18">
         <f>COUNTIF(E7:H7,"○")+COUNTIF(E7:H7,"△")</f>
         <v/>
       </c>
-      <c r="J7" s="10" t="n"/>
-      <c r="K7" s="14" t="inlineStr">
+      <c r="J7" s="11" t="n"/>
+      <c r="K7" s="16" t="inlineStr">
         <is>
           <t>RC案で唯一3ページ揃い。採用するかの判断／送信はメーラー起動のみ</t>
         </is>
       </c>
-      <c r="L7" s="18" t="inlineStr">
+      <c r="L7" s="19" t="inlineStr">
         <is>
           <t>資料請求を開く</t>
         </is>
       </c>
-      <c r="M7" s="18" t="inlineStr">
+      <c r="M7" s="19" t="inlineStr">
         <is>
           <t>会社概要を開く</t>
         </is>
       </c>
-      <c r="N7" s="18" t="inlineStr">
+      <c r="N7" s="19" t="inlineStr">
         <is>
           <t>LPを開く</t>
         </is>
       </c>
-      <c r="O7" s="19" t="inlineStr">
+      <c r="O7" s="20" t="inlineStr">
         <is>
           <t>7355f424</t>
         </is>
       </c>
-      <c r="P7" s="16" t="inlineStr">
+      <c r="P7" s="17" t="inlineStr">
         <is>
           <t>2026-08-31</t>
         </is>
@@ -1026,78 +1015,78 @@
           <t>REALIZE CLUB（法人向け）</t>
         </is>
       </c>
-      <c r="B8" s="20" t="inlineStr">
+      <c r="B8" s="15" t="inlineStr">
         <is>
           <t>別案</t>
         </is>
       </c>
-      <c r="C8" s="5" t="inlineStr">
+      <c r="C8" s="7" t="inlineStr">
         <is>
           <t>困る前に、灯す。</t>
         </is>
       </c>
-      <c r="D8" s="5" t="inlineStr">
+      <c r="D8" s="7" t="inlineStr">
         <is>
           <t>漆黒 × 炎のグラデーション</t>
         </is>
       </c>
-      <c r="E8" s="7" t="inlineStr">
+      <c r="E8" s="8" t="inlineStr">
         <is>
           <t>○</t>
         </is>
       </c>
-      <c r="F8" s="7" t="inlineStr">
+      <c r="F8" s="8" t="inlineStr">
         <is>
           <t>△</t>
         </is>
       </c>
-      <c r="G8" s="7" t="inlineStr">
+      <c r="G8" s="8" t="inlineStr">
         <is>
           <t>×</t>
         </is>
       </c>
-      <c r="H8" s="8">
+      <c r="H8" s="9">
         <f>IF(J8="","×","○")</f>
         <v/>
       </c>
-      <c r="I8" s="9">
+      <c r="I8" s="10">
         <f>COUNTIF(E8:H8,"○")+COUNTIF(E8:H8,"△")</f>
         <v/>
       </c>
-      <c r="J8" s="10" t="n"/>
-      <c r="K8" s="5" t="inlineStr">
+      <c r="J8" s="11" t="n"/>
+      <c r="K8" s="7" t="inlineStr">
         <is>
           <t>kaisha.html ほかへの相対リンクが残り、単体では飛べない／会社概要ページの作成</t>
         </is>
       </c>
-      <c r="L8" s="12" t="inlineStr">
+      <c r="L8" s="13" t="inlineStr">
         <is>
           <t>（同ファイル内）</t>
         </is>
       </c>
-      <c r="M8" s="12" t="inlineStr">
+      <c r="M8" s="13" t="inlineStr">
         <is>
           <t>未作成</t>
         </is>
       </c>
-      <c r="N8" s="11" t="inlineStr">
+      <c r="N8" s="12" t="inlineStr">
         <is>
           <t>LPを開く</t>
         </is>
       </c>
-      <c r="O8" s="13" t="inlineStr">
+      <c r="O8" s="14" t="inlineStr">
         <is>
           <t>ded9a489</t>
         </is>
       </c>
-      <c r="P8" s="8" t="inlineStr">
+      <c r="P8" s="9" t="inlineStr">
         <is>
           <t>2026-08-31</t>
         </is>
       </c>
     </row>
     <row r="9" ht="46" customHeight="1">
-      <c r="A9" s="14" t="inlineStr">
+      <c r="A9" s="5" t="inlineStr">
         <is>
           <t>REALIZE CLUB（法人向け）</t>
         </is>
@@ -1107,41 +1096,41 @@
           <t>別案</t>
         </is>
       </c>
-      <c r="C9" s="14" t="inlineStr">
+      <c r="C9" s="16" t="inlineStr">
         <is>
           <t>その安心、今がお得。</t>
         </is>
       </c>
-      <c r="D9" s="14" t="inlineStr">
+      <c r="D9" s="16" t="inlineStr">
         <is>
           <t>スーパーの特売ポップ／白地に赤と黄</t>
         </is>
       </c>
-      <c r="E9" s="7" t="inlineStr">
+      <c r="E9" s="8" t="inlineStr">
         <is>
           <t>○</t>
         </is>
       </c>
-      <c r="F9" s="7" t="inlineStr">
+      <c r="F9" s="8" t="inlineStr">
         <is>
           <t>△</t>
         </is>
       </c>
-      <c r="G9" s="7" t="inlineStr">
+      <c r="G9" s="8" t="inlineStr">
         <is>
           <t>×</t>
         </is>
       </c>
-      <c r="H9" s="16">
+      <c r="H9" s="17">
         <f>IF(J9="","×","○")</f>
         <v/>
       </c>
-      <c r="I9" s="17">
+      <c r="I9" s="18">
         <f>COUNTIF(E9:H9,"○")+COUNTIF(E9:H9,"△")</f>
         <v/>
       </c>
-      <c r="J9" s="10" t="n"/>
-      <c r="K9" s="14" t="inlineStr">
+      <c r="J9" s="11" t="n"/>
+      <c r="K9" s="16" t="inlineStr">
         <is>
           <t>リンクがすべてページ内アンカー。外部への導線が1本もない／会社概要ページ、送信先の設定</t>
         </is>
@@ -1156,17 +1145,17 @@
           <t>未作成</t>
         </is>
       </c>
-      <c r="N9" s="18" t="inlineStr">
+      <c r="N9" s="19" t="inlineStr">
         <is>
           <t>LPを開く</t>
         </is>
       </c>
-      <c r="O9" s="19" t="inlineStr">
+      <c r="O9" s="20" t="inlineStr">
         <is>
           <t>4ce48691</t>
         </is>
       </c>
-      <c r="P9" s="16" t="inlineStr">
+      <c r="P9" s="17" t="inlineStr">
         <is>
           <t>2026-08-31</t>
         </is>
@@ -1178,147 +1167,147 @@
           <t>REALIZE CLUB（法人向け）</t>
         </is>
       </c>
-      <c r="B10" s="20" t="inlineStr">
+      <c r="B10" s="15" t="inlineStr">
         <is>
           <t>別案</t>
         </is>
       </c>
-      <c r="C10" s="5" t="inlineStr">
+      <c r="C10" s="7" t="inlineStr">
         <is>
           <t>社員が、溶けていく前に。</t>
         </is>
       </c>
-      <c r="D10" s="5" t="inlineStr">
+      <c r="D10" s="7" t="inlineStr">
         <is>
           <t>アイスのメタファー／手描き風</t>
         </is>
       </c>
-      <c r="E10" s="7" t="inlineStr">
+      <c r="E10" s="8" t="inlineStr">
         <is>
           <t>○</t>
         </is>
       </c>
-      <c r="F10" s="7" t="inlineStr">
+      <c r="F10" s="8" t="inlineStr">
         <is>
           <t>△</t>
         </is>
       </c>
-      <c r="G10" s="7" t="inlineStr">
+      <c r="G10" s="8" t="inlineStr">
         <is>
           <t>×</t>
         </is>
       </c>
-      <c r="H10" s="8">
+      <c r="H10" s="9">
         <f>IF(J10="","×","○")</f>
         <v/>
       </c>
-      <c r="I10" s="9">
+      <c r="I10" s="10">
         <f>COUNTIF(E10:H10,"○")+COUNTIF(E10:H10,"△")</f>
         <v/>
       </c>
-      <c r="J10" s="10" t="n"/>
-      <c r="K10" s="5" t="inlineStr">
+      <c r="J10" s="11" t="n"/>
+      <c r="K10" s="7" t="inlineStr">
         <is>
           <t>会社概要ページが未作成／送信はメーラー起動のみ</t>
         </is>
       </c>
-      <c r="L10" s="11" t="inlineStr">
+      <c r="L10" s="12" t="inlineStr">
         <is>
           <t>資料請求を開く</t>
         </is>
       </c>
-      <c r="M10" s="12" t="inlineStr">
+      <c r="M10" s="13" t="inlineStr">
         <is>
           <t>未作成</t>
         </is>
       </c>
-      <c r="N10" s="11" t="inlineStr">
+      <c r="N10" s="12" t="inlineStr">
         <is>
           <t>LPを開く</t>
         </is>
       </c>
-      <c r="O10" s="13" t="inlineStr">
+      <c r="O10" s="14" t="inlineStr">
         <is>
           <t>b0f16478</t>
         </is>
       </c>
-      <c r="P10" s="8" t="inlineStr">
+      <c r="P10" s="9" t="inlineStr">
         <is>
           <t>2026-08-28</t>
         </is>
       </c>
     </row>
     <row r="11" ht="46" customHeight="1">
-      <c r="A11" s="14" t="inlineStr">
+      <c r="A11" s="5" t="inlineStr">
         <is>
           <t>LIFE MAKE PARTNERS（加盟店募集）</t>
         </is>
       </c>
-      <c r="B11" s="22" t="inlineStr">
+      <c r="B11" s="6" t="inlineStr">
         <is>
           <t>現行</t>
         </is>
       </c>
-      <c r="C11" s="14" t="inlineStr">
+      <c r="C11" s="16" t="inlineStr">
         <is>
           <t>家より先に、人生の話を。</t>
         </is>
       </c>
-      <c r="D11" s="14" t="inlineStr">
+      <c r="D11" s="16" t="inlineStr">
         <is>
           <t>韓国料理店の看板／木の壁 × 生成りの横断幕</t>
         </is>
       </c>
-      <c r="E11" s="7" t="inlineStr">
+      <c r="E11" s="8" t="inlineStr">
         <is>
           <t>○</t>
         </is>
       </c>
-      <c r="F11" s="7" t="inlineStr">
+      <c r="F11" s="8" t="inlineStr">
         <is>
           <t>○</t>
         </is>
       </c>
-      <c r="G11" s="7" t="inlineStr">
+      <c r="G11" s="8" t="inlineStr">
         <is>
           <t>○</t>
         </is>
       </c>
-      <c r="H11" s="16">
+      <c r="H11" s="17">
         <f>IF(J11="","×","○")</f>
         <v/>
       </c>
-      <c r="I11" s="17">
+      <c r="I11" s="18">
         <f>COUNTIF(E11:H11,"○")+COUNTIF(E11:H11,"△")</f>
         <v/>
       </c>
-      <c r="J11" s="10" t="n"/>
-      <c r="K11" s="14" t="inlineStr">
+      <c r="J11" s="11" t="n"/>
+      <c r="K11" s="16" t="inlineStr">
         <is>
           <t>本番ドメインへの公開だけが残り。問い合わせはLINE公式（lin.ee/WHYApuM）に集約済み</t>
         </is>
       </c>
-      <c r="L11" s="18" t="inlineStr">
+      <c r="L11" s="19" t="inlineStr">
         <is>
           <t>資料請求を開く</t>
         </is>
       </c>
-      <c r="M11" s="18" t="inlineStr">
+      <c r="M11" s="19" t="inlineStr">
         <is>
           <t>会社概要を開く</t>
         </is>
       </c>
-      <c r="N11" s="18" t="inlineStr">
+      <c r="N11" s="19" t="inlineStr">
         <is>
           <t>LPを開く</t>
         </is>
       </c>
-      <c r="O11" s="19" t="inlineStr">
+      <c r="O11" s="20" t="inlineStr">
         <is>
           <t>7f212d2f</t>
         </is>
       </c>
-      <c r="P11" s="16" t="inlineStr">
+      <c r="P11" s="17" t="inlineStr">
         <is>
           <t>2026-09-03</t>
         </is>
@@ -1330,78 +1319,78 @@
           <t>LIFE MAKE PARTNERS（加盟店募集）</t>
         </is>
       </c>
-      <c r="B12" s="20" t="inlineStr">
+      <c r="B12" s="15" t="inlineStr">
         <is>
           <t>別案</t>
         </is>
       </c>
-      <c r="C12" s="5" t="inlineStr">
+      <c r="C12" s="7" t="inlineStr">
         <is>
           <t>いつも同じ集客ばっかやってんじゃねぇ！</t>
         </is>
       </c>
-      <c r="D12" s="5" t="inlineStr">
+      <c r="D12" s="7" t="inlineStr">
         <is>
           <t>喝・挑発ポスター／赤と黄の斜めストライプ</t>
         </is>
       </c>
-      <c r="E12" s="7" t="inlineStr">
+      <c r="E12" s="8" t="inlineStr">
         <is>
           <t>○</t>
         </is>
       </c>
-      <c r="F12" s="7" t="inlineStr">
+      <c r="F12" s="8" t="inlineStr">
         <is>
           <t>△</t>
         </is>
       </c>
-      <c r="G12" s="7" t="inlineStr">
+      <c r="G12" s="8" t="inlineStr">
         <is>
           <t>×</t>
         </is>
       </c>
-      <c r="H12" s="8">
+      <c r="H12" s="9">
         <f>IF(J12="","×","○")</f>
         <v/>
       </c>
-      <c r="I12" s="9">
+      <c r="I12" s="10">
         <f>COUNTIF(E12:H12,"○")+COUNTIF(E12:H12,"△")</f>
         <v/>
       </c>
-      <c r="J12" s="10" t="n"/>
-      <c r="K12" s="5" t="inlineStr">
+      <c r="J12" s="11" t="n"/>
+      <c r="K12" s="7" t="inlineStr">
         <is>
           <t>kaisha-katsu.html ほかへの相対リンクが残り飛べない／行き先が「#」のままのボタンが2つ</t>
         </is>
       </c>
-      <c r="L12" s="12" t="inlineStr">
+      <c r="L12" s="13" t="inlineStr">
         <is>
           <t>（同ページ内フォーム）</t>
         </is>
       </c>
-      <c r="M12" s="12" t="inlineStr">
+      <c r="M12" s="13" t="inlineStr">
         <is>
           <t>未作成</t>
         </is>
       </c>
-      <c r="N12" s="11" t="inlineStr">
+      <c r="N12" s="12" t="inlineStr">
         <is>
           <t>LPを開く</t>
         </is>
       </c>
-      <c r="O12" s="13" t="inlineStr">
+      <c r="O12" s="14" t="inlineStr">
         <is>
           <t>db82fc95</t>
         </is>
       </c>
-      <c r="P12" s="8" t="inlineStr">
+      <c r="P12" s="9" t="inlineStr">
         <is>
           <t>2026-08-28</t>
         </is>
       </c>
     </row>
     <row r="13" ht="46" customHeight="1">
-      <c r="A13" s="14" t="inlineStr">
+      <c r="A13" s="5" t="inlineStr">
         <is>
           <t>LIFE MAKE PARTNERS（加盟店募集）</t>
         </is>
@@ -1411,66 +1400,66 @@
           <t>別案</t>
         </is>
       </c>
-      <c r="C13" s="14" t="inlineStr">
+      <c r="C13" s="16" t="inlineStr">
         <is>
           <t>加盟資格は、人生への愛。ただそれだけ。</t>
         </is>
       </c>
-      <c r="D13" s="14" t="inlineStr">
+      <c r="D13" s="16" t="inlineStr">
         <is>
           <t>星空タウン／RC星空案と同じ世界観</t>
         </is>
       </c>
-      <c r="E13" s="7" t="inlineStr">
+      <c r="E13" s="8" t="inlineStr">
         <is>
           <t>○</t>
         </is>
       </c>
-      <c r="F13" s="7" t="inlineStr">
+      <c r="F13" s="8" t="inlineStr">
         <is>
           <t>○</t>
         </is>
       </c>
-      <c r="G13" s="7" t="inlineStr">
+      <c r="G13" s="8" t="inlineStr">
         <is>
           <t>△</t>
         </is>
       </c>
-      <c r="H13" s="16">
+      <c r="H13" s="17">
         <f>IF(J13="","×","○")</f>
         <v/>
       </c>
-      <c r="I13" s="17">
+      <c r="I13" s="18">
         <f>COUNTIF(E13:H13,"○")+COUNTIF(E13:H13,"△")</f>
         <v/>
       </c>
-      <c r="J13" s="10" t="n"/>
-      <c r="K13" s="14" t="inlineStr">
+      <c r="J13" s="11" t="n"/>
+      <c r="K13" s="16" t="inlineStr">
         <is>
           <t>行き先が「#」のままのボタンが2つ／現行案との統廃合の判断</t>
         </is>
       </c>
-      <c r="L13" s="18" t="inlineStr">
+      <c r="L13" s="19" t="inlineStr">
         <is>
           <t>資料請求を開く</t>
         </is>
       </c>
-      <c r="M13" s="18" t="inlineStr">
+      <c r="M13" s="19" t="inlineStr">
         <is>
           <t>会社概要を開く</t>
         </is>
       </c>
-      <c r="N13" s="18" t="inlineStr">
+      <c r="N13" s="19" t="inlineStr">
         <is>
           <t>LPを開く</t>
         </is>
       </c>
-      <c r="O13" s="19" t="inlineStr">
+      <c r="O13" s="20" t="inlineStr">
         <is>
           <t>65b43069</t>
         </is>
       </c>
-      <c r="P13" s="16" t="inlineStr">
+      <c r="P13" s="17" t="inlineStr">
         <is>
           <t>2026-08-24</t>
         </is>
@@ -1487,142 +1476,142 @@
           <t>現行</t>
         </is>
       </c>
-      <c r="C14" s="5" t="inlineStr">
+      <c r="C14" s="7" t="inlineStr">
         <is>
           <t>不動産屋が、まちの相談窓口になる。</t>
         </is>
       </c>
-      <c r="D14" s="5" t="inlineStr">
+      <c r="D14" s="7" t="inlineStr">
         <is>
           <t>銭湯ポスター（リソグラフ2色刷り）／LINE誘導版</t>
         </is>
       </c>
-      <c r="E14" s="7" t="inlineStr">
+      <c r="E14" s="8" t="inlineStr">
         <is>
           <t>○</t>
         </is>
       </c>
-      <c r="F14" s="7" t="inlineStr">
+      <c r="F14" s="8" t="inlineStr">
         <is>
           <t>○</t>
         </is>
       </c>
-      <c r="G14" s="7" t="inlineStr">
+      <c r="G14" s="8" t="inlineStr">
         <is>
           <t>△</t>
         </is>
       </c>
-      <c r="H14" s="8">
+      <c r="H14" s="9">
         <f>IF(J14="","×","○")</f>
         <v/>
       </c>
-      <c r="I14" s="9">
+      <c r="I14" s="10">
         <f>COUNTIF(E14:H14,"○")+COUNTIF(E14:H14,"△")</f>
         <v/>
       </c>
-      <c r="J14" s="10" t="n"/>
-      <c r="K14" s="5" t="inlineStr">
+      <c r="J14" s="11" t="n"/>
+      <c r="K14" s="7" t="inlineStr">
         <is>
           <t>行き先が「#」のままのリンクが2つ残っている／本番ドメインへの公開</t>
         </is>
       </c>
-      <c r="L14" s="11" t="inlineStr">
+      <c r="L14" s="12" t="inlineStr">
         <is>
           <t>資料請求を開く</t>
         </is>
       </c>
-      <c r="M14" s="11" t="inlineStr">
+      <c r="M14" s="12" t="inlineStr">
         <is>
           <t>会社概要を開く</t>
         </is>
       </c>
-      <c r="N14" s="11" t="inlineStr">
+      <c r="N14" s="12" t="inlineStr">
         <is>
           <t>LPを開く</t>
         </is>
       </c>
-      <c r="O14" s="13" t="inlineStr">
+      <c r="O14" s="14" t="inlineStr">
         <is>
           <t>1a259364</t>
         </is>
       </c>
-      <c r="P14" s="8" t="inlineStr">
+      <c r="P14" s="9" t="inlineStr">
         <is>
           <t>2026-09-03</t>
         </is>
       </c>
     </row>
     <row r="15" ht="46" customHeight="1">
-      <c r="A15" s="14" t="inlineStr">
+      <c r="A15" s="5" t="inlineStr">
         <is>
           <t>まちの相談窓口</t>
         </is>
       </c>
-      <c r="B15" s="23" t="inlineStr">
+      <c r="B15" s="22" t="inlineStr">
         <is>
           <t>旧版</t>
         </is>
       </c>
-      <c r="C15" s="14" t="inlineStr">
+      <c r="C15" s="16" t="inlineStr">
         <is>
           <t>まちの相談窓口（フォーム版）</t>
         </is>
       </c>
-      <c r="D15" s="14" t="inlineStr">
+      <c r="D15" s="16" t="inlineStr">
         <is>
           <t>銭湯ポスター／申込フォーム内蔵</t>
         </is>
       </c>
-      <c r="E15" s="7" t="inlineStr">
+      <c r="E15" s="8" t="inlineStr">
         <is>
           <t>○</t>
         </is>
       </c>
-      <c r="F15" s="7" t="inlineStr">
+      <c r="F15" s="8" t="inlineStr">
         <is>
           <t>○</t>
         </is>
       </c>
-      <c r="G15" s="7" t="inlineStr">
+      <c r="G15" s="8" t="inlineStr">
         <is>
           <t>△</t>
         </is>
       </c>
-      <c r="H15" s="16">
+      <c r="H15" s="17">
         <f>IF(J15="","×","○")</f>
         <v/>
       </c>
-      <c r="I15" s="17">
+      <c r="I15" s="18">
         <f>COUNTIF(E15:H15,"○")+COUNTIF(E15:H15,"△")</f>
         <v/>
       </c>
-      <c r="J15" s="10" t="n"/>
-      <c r="K15" s="14" t="inlineStr">
+      <c r="J15" s="11" t="n"/>
+      <c r="K15" s="16" t="inlineStr">
         <is>
           <t>現行のLINE誘導版に置き換わっている。残すか消すかの判断</t>
         </is>
       </c>
-      <c r="L15" s="18" t="inlineStr">
+      <c r="L15" s="19" t="inlineStr">
         <is>
           <t>資料請求を開く</t>
         </is>
       </c>
-      <c r="M15" s="18" t="inlineStr">
+      <c r="M15" s="19" t="inlineStr">
         <is>
           <t>会社概要を開く</t>
         </is>
       </c>
-      <c r="N15" s="18" t="inlineStr">
+      <c r="N15" s="19" t="inlineStr">
         <is>
           <t>LPを開く</t>
         </is>
       </c>
-      <c r="O15" s="19" t="inlineStr">
+      <c r="O15" s="20" t="inlineStr">
         <is>
           <t>39f0d878</t>
         </is>
       </c>
-      <c r="P15" s="16" t="inlineStr">
+      <c r="P15" s="17" t="inlineStr">
         <is>
           <t>2026-08-20</t>
         </is>
@@ -1634,103 +1623,103 @@
           <t>不動産FC加盟</t>
         </is>
       </c>
-      <c r="B16" s="24" t="inlineStr">
+      <c r="B16" s="22" t="inlineStr">
         <is>
           <t>単発</t>
         </is>
       </c>
-      <c r="C16" s="5" t="inlineStr">
+      <c r="C16" s="7" t="inlineStr">
         <is>
           <t>収益が積み上がる不動産FC加盟へ。</t>
         </is>
       </c>
-      <c r="D16" s="5" t="inlineStr">
+      <c r="D16" s="7" t="inlineStr">
         <is>
           <t>ボクシング／黒地 × 赤とゴールド</t>
         </is>
       </c>
-      <c r="E16" s="7" t="inlineStr">
+      <c r="E16" s="8" t="inlineStr">
         <is>
           <t>○</t>
         </is>
       </c>
-      <c r="F16" s="7" t="inlineStr">
+      <c r="F16" s="8" t="inlineStr">
         <is>
           <t>×</t>
         </is>
       </c>
-      <c r="G16" s="7" t="inlineStr">
+      <c r="G16" s="8" t="inlineStr">
         <is>
           <t>×</t>
         </is>
       </c>
-      <c r="H16" s="8">
+      <c r="H16" s="9">
         <f>IF(J16="","×","○")</f>
         <v/>
       </c>
-      <c r="I16" s="9">
+      <c r="I16" s="10">
         <f>COUNTIF(E16:H16,"○")+COUNTIF(E16:H16,"△")</f>
         <v/>
       </c>
-      <c r="J16" s="10" t="n"/>
-      <c r="K16" s="5" t="inlineStr">
+      <c r="J16" s="11" t="n"/>
+      <c r="K16" s="7" t="inlineStr">
         <is>
           <t>ページのタイトルタグが空。共有すると名前なしで出る／資料請求・会社概要ページ、送信先の設定</t>
         </is>
       </c>
-      <c r="L16" s="12" t="inlineStr">
+      <c r="L16" s="13" t="inlineStr">
         <is>
           <t>（同ページ内フォーム）</t>
         </is>
       </c>
-      <c r="M16" s="12" t="inlineStr">
+      <c r="M16" s="13" t="inlineStr">
         <is>
           <t>未作成</t>
         </is>
       </c>
-      <c r="N16" s="11" t="inlineStr">
+      <c r="N16" s="12" t="inlineStr">
         <is>
           <t>LPを開く</t>
         </is>
       </c>
-      <c r="O16" s="13" t="inlineStr">
+      <c r="O16" s="14" t="inlineStr">
         <is>
           <t>d5160792</t>
         </is>
       </c>
-      <c r="P16" s="8" t="inlineStr">
+      <c r="P16" s="9" t="inlineStr">
         <is>
           <t>2026-08-19</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="D17" s="25" t="inlineStr">
+      <c r="D17" s="23" t="inlineStr">
         <is>
           <t>合計 / 平均</t>
         </is>
       </c>
-      <c r="E17" s="26">
+      <c r="E17" s="24">
         <f>COUNTIF(E6:E16,"○")</f>
         <v/>
       </c>
-      <c r="F17" s="26">
+      <c r="F17" s="24">
         <f>COUNTIF(F6:F16,"○")</f>
         <v/>
       </c>
-      <c r="G17" s="26">
+      <c r="G17" s="24">
         <f>COUNTIF(G6:G16,"○")</f>
         <v/>
       </c>
-      <c r="H17" s="26">
+      <c r="H17" s="24">
         <f>COUNTIF(H6:H16,"○")</f>
         <v/>
       </c>
-      <c r="I17" s="27">
+      <c r="I17" s="25">
         <f>AVERAGE(I6:I16)</f>
         <v/>
       </c>
-      <c r="J17" s="28">
+      <c r="J17" s="26">
         <f>COUNTA(J6:J16)&amp;" 本 公開済み"</f>
         <v/>
       </c>
@@ -1757,9 +1746,15 @@
       </dataBar>
     </cfRule>
   </conditionalFormatting>
-  <dataValidations count="1">
+  <dataValidations count="3">
     <dataValidation sqref="E6:G16" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" promptTitle="選んでください" prompt="○＝できている／△＝仮づけ／×＝手つかず" type="list">
       <formula1>"○,△,×"</formula1>
+    </dataValidation>
+    <dataValidation sqref="A6:A16" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" promptTitle="案件を選ぶ" prompt="どの案件のLPかを選びます" type="list">
+      <formula1>'選択肢'!$B$2:$B$5</formula1>
+    </dataValidation>
+    <dataValidation sqref="B6:B16" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" promptTitle="状態を選ぶ" prompt="現行／別案／旧版／単発" type="list">
+      <formula1>'選択肢'!$C$2:$C$5</formula1>
     </dataValidation>
   </dataValidations>
   <hyperlinks>
@@ -1798,118 +1793,240 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A22"/>
+  <dimension ref="A1:F22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="30" customWidth="1" min="2" max="2"/>
+    <col width="30" customWidth="1" min="3" max="3"/>
+    <col width="30" customWidth="1" min="4" max="4"/>
+    <col width="30" customWidth="1" min="5" max="5"/>
+    <col width="30" customWidth="1" min="6" max="6"/>
+  </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="29" t="inlineStr">
+      <c r="A1" s="27" t="inlineStr">
         <is>
           <t>進捗</t>
         </is>
       </c>
+      <c r="B1" s="27" t="inlineStr">
+        <is>
+          <t>案件</t>
+        </is>
+      </c>
+      <c r="C1" s="27" t="inlineStr">
+        <is>
+          <t>LPの状態</t>
+        </is>
+      </c>
+      <c r="D1" s="27" t="inlineStr">
+        <is>
+          <t>区分</t>
+        </is>
+      </c>
+      <c r="E1" s="27" t="inlineStr">
+        <is>
+          <t>優先</t>
+        </is>
+      </c>
+      <c r="F1" s="27" t="inlineStr">
+        <is>
+          <t>状態</t>
+        </is>
+      </c>
     </row>
     <row r="2">
-      <c r="A2" s="30" t="n">
+      <c r="A2" s="28" t="n">
         <v>0</v>
       </c>
+      <c r="B2" s="29" t="inlineStr">
+        <is>
+          <t>REALIZE CLUB（法人向け）</t>
+        </is>
+      </c>
+      <c r="C2" s="29" t="inlineStr">
+        <is>
+          <t>現行</t>
+        </is>
+      </c>
+      <c r="D2" s="29" t="inlineStr">
+        <is>
+          <t>LP</t>
+        </is>
+      </c>
+      <c r="E2" s="29" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="F2" s="29" t="inlineStr">
+        <is>
+          <t>未着手</t>
+        </is>
+      </c>
     </row>
     <row r="3">
-      <c r="A3" s="30" t="n">
+      <c r="A3" s="28" t="n">
         <v>0.05</v>
       </c>
+      <c r="B3" s="29" t="inlineStr">
+        <is>
+          <t>LIFE MAKE PARTNERS（加盟店募集）</t>
+        </is>
+      </c>
+      <c r="C3" s="29" t="inlineStr">
+        <is>
+          <t>別案</t>
+        </is>
+      </c>
+      <c r="D3" s="29" t="inlineStr">
+        <is>
+          <t>教材・ツール</t>
+        </is>
+      </c>
+      <c r="E3" s="29" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="F3" s="29" t="inlineStr">
+        <is>
+          <t>進行中</t>
+        </is>
+      </c>
     </row>
     <row r="4">
-      <c r="A4" s="30" t="n">
+      <c r="A4" s="28" t="n">
         <v>0.1</v>
       </c>
+      <c r="B4" s="29" t="inlineStr">
+        <is>
+          <t>まちの相談窓口</t>
+        </is>
+      </c>
+      <c r="C4" s="29" t="inlineStr">
+        <is>
+          <t>旧版</t>
+        </is>
+      </c>
+      <c r="D4" s="29" t="inlineStr">
+        <is>
+          <t>動画</t>
+        </is>
+      </c>
+      <c r="E4" s="29" t="inlineStr">
+        <is>
+          <t>P3</t>
+        </is>
+      </c>
+      <c r="F4" s="29" t="inlineStr">
+        <is>
+          <t>確認待ち</t>
+        </is>
+      </c>
     </row>
     <row r="5">
-      <c r="A5" s="30" t="n">
+      <c r="A5" s="28" t="n">
         <v>0.15</v>
       </c>
+      <c r="B5" s="29" t="inlineStr">
+        <is>
+          <t>不動産FC加盟</t>
+        </is>
+      </c>
+      <c r="C5" s="29" t="inlineStr">
+        <is>
+          <t>単発</t>
+        </is>
+      </c>
+      <c r="D5" s="29" t="inlineStr">
+        <is>
+          <t>広告</t>
+        </is>
+      </c>
     </row>
     <row r="6">
-      <c r="A6" s="30" t="n">
+      <c r="A6" s="28" t="n">
         <v>0.2</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="30" t="n">
+      <c r="A7" s="28" t="n">
         <v>0.25</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="30" t="n">
+      <c r="A8" s="28" t="n">
         <v>0.3</v>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="30" t="n">
+      <c r="A9" s="28" t="n">
         <v>0.35</v>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="30" t="n">
+      <c r="A10" s="28" t="n">
         <v>0.4</v>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="30" t="n">
+      <c r="A11" s="28" t="n">
         <v>0.45</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="30" t="n">
+      <c r="A12" s="28" t="n">
         <v>0.5</v>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="30" t="n">
+      <c r="A13" s="28" t="n">
         <v>0.55</v>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="30" t="n">
+      <c r="A14" s="28" t="n">
         <v>0.6000000000000001</v>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="30" t="n">
+      <c r="A15" s="28" t="n">
         <v>0.65</v>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="30" t="n">
+      <c r="A16" s="28" t="n">
         <v>0.7000000000000001</v>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="30" t="n">
+      <c r="A17" s="28" t="n">
         <v>0.75</v>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="30" t="n">
+      <c r="A18" s="28" t="n">
         <v>0.8</v>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="30" t="n">
+      <c r="A19" s="28" t="n">
         <v>0.8500000000000001</v>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="30" t="n">
+      <c r="A20" s="28" t="n">
         <v>0.9</v>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="30" t="n">
+      <c r="A21" s="28" t="n">
         <v>0.9500000000000001</v>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="30" t="n">
+      <c r="A22" s="28" t="n">
         <v>1</v>
       </c>
     </row>
@@ -2007,7 +2124,7 @@
       </c>
     </row>
     <row r="6" ht="32" customHeight="1">
-      <c r="A6" s="13" t="inlineStr">
+      <c r="A6" s="30" t="inlineStr">
         <is>
           <t>教材・ツール</t>
         </is>
@@ -2017,17 +2134,17 @@
           <t>P2</t>
         </is>
       </c>
-      <c r="C6" s="5" t="inlineStr">
+      <c r="C6" s="7" t="inlineStr">
         <is>
           <t>eラーニング（ツール本体）</t>
         </is>
       </c>
-      <c r="D6" s="5" t="inlineStr">
+      <c r="D6" s="7" t="inlineStr">
         <is>
           <t>LMP事業 · Web・ツール・システム</t>
         </is>
       </c>
-      <c r="E6" s="13" t="inlineStr">
+      <c r="E6" s="14" t="inlineStr">
         <is>
           <t>社長・白石・片山</t>
         </is>
@@ -2035,20 +2152,20 @@
       <c r="F6" s="31" t="n">
         <v>0.5</v>
       </c>
-      <c r="G6" s="32" t="inlineStr">
+      <c r="G6" s="15" t="inlineStr">
         <is>
           <t>進行中</t>
         </is>
       </c>
-      <c r="H6" s="33" t="n"/>
-      <c r="I6" s="5" t="inlineStr">
+      <c r="H6" s="32" t="n"/>
+      <c r="I6" s="7" t="inlineStr">
         <is>
           <t>加盟店が学ぶ画面そのもの</t>
         </is>
       </c>
     </row>
     <row r="7" ht="32" customHeight="1">
-      <c r="A7" s="13" t="inlineStr">
+      <c r="A7" s="30" t="inlineStr">
         <is>
           <t>教材・ツール</t>
         </is>
@@ -2058,17 +2175,17 @@
           <t>P2</t>
         </is>
       </c>
-      <c r="C7" s="5" t="inlineStr">
+      <c r="C7" s="7" t="inlineStr">
         <is>
           <t>eラーニング動画</t>
         </is>
       </c>
-      <c r="D7" s="5" t="inlineStr">
+      <c r="D7" s="7" t="inlineStr">
         <is>
           <t>LMP事業 · Web・ツール・システム</t>
         </is>
       </c>
-      <c r="E7" s="34" t="inlineStr">
+      <c r="E7" s="33" t="inlineStr">
         <is>
           <t>未定</t>
         </is>
@@ -2076,20 +2193,20 @@
       <c r="F7" s="31" t="n">
         <v>0.2</v>
       </c>
-      <c r="G7" s="32" t="inlineStr">
+      <c r="G7" s="15" t="inlineStr">
         <is>
           <t>進行中</t>
         </is>
       </c>
-      <c r="H7" s="33" t="n"/>
-      <c r="I7" s="5" t="inlineStr">
+      <c r="H7" s="32" t="n"/>
+      <c r="I7" s="7" t="inlineStr">
         <is>
           <t>教材の中で流す動画。担当が決まっていない</t>
         </is>
       </c>
     </row>
     <row r="8" ht="32" customHeight="1">
-      <c r="A8" s="13" t="inlineStr">
+      <c r="A8" s="30" t="inlineStr">
         <is>
           <t>教材・ツール</t>
         </is>
@@ -2099,17 +2216,17 @@
           <t>P2</t>
         </is>
       </c>
-      <c r="C8" s="5" t="inlineStr">
+      <c r="C8" s="7" t="inlineStr">
         <is>
           <t>教育診断</t>
         </is>
       </c>
-      <c r="D8" s="5" t="inlineStr">
+      <c r="D8" s="7" t="inlineStr">
         <is>
           <t>RC事業 · Web・ツール・システム</t>
         </is>
       </c>
-      <c r="E8" s="13" t="inlineStr">
+      <c r="E8" s="14" t="inlineStr">
         <is>
           <t>白石</t>
         </is>
@@ -2117,20 +2234,20 @@
       <c r="F8" s="31" t="n">
         <v>0.8</v>
       </c>
-      <c r="G8" s="32" t="inlineStr">
+      <c r="G8" s="15" t="inlineStr">
         <is>
           <t>進行中</t>
         </is>
       </c>
-      <c r="H8" s="33" t="n"/>
-      <c r="I8" s="5" t="inlineStr">
+      <c r="H8" s="32" t="n"/>
+      <c r="I8" s="7" t="inlineStr">
         <is>
           <t>学ぶ前に現在地をはかる</t>
         </is>
       </c>
     </row>
     <row r="9" ht="32" customHeight="1">
-      <c r="A9" s="13" t="inlineStr">
+      <c r="A9" s="30" t="inlineStr">
         <is>
           <t>教材・ツール</t>
         </is>
@@ -2140,17 +2257,17 @@
           <t>P2</t>
         </is>
       </c>
-      <c r="C9" s="5" t="inlineStr">
+      <c r="C9" s="7" t="inlineStr">
         <is>
           <t>教科書の前段階の資料</t>
         </is>
       </c>
-      <c r="D9" s="5" t="inlineStr">
+      <c r="D9" s="7" t="inlineStr">
         <is>
           <t>RC事業 · 動画・コンテンツ</t>
         </is>
       </c>
-      <c r="E9" s="13" t="inlineStr">
+      <c r="E9" s="14" t="inlineStr">
         <is>
           <t>白石</t>
         </is>
@@ -2158,20 +2275,20 @@
       <c r="F9" s="31" t="n">
         <v>0.6</v>
       </c>
-      <c r="G9" s="32" t="inlineStr">
+      <c r="G9" s="15" t="inlineStr">
         <is>
           <t>進行中</t>
         </is>
       </c>
-      <c r="H9" s="33" t="n"/>
-      <c r="I9" s="5" t="inlineStr">
+      <c r="H9" s="32" t="n"/>
+      <c r="I9" s="7" t="inlineStr">
         <is>
           <t>教材のもとになる原稿</t>
         </is>
       </c>
     </row>
     <row r="10" ht="32" customHeight="1">
-      <c r="A10" s="13" t="inlineStr">
+      <c r="A10" s="30" t="inlineStr">
         <is>
           <t>教材・ツール</t>
         </is>
@@ -2181,17 +2298,17 @@
           <t>P2</t>
         </is>
       </c>
-      <c r="C10" s="5" t="inlineStr">
+      <c r="C10" s="7" t="inlineStr">
         <is>
           <t>各ツールマニュアル作成</t>
         </is>
       </c>
-      <c r="D10" s="5" t="inlineStr">
+      <c r="D10" s="7" t="inlineStr">
         <is>
           <t>LMP事業 · 営業・資料</t>
         </is>
       </c>
-      <c r="E10" s="34" t="inlineStr">
+      <c r="E10" s="33" t="inlineStr">
         <is>
           <t>未定</t>
         </is>
@@ -2199,20 +2316,20 @@
       <c r="F10" s="31" t="n">
         <v>0</v>
       </c>
-      <c r="G10" s="35" t="inlineStr">
+      <c r="G10" s="22" t="inlineStr">
         <is>
           <t>未着手</t>
         </is>
       </c>
-      <c r="H10" s="33" t="n"/>
-      <c r="I10" s="5" t="inlineStr">
+      <c r="H10" s="32" t="n"/>
+      <c r="I10" s="7" t="inlineStr">
         <is>
           <t>担当が決まっていない</t>
         </is>
       </c>
     </row>
     <row r="11" ht="32" customHeight="1">
-      <c r="A11" s="13" t="inlineStr">
+      <c r="A11" s="30" t="inlineStr">
         <is>
           <t>教材・ツール</t>
         </is>
@@ -2222,17 +2339,17 @@
           <t>P2</t>
         </is>
       </c>
-      <c r="C11" s="5" t="inlineStr">
+      <c r="C11" s="7" t="inlineStr">
         <is>
           <t>研修会準備</t>
         </is>
       </c>
-      <c r="D11" s="5" t="inlineStr">
+      <c r="D11" s="7" t="inlineStr">
         <is>
           <t>LMP事業 · 加盟開発</t>
         </is>
       </c>
-      <c r="E11" s="13" t="inlineStr">
+      <c r="E11" s="14" t="inlineStr">
         <is>
           <t>白石・池之上・大熊</t>
         </is>
@@ -2240,16 +2357,16 @@
       <c r="F11" s="31" t="n">
         <v>0</v>
       </c>
-      <c r="G11" s="35" t="inlineStr">
+      <c r="G11" s="22" t="inlineStr">
         <is>
           <t>未着手</t>
         </is>
       </c>
-      <c r="H11" s="33" t="n"/>
-      <c r="I11" s="5" t="inlineStr"/>
+      <c r="H11" s="32" t="n"/>
+      <c r="I11" s="7" t="inlineStr"/>
     </row>
     <row r="12" ht="32" customHeight="1">
-      <c r="A12" s="13" t="inlineStr">
+      <c r="A12" s="30" t="inlineStr">
         <is>
           <t>教材・ツール</t>
         </is>
@@ -2259,17 +2376,17 @@
           <t>P2</t>
         </is>
       </c>
-      <c r="C12" s="5" t="inlineStr">
+      <c r="C12" s="7" t="inlineStr">
         <is>
           <t>eラーニング接続・設計</t>
         </is>
       </c>
-      <c r="D12" s="5" t="inlineStr">
+      <c r="D12" s="7" t="inlineStr">
         <is>
           <t>RCP事業 · Web・ツール・システム</t>
         </is>
       </c>
-      <c r="E12" s="13" t="inlineStr">
+      <c r="E12" s="14" t="inlineStr">
         <is>
           <t>白石</t>
         </is>
@@ -2277,16 +2394,16 @@
       <c r="F12" s="31" t="n">
         <v>0</v>
       </c>
-      <c r="G12" s="35" t="inlineStr">
+      <c r="G12" s="22" t="inlineStr">
         <is>
           <t>未着手</t>
         </is>
       </c>
-      <c r="H12" s="33" t="n"/>
-      <c r="I12" s="5" t="inlineStr"/>
+      <c r="H12" s="32" t="n"/>
+      <c r="I12" s="7" t="inlineStr"/>
     </row>
     <row r="13" ht="32" customHeight="1">
-      <c r="A13" s="13" t="inlineStr">
+      <c r="A13" s="30" t="inlineStr">
         <is>
           <t>教材・ツール</t>
         </is>
@@ -2296,17 +2413,17 @@
           <t>P2</t>
         </is>
       </c>
-      <c r="C13" s="5" t="inlineStr">
+      <c r="C13" s="7" t="inlineStr">
         <is>
           <t>AIロープレ（アオ先生）</t>
         </is>
       </c>
-      <c r="D13" s="5" t="inlineStr">
+      <c r="D13" s="7" t="inlineStr">
         <is>
           <t>AIアオ先生 · 営業コーチ</t>
         </is>
       </c>
-      <c r="E13" s="13" t="inlineStr">
+      <c r="E13" s="14" t="inlineStr">
         <is>
           <t>池之上</t>
         </is>
@@ -2314,20 +2431,20 @@
       <c r="F13" s="31" t="n">
         <v>0.9</v>
       </c>
-      <c r="G13" s="36" t="inlineStr">
+      <c r="G13" s="6" t="inlineStr">
         <is>
           <t>確認待ち</t>
         </is>
       </c>
-      <c r="H13" s="33" t="n"/>
-      <c r="I13" s="5" t="inlineStr">
+      <c r="H13" s="32" t="n"/>
+      <c r="I13" s="7" t="inlineStr">
         <is>
           <t>制作MASTERのみに記載</t>
         </is>
       </c>
     </row>
     <row r="14" ht="32" customHeight="1">
-      <c r="A14" s="13" t="inlineStr">
+      <c r="A14" s="30" t="inlineStr">
         <is>
           <t>動画</t>
         </is>
@@ -2337,17 +2454,17 @@
           <t>P2</t>
         </is>
       </c>
-      <c r="C14" s="5" t="inlineStr">
+      <c r="C14" s="7" t="inlineStr">
         <is>
           <t>結婚後の暮らしと人生設計動画</t>
         </is>
       </c>
-      <c r="D14" s="5" t="inlineStr">
+      <c r="D14" s="7" t="inlineStr">
         <is>
           <t>RC事業 · 動画・コンテンツ</t>
         </is>
       </c>
-      <c r="E14" s="13" t="inlineStr">
+      <c r="E14" s="14" t="inlineStr">
         <is>
           <t>白石</t>
         </is>
@@ -2355,20 +2472,20 @@
       <c r="F14" s="31" t="n">
         <v>0.7</v>
       </c>
-      <c r="G14" s="32" t="inlineStr">
+      <c r="G14" s="15" t="inlineStr">
         <is>
           <t>進行中</t>
         </is>
       </c>
-      <c r="H14" s="33" t="n"/>
-      <c r="I14" s="5" t="inlineStr">
+      <c r="H14" s="32" t="n"/>
+      <c r="I14" s="7" t="inlineStr">
         <is>
           <t>動画で唯一動いている1本</t>
         </is>
       </c>
     </row>
     <row r="15" ht="32" customHeight="1">
-      <c r="A15" s="13" t="inlineStr">
+      <c r="A15" s="30" t="inlineStr">
         <is>
           <t>動画</t>
         </is>
@@ -2378,17 +2495,17 @@
           <t>P2</t>
         </is>
       </c>
-      <c r="C15" s="5" t="inlineStr">
+      <c r="C15" s="7" t="inlineStr">
         <is>
           <t>サービス説明動画</t>
         </is>
       </c>
-      <c r="D15" s="5" t="inlineStr">
+      <c r="D15" s="7" t="inlineStr">
         <is>
           <t>RC事業 · 動画・コンテンツ</t>
         </is>
       </c>
-      <c r="E15" s="13" t="inlineStr">
+      <c r="E15" s="14" t="inlineStr">
         <is>
           <t>白石</t>
         </is>
@@ -2396,16 +2513,16 @@
       <c r="F15" s="31" t="n">
         <v>0</v>
       </c>
-      <c r="G15" s="35" t="inlineStr">
+      <c r="G15" s="22" t="inlineStr">
         <is>
           <t>未着手</t>
         </is>
       </c>
-      <c r="H15" s="33" t="n"/>
-      <c r="I15" s="5" t="inlineStr"/>
+      <c r="H15" s="32" t="n"/>
+      <c r="I15" s="7" t="inlineStr"/>
     </row>
     <row r="16" ht="32" customHeight="1">
-      <c r="A16" s="13" t="inlineStr">
+      <c r="A16" s="30" t="inlineStr">
         <is>
           <t>動画</t>
         </is>
@@ -2415,17 +2532,17 @@
           <t>P2</t>
         </is>
       </c>
-      <c r="C16" s="5" t="inlineStr">
+      <c r="C16" s="7" t="inlineStr">
         <is>
           <t>toC動画</t>
         </is>
       </c>
-      <c r="D16" s="5" t="inlineStr">
+      <c r="D16" s="7" t="inlineStr">
         <is>
           <t>RC事業 · 動画・コンテンツ</t>
         </is>
       </c>
-      <c r="E16" s="13" t="inlineStr">
+      <c r="E16" s="14" t="inlineStr">
         <is>
           <t>白石</t>
         </is>
@@ -2433,16 +2550,16 @@
       <c r="F16" s="31" t="n">
         <v>0</v>
       </c>
-      <c r="G16" s="35" t="inlineStr">
+      <c r="G16" s="22" t="inlineStr">
         <is>
           <t>未着手</t>
         </is>
       </c>
-      <c r="H16" s="33" t="n"/>
-      <c r="I16" s="5" t="inlineStr"/>
+      <c r="H16" s="32" t="n"/>
+      <c r="I16" s="7" t="inlineStr"/>
     </row>
     <row r="17" ht="32" customHeight="1">
-      <c r="A17" s="13" t="inlineStr">
+      <c r="A17" s="30" t="inlineStr">
         <is>
           <t>動画</t>
         </is>
@@ -2452,17 +2569,17 @@
           <t>P2</t>
         </is>
       </c>
-      <c r="C17" s="5" t="inlineStr">
+      <c r="C17" s="7" t="inlineStr">
         <is>
           <t>サービスデモ動画</t>
         </is>
       </c>
-      <c r="D17" s="5" t="inlineStr">
+      <c r="D17" s="7" t="inlineStr">
         <is>
           <t>RCP事業 · 動画・コンテンツ</t>
         </is>
       </c>
-      <c r="E17" s="13" t="inlineStr">
+      <c r="E17" s="14" t="inlineStr">
         <is>
           <t>白石</t>
         </is>
@@ -2470,16 +2587,16 @@
       <c r="F17" s="31" t="n">
         <v>0</v>
       </c>
-      <c r="G17" s="35" t="inlineStr">
+      <c r="G17" s="22" t="inlineStr">
         <is>
           <t>未着手</t>
         </is>
       </c>
-      <c r="H17" s="33" t="n"/>
-      <c r="I17" s="5" t="inlineStr"/>
+      <c r="H17" s="32" t="n"/>
+      <c r="I17" s="7" t="inlineStr"/>
     </row>
     <row r="18" ht="32" customHeight="1">
-      <c r="A18" s="13" t="inlineStr">
+      <c r="A18" s="30" t="inlineStr">
         <is>
           <t>動画</t>
         </is>
@@ -2489,17 +2606,17 @@
           <t>P2</t>
         </is>
       </c>
-      <c r="C18" s="5" t="inlineStr">
+      <c r="C18" s="7" t="inlineStr">
         <is>
           <t>水谷先生の本の動画</t>
         </is>
       </c>
-      <c r="D18" s="5" t="inlineStr">
+      <c r="D18" s="7" t="inlineStr">
         <is>
           <t>RCP事業 · 動画・コンテンツ</t>
         </is>
       </c>
-      <c r="E18" s="13" t="inlineStr">
+      <c r="E18" s="14" t="inlineStr">
         <is>
           <t>白石</t>
         </is>
@@ -2507,16 +2624,16 @@
       <c r="F18" s="31" t="n">
         <v>0</v>
       </c>
-      <c r="G18" s="35" t="inlineStr">
+      <c r="G18" s="22" t="inlineStr">
         <is>
           <t>未着手</t>
         </is>
       </c>
-      <c r="H18" s="33" t="n"/>
-      <c r="I18" s="5" t="inlineStr"/>
+      <c r="H18" s="32" t="n"/>
+      <c r="I18" s="7" t="inlineStr"/>
     </row>
     <row r="19" ht="32" customHeight="1">
-      <c r="A19" s="13" t="inlineStr">
+      <c r="A19" s="30" t="inlineStr">
         <is>
           <t>動画</t>
         </is>
@@ -2526,17 +2643,17 @@
           <t>P3</t>
         </is>
       </c>
-      <c r="C19" s="5" t="inlineStr">
+      <c r="C19" s="7" t="inlineStr">
         <is>
           <t>OEM各先生の宣伝動画（5本）</t>
         </is>
       </c>
-      <c r="D19" s="5" t="inlineStr">
+      <c r="D19" s="7" t="inlineStr">
         <is>
           <t>RCP PPモデル · OEM</t>
         </is>
       </c>
-      <c r="E19" s="13" t="inlineStr">
+      <c r="E19" s="14" t="inlineStr">
         <is>
           <t>白石</t>
         </is>
@@ -2544,20 +2661,20 @@
       <c r="F19" s="31" t="n">
         <v>0</v>
       </c>
-      <c r="G19" s="35" t="inlineStr">
+      <c r="G19" s="22" t="inlineStr">
         <is>
           <t>未着手</t>
         </is>
       </c>
-      <c r="H19" s="33" t="n"/>
-      <c r="I19" s="5" t="inlineStr">
+      <c r="H19" s="32" t="n"/>
+      <c r="I19" s="7" t="inlineStr">
         <is>
           <t>AKさん・大橋会長・木原さん・水谷先生・藤田先生</t>
         </is>
       </c>
     </row>
     <row r="20" ht="32" customHeight="1">
-      <c r="A20" s="13" t="inlineStr">
+      <c r="A20" s="30" t="inlineStr">
         <is>
           <t>動画</t>
         </is>
@@ -2567,17 +2684,17 @@
           <t>P3</t>
         </is>
       </c>
-      <c r="C20" s="5" t="inlineStr">
+      <c r="C20" s="7" t="inlineStr">
         <is>
           <t>宣伝動画・PV ロング／ショート（7本）</t>
         </is>
       </c>
-      <c r="D20" s="5" t="inlineStr">
+      <c r="D20" s="7" t="inlineStr">
         <is>
           <t>RC／RCP／HI／PP · REALIZE QUEST</t>
         </is>
       </c>
-      <c r="E20" s="13" t="inlineStr">
+      <c r="E20" s="14" t="inlineStr">
         <is>
           <t>白石・片山</t>
         </is>
@@ -2585,16 +2702,16 @@
       <c r="F20" s="31" t="n">
         <v>0</v>
       </c>
-      <c r="G20" s="35" t="inlineStr">
+      <c r="G20" s="22" t="inlineStr">
         <is>
           <t>未着手</t>
         </is>
       </c>
-      <c r="H20" s="33" t="n"/>
-      <c r="I20" s="5" t="inlineStr"/>
+      <c r="H20" s="32" t="n"/>
+      <c r="I20" s="7" t="inlineStr"/>
     </row>
     <row r="21" ht="32" customHeight="1">
-      <c r="A21" s="13" t="inlineStr">
+      <c r="A21" s="30" t="inlineStr">
         <is>
           <t>動画</t>
         </is>
@@ -2604,17 +2721,17 @@
           <t>P3</t>
         </is>
       </c>
-      <c r="C21" s="5" t="inlineStr">
+      <c r="C21" s="7" t="inlineStr">
         <is>
           <t>採用まわりの動画（2本）</t>
         </is>
       </c>
-      <c r="D21" s="5" t="inlineStr">
+      <c r="D21" s="7" t="inlineStr">
         <is>
           <t>採用 · 学生募集</t>
         </is>
       </c>
-      <c r="E21" s="13" t="inlineStr">
+      <c r="E21" s="14" t="inlineStr">
         <is>
           <t>白石・片山</t>
         </is>
@@ -2622,46 +2739,46 @@
       <c r="F21" s="31" t="n">
         <v>0</v>
       </c>
-      <c r="G21" s="35" t="inlineStr">
+      <c r="G21" s="22" t="inlineStr">
         <is>
           <t>未着手</t>
         </is>
       </c>
-      <c r="H21" s="33" t="n"/>
-      <c r="I21" s="5" t="inlineStr">
+      <c r="H21" s="32" t="n"/>
+      <c r="I21" s="7" t="inlineStr">
         <is>
           <t>PR動画・SNS採用募集動画</t>
         </is>
       </c>
     </row>
     <row r="22">
-      <c r="E22" s="25" t="inlineStr">
+      <c r="E22" s="23" t="inlineStr">
         <is>
           <t>平均</t>
         </is>
       </c>
-      <c r="F22" s="37">
+      <c r="F22" s="34">
         <f>AVERAGE(F6:F21)</f>
         <v/>
       </c>
-      <c r="G22" s="28">
+      <c r="G22" s="26">
         <f>COUNTIF(G6:G21,"未着手")&amp;" 件未着手"</f>
         <v/>
       </c>
-      <c r="H22" s="28">
+      <c r="H22" s="26">
         <f>COUNTA(H6:H21)&amp;" 件 登録済み"</f>
         <v/>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="38" t="inlineStr">
+      <c r="A24" s="35" t="inlineStr">
         <is>
           <t>できている設計書・ガイド</t>
         </is>
       </c>
     </row>
     <row r="25">
-      <c r="C25" s="39" t="inlineStr">
+      <c r="C25" s="36" t="inlineStr">
         <is>
           <t>LIFE CHECK42 Eラーニング画面設計書</t>
         </is>
@@ -2676,14 +2793,14 @@
           <t>2026-08-31</t>
         </is>
       </c>
-      <c r="I25" s="40" t="inlineStr">
+      <c r="I25" s="37" t="inlineStr">
         <is>
           <t>開く</t>
         </is>
       </c>
     </row>
     <row r="26">
-      <c r="C26" s="39" t="inlineStr">
+      <c r="C26" s="36" t="inlineStr">
         <is>
           <t>RCP ノーマル版 eラーニング｜UI提案 v1</t>
         </is>
@@ -2698,14 +2815,14 @@
           <t>2026-08-05</t>
         </is>
       </c>
-      <c r="I26" s="40" t="inlineStr">
+      <c r="I26" s="37" t="inlineStr">
         <is>
           <t>開く</t>
         </is>
       </c>
     </row>
     <row r="27">
-      <c r="C27" s="39" t="inlineStr">
+      <c r="C27" s="36" t="inlineStr">
         <is>
           <t>AIロープレ 操作ガイド</t>
         </is>
@@ -2720,14 +2837,14 @@
           <t>2026-08-31</t>
         </is>
       </c>
-      <c r="I27" s="40" t="inlineStr">
+      <c r="I27" s="37" t="inlineStr">
         <is>
           <t>開く</t>
         </is>
       </c>
     </row>
     <row r="28">
-      <c r="C28" s="39" t="inlineStr">
+      <c r="C28" s="36" t="inlineStr">
         <is>
           <t>生成AI動画講座 比較検討</t>
         </is>
@@ -2742,7 +2859,7 @@
           <t>2026-08-21</t>
         </is>
       </c>
-      <c r="I28" s="40" t="inlineStr">
+      <c r="I28" s="37" t="inlineStr">
         <is>
           <t>開く</t>
         </is>
@@ -2759,12 +2876,18 @@
       </dataBar>
     </cfRule>
   </conditionalFormatting>
-  <dataValidations count="2">
+  <dataValidations count="4">
     <dataValidation sqref="F6:F21" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" promptTitle="進捗を選ぶ" prompt="5%きざみで選べます。直接入力もできます。" type="list">
       <formula1>'選択肢'!$A$2:$A$22</formula1>
     </dataValidation>
+    <dataValidation sqref="A6:A21" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" promptTitle="区分を選ぶ" prompt="LP／教材・ツール／動画／広告" type="list">
+      <formula1>'選択肢'!$D$2:$D$5</formula1>
+    </dataValidation>
+    <dataValidation sqref="B6:B21" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" promptTitle="優先を選ぶ" prompt="工程表の優先度" type="list">
+      <formula1>'選択肢'!$E$2:$E$4</formula1>
+    </dataValidation>
     <dataValidation sqref="G6:G21" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" promptTitle="状態を選ぶ" prompt="未着手／進行中／確認待ち" type="list">
-      <formula1>"未着手,進行中,確認待ち"</formula1>
+      <formula1>'選択肢'!$F$2:$F$4</formula1>
     </dataValidation>
   </dataValidations>
   <hyperlinks>
@@ -2867,7 +2990,7 @@
       </c>
     </row>
     <row r="6" ht="32" customHeight="1">
-      <c r="A6" s="13" t="inlineStr">
+      <c r="A6" s="30" t="inlineStr">
         <is>
           <t>広告</t>
         </is>
@@ -2877,17 +3000,17 @@
           <t>P2</t>
         </is>
       </c>
-      <c r="C6" s="5" t="inlineStr">
+      <c r="C6" s="7" t="inlineStr">
         <is>
           <t>広告制作</t>
         </is>
       </c>
-      <c r="D6" s="5" t="inlineStr">
+      <c r="D6" s="7" t="inlineStr">
         <is>
           <t>RC法人開拓 · 地域企業への入口</t>
         </is>
       </c>
-      <c r="E6" s="13" t="inlineStr">
+      <c r="E6" s="14" t="inlineStr">
         <is>
           <t>大熊・片山</t>
         </is>
@@ -2895,20 +3018,20 @@
       <c r="F6" s="31" t="n">
         <v>0</v>
       </c>
-      <c r="G6" s="35" t="inlineStr">
+      <c r="G6" s="22" t="inlineStr">
         <is>
           <t>未着手</t>
         </is>
       </c>
-      <c r="H6" s="33" t="n"/>
-      <c r="I6" s="5" t="inlineStr">
+      <c r="H6" s="32" t="n"/>
+      <c r="I6" s="7" t="inlineStr">
         <is>
           <t>バナー・原稿などのクリエイティブ</t>
         </is>
       </c>
     </row>
     <row r="7" ht="32" customHeight="1">
-      <c r="A7" s="13" t="inlineStr">
+      <c r="A7" s="30" t="inlineStr">
         <is>
           <t>広告</t>
         </is>
@@ -2918,17 +3041,17 @@
           <t>P2</t>
         </is>
       </c>
-      <c r="C7" s="5" t="inlineStr">
+      <c r="C7" s="7" t="inlineStr">
         <is>
           <t>広告運用</t>
         </is>
       </c>
-      <c r="D7" s="5" t="inlineStr">
+      <c r="D7" s="7" t="inlineStr">
         <is>
           <t>RC法人開拓／LMP加盟開発</t>
         </is>
       </c>
-      <c r="E7" s="13" t="inlineStr">
+      <c r="E7" s="14" t="inlineStr">
         <is>
           <t>池之上・片山</t>
         </is>
@@ -2936,20 +3059,20 @@
       <c r="F7" s="31" t="n">
         <v>0</v>
       </c>
-      <c r="G7" s="35" t="inlineStr">
+      <c r="G7" s="22" t="inlineStr">
         <is>
           <t>未着手</t>
         </is>
       </c>
-      <c r="H7" s="33" t="n"/>
-      <c r="I7" s="5" t="inlineStr">
+      <c r="H7" s="32" t="n"/>
+      <c r="I7" s="7" t="inlineStr">
         <is>
           <t>出稿・予算・改善</t>
         </is>
       </c>
     </row>
     <row r="8" ht="32" customHeight="1">
-      <c r="A8" s="13" t="inlineStr">
+      <c r="A8" s="30" t="inlineStr">
         <is>
           <t>広告</t>
         </is>
@@ -2959,17 +3082,17 @@
           <t>P2</t>
         </is>
       </c>
-      <c r="C8" s="5" t="inlineStr">
+      <c r="C8" s="7" t="inlineStr">
         <is>
           <t>広告クリエイティブチェック</t>
         </is>
       </c>
-      <c r="D8" s="5" t="inlineStr">
+      <c r="D8" s="7" t="inlineStr">
         <is>
           <t>LMP事業 · 全体品質確認</t>
         </is>
       </c>
-      <c r="E8" s="13" t="inlineStr">
+      <c r="E8" s="14" t="inlineStr">
         <is>
           <t>白石</t>
         </is>
@@ -2977,20 +3100,20 @@
       <c r="F8" s="31" t="n">
         <v>0</v>
       </c>
-      <c r="G8" s="35" t="inlineStr">
+      <c r="G8" s="22" t="inlineStr">
         <is>
           <t>未着手</t>
         </is>
       </c>
-      <c r="H8" s="33" t="n"/>
-      <c r="I8" s="5" t="inlineStr">
+      <c r="H8" s="32" t="n"/>
+      <c r="I8" s="7" t="inlineStr">
         <is>
           <t>出す前の品質確認</t>
         </is>
       </c>
     </row>
     <row r="9" ht="32" customHeight="1">
-      <c r="A9" s="13" t="inlineStr">
+      <c r="A9" s="30" t="inlineStr">
         <is>
           <t>広告</t>
         </is>
@@ -3000,17 +3123,17 @@
           <t>P3</t>
         </is>
       </c>
-      <c r="C9" s="5" t="inlineStr">
+      <c r="C9" s="7" t="inlineStr">
         <is>
           <t>広告表示のチェック（景表法）</t>
         </is>
       </c>
-      <c r="D9" s="5" t="inlineStr">
+      <c r="D9" s="7" t="inlineStr">
         <is>
           <t>社内業務 · 法務・業法</t>
         </is>
       </c>
-      <c r="E9" s="13" t="inlineStr">
+      <c r="E9" s="14" t="inlineStr">
         <is>
           <t>社長・寺井・池之上・弁護士</t>
         </is>
@@ -3018,20 +3141,20 @@
       <c r="F9" s="31" t="n">
         <v>0</v>
       </c>
-      <c r="G9" s="35" t="inlineStr">
+      <c r="G9" s="22" t="inlineStr">
         <is>
           <t>未着手</t>
         </is>
       </c>
-      <c r="H9" s="33" t="n"/>
-      <c r="I9" s="5" t="inlineStr">
+      <c r="H9" s="32" t="n"/>
+      <c r="I9" s="7" t="inlineStr">
         <is>
           <t>言い切り表現・実績表示の法務確認</t>
         </is>
       </c>
     </row>
     <row r="10" ht="32" customHeight="1">
-      <c r="A10" s="13" t="inlineStr">
+      <c r="A10" s="30" t="inlineStr">
         <is>
           <t>広告</t>
         </is>
@@ -3041,17 +3164,17 @@
           <t>P3</t>
         </is>
       </c>
-      <c r="C10" s="5" t="inlineStr">
+      <c r="C10" s="7" t="inlineStr">
         <is>
           <t>広報・告知（LP・SNS）4件</t>
         </is>
       </c>
-      <c r="D10" s="5" t="inlineStr">
+      <c r="D10" s="7" t="inlineStr">
         <is>
           <t>RC／RCP／HI／PP · REALIZE QUEST</t>
         </is>
       </c>
-      <c r="E10" s="13" t="inlineStr">
+      <c r="E10" s="14" t="inlineStr">
         <is>
           <t>白石</t>
         </is>
@@ -3059,29 +3182,29 @@
       <c r="F10" s="31" t="n">
         <v>0</v>
       </c>
-      <c r="G10" s="35" t="inlineStr">
+      <c r="G10" s="22" t="inlineStr">
         <is>
           <t>未着手</t>
         </is>
       </c>
-      <c r="H10" s="33" t="n"/>
-      <c r="I10" s="5" t="inlineStr"/>
+      <c r="H10" s="32" t="n"/>
+      <c r="I10" s="7" t="inlineStr"/>
     </row>
     <row r="11">
-      <c r="E11" s="25" t="inlineStr">
+      <c r="E11" s="23" t="inlineStr">
         <is>
           <t>平均</t>
         </is>
       </c>
-      <c r="F11" s="37">
+      <c r="F11" s="34">
         <f>AVERAGE(F6:F10)</f>
         <v/>
       </c>
-      <c r="G11" s="28">
+      <c r="G11" s="26">
         <f>COUNTIF(G6:G10,"未着手")&amp;" 件未着手"</f>
         <v/>
       </c>
-      <c r="H11" s="28">
+      <c r="H11" s="26">
         <f>COUNTA(H6:H10)&amp;" 件 登録済み"</f>
         <v/>
       </c>
@@ -3097,12 +3220,18 @@
       </dataBar>
     </cfRule>
   </conditionalFormatting>
-  <dataValidations count="2">
+  <dataValidations count="4">
     <dataValidation sqref="F6:F10" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" promptTitle="進捗を選ぶ" prompt="5%きざみで選べます。直接入力もできます。" type="list">
       <formula1>'選択肢'!$A$2:$A$22</formula1>
     </dataValidation>
+    <dataValidation sqref="A6:A10" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" promptTitle="区分を選ぶ" prompt="LP／教材・ツール／動画／広告" type="list">
+      <formula1>'選択肢'!$D$2:$D$5</formula1>
+    </dataValidation>
+    <dataValidation sqref="B6:B10" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" promptTitle="優先を選ぶ" prompt="工程表の優先度" type="list">
+      <formula1>'選択肢'!$E$2:$E$4</formula1>
+    </dataValidation>
     <dataValidation sqref="G6:G10" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" promptTitle="状態を選ぶ" prompt="未着手／進行中／確認待ち" type="list">
-      <formula1>"未着手,進行中,確認待ち"</formula1>
+      <formula1>'選択肢'!$F$2:$F$4</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -3116,7 +3245,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B34"/>
+  <dimension ref="A1:B36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -3124,318 +3253,342 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="41" t="inlineStr">
+      <c r="A1" s="38" t="inlineStr">
         <is>
           <t>凡例と出典</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="42" t="inlineStr">
+      <c r="A3" s="39" t="inlineStr">
         <is>
           <t>LPシートの4段</t>
         </is>
       </c>
     </row>
     <row r="4" ht="36" customHeight="1">
-      <c r="A4" s="43" t="inlineStr">
+      <c r="A4" s="40" t="inlineStr">
         <is>
           <t>①原稿・デザイン</t>
         </is>
       </c>
-      <c r="B4" s="44" t="inlineStr">
+      <c r="B4" s="41" t="inlineStr">
         <is>
           <t>本編の文章とデザインが最後まで通っている</t>
         </is>
       </c>
     </row>
     <row r="5" ht="36" customHeight="1">
-      <c r="A5" s="43" t="inlineStr">
+      <c r="A5" s="40" t="inlineStr">
         <is>
           <t>②付随ページ</t>
         </is>
       </c>
-      <c r="B5" s="44" t="inlineStr">
+      <c r="B5" s="41" t="inlineStr">
         <is>
           <t>資料請求・会社概要など、必要な付随ページが揃っている</t>
         </is>
       </c>
     </row>
     <row r="6" ht="36" customHeight="1">
-      <c r="A6" s="43" t="inlineStr">
+      <c r="A6" s="40" t="inlineStr">
         <is>
           <t>③問い合わせ導線</t>
         </is>
       </c>
-      <c r="B6" s="44" t="inlineStr">
+      <c r="B6" s="41" t="inlineStr">
         <is>
           <t>ボタンの行き先が実在し、問い合わせが届く先につながっている</t>
         </is>
       </c>
     </row>
     <row r="7" ht="36" customHeight="1">
-      <c r="A7" s="43" t="inlineStr">
+      <c r="A7" s="40" t="inlineStr">
         <is>
           <t>④本番公開</t>
         </is>
       </c>
-      <c r="B7" s="44" t="inlineStr">
+      <c r="B7" s="41" t="inlineStr">
         <is>
           <t>独自ドメインで公開され、J列に本番URLが入っている（自動判定）</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="42" t="inlineStr">
+      <c r="A9" s="39" t="inlineStr">
         <is>
           <t>記号</t>
         </is>
       </c>
     </row>
     <row r="10" ht="36" customHeight="1">
-      <c r="A10" s="43" t="inlineStr">
+      <c r="A10" s="40" t="inlineStr">
         <is>
           <t>○</t>
         </is>
       </c>
-      <c r="B10" s="44" t="inlineStr">
+      <c r="B10" s="41" t="inlineStr">
         <is>
           <t>できている</t>
         </is>
       </c>
     </row>
     <row r="11" ht="36" customHeight="1">
-      <c r="A11" s="43" t="inlineStr">
+      <c r="A11" s="40" t="inlineStr">
         <is>
           <t>△</t>
         </is>
       </c>
-      <c r="B11" s="44" t="inlineStr">
+      <c r="B11" s="41" t="inlineStr">
         <is>
           <t>仮づけ。メーラーを開くだけ、または行き先が「#」のまま</t>
         </is>
       </c>
     </row>
     <row r="12" ht="36" customHeight="1">
-      <c r="A12" s="43" t="inlineStr">
+      <c r="A12" s="40" t="inlineStr">
         <is>
           <t>×</t>
         </is>
       </c>
-      <c r="B12" s="44" t="inlineStr">
+      <c r="B12" s="41" t="inlineStr">
         <is>
           <t>手つかず／ページが存在しない</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="42" t="inlineStr">
+      <c r="A14" s="39" t="inlineStr">
         <is>
           <t>状態（eラーニング・動画／広告シート）</t>
         </is>
       </c>
     </row>
     <row r="15" ht="36" customHeight="1">
-      <c r="A15" s="43" t="inlineStr">
+      <c r="A15" s="40" t="inlineStr">
         <is>
           <t>確認待ち</t>
         </is>
       </c>
-      <c r="B15" s="44" t="inlineStr">
+      <c r="B15" s="41" t="inlineStr">
         <is>
           <t>作業は終わり、誰かの確認を待っている</t>
         </is>
       </c>
     </row>
     <row r="16" ht="36" customHeight="1">
-      <c r="A16" s="43" t="inlineStr">
+      <c r="A16" s="40" t="inlineStr">
         <is>
           <t>進行中</t>
         </is>
       </c>
-      <c r="B16" s="44" t="inlineStr">
+      <c r="B16" s="41" t="inlineStr">
         <is>
           <t>いま手が動いている</t>
         </is>
       </c>
     </row>
     <row r="17" ht="36" customHeight="1">
-      <c r="A17" s="43" t="inlineStr">
+      <c r="A17" s="40" t="inlineStr">
         <is>
           <t>未着手</t>
         </is>
       </c>
-      <c r="B17" s="44" t="inlineStr">
+      <c r="B17" s="41" t="inlineStr">
         <is>
           <t>まだ始まっていない</t>
         </is>
       </c>
     </row>
     <row r="18" ht="36" customHeight="1">
-      <c r="A18" s="43" t="inlineStr">
+      <c r="A18" s="40" t="inlineStr">
         <is>
           <t>P2／P3</t>
         </is>
       </c>
-      <c r="B18" s="44" t="inlineStr">
+      <c r="B18" s="41" t="inlineStr">
         <is>
           <t>工程表の優先度。P3は「中核が回り出してから戻ってくる」もの</t>
         </is>
       </c>
     </row>
     <row r="19" ht="36" customHeight="1">
-      <c r="A19" s="43" t="inlineStr">
+      <c r="A19" s="40" t="inlineStr">
         <is>
           <t>赤い担当名</t>
         </is>
       </c>
-      <c r="B19" s="44" t="inlineStr">
+      <c r="B19" s="41" t="inlineStr">
         <is>
           <t>担当が「未定」の仕事。誰かを決めないと進みません</t>
         </is>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="42" t="inlineStr">
+      <c r="A21" s="39" t="inlineStr">
         <is>
           <t>使い方</t>
         </is>
       </c>
     </row>
     <row r="22" ht="36" customHeight="1">
-      <c r="A22" s="43" t="inlineStr">
+      <c r="A22" s="40" t="inlineStr">
+        <is>
+          <t>案件・区分のセル（水色）</t>
+        </is>
+      </c>
+      <c r="B22" s="41" t="inlineStr">
+        <is>
+          <t>LPシートのA列（案件）とB列（状態）、他シートのA列（区分）とB列（優先）は、クリックすると▼が出て選べます。行の並べ替えをしなくても、絞り込みで見たい案件だけ出せます。</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="36" customHeight="1">
+      <c r="A23" s="40" t="inlineStr">
         <is>
           <t>進捗のセル（水色）</t>
         </is>
       </c>
-      <c r="B22" s="44" t="inlineStr">
+      <c r="B23" s="41" t="inlineStr">
         <is>
           <t>クリックすると右に▼が出ます。0%〜100%を5%きざみで選べます（直接入力も可）。選ぶとセルの中のバーがその長さに変わります。</t>
         </is>
       </c>
     </row>
-    <row r="23" ht="36" customHeight="1">
-      <c r="A23" s="43" t="inlineStr">
+    <row r="24" ht="36" customHeight="1">
+      <c r="A24" s="40" t="inlineStr">
         <is>
           <t>状態のセル（水色）</t>
         </is>
       </c>
-      <c r="B23" s="44" t="inlineStr">
+      <c r="B24" s="41" t="inlineStr">
         <is>
           <t>クリックして 未着手／進行中／確認待ち を選びます。</t>
         </is>
       </c>
     </row>
-    <row r="24" ht="36" customHeight="1">
-      <c r="A24" s="43" t="inlineStr">
+    <row r="25" ht="36" customHeight="1">
+      <c r="A25" s="40" t="inlineStr">
         <is>
           <t>LPの○△×（水色）</t>
         </is>
       </c>
-      <c r="B24" s="44" t="inlineStr">
+      <c r="B25" s="41" t="inlineStr">
         <is>
           <t>E〜G列。クリックして選び直せます。H列の④本番公開はJ列のURL有無から自動で決まります。</t>
         </is>
       </c>
     </row>
-    <row r="25" ht="36" customHeight="1">
-      <c r="A25" s="43" t="inlineStr">
+    <row r="26" ht="36" customHeight="1">
+      <c r="A26" s="40" t="inlineStr">
         <is>
           <t>列見出しの▼</t>
         </is>
       </c>
-      <c r="B25" s="44" t="inlineStr">
+      <c r="B26" s="41" t="inlineStr">
         <is>
           <t>各シートの見出し行にオートフィルタが付いています。▼から値を選ぶと、その行だけ表示されます。複数の列を組み合わせられます。</t>
         </is>
       </c>
     </row>
-    <row r="26" ht="36" customHeight="1">
-      <c r="A26" s="43" t="inlineStr">
+    <row r="27" ht="36" customHeight="1">
+      <c r="A27" s="40" t="inlineStr">
         <is>
           <t>黄色の記入欄</t>
         </is>
       </c>
-      <c r="B26" s="44" t="inlineStr">
+      <c r="B27" s="41" t="inlineStr">
         <is>
           <t>公開したURL・動画URL・広告の入稿先を貼ります。</t>
         </is>
       </c>
     </row>
-    <row r="27" ht="36" customHeight="1">
-      <c r="A27" s="43" t="inlineStr">
+    <row r="28" ht="36" customHeight="1">
+      <c r="A28" s="40" t="inlineStr">
         <is>
           <t>自動で動く数字</t>
         </is>
       </c>
-      <c r="B27" s="44" t="inlineStr">
+      <c r="B28" s="41" t="inlineStr">
         <is>
           <t>LPシートは④と到達度、各シートの最下段の平均・件数が数式です。手で書き換えないでください。</t>
         </is>
       </c>
     </row>
-    <row r="29">
-      <c r="A29" s="42" t="inlineStr">
+    <row r="29" ht="36" customHeight="1">
+      <c r="A29" s="40" t="inlineStr">
+        <is>
+          <t>選択肢を増やしたいとき</t>
+        </is>
+      </c>
+      <c r="B29" s="41" t="inlineStr">
+        <is>
+          <t>非表示シート「選択肢」に一覧が入っています。表示して値を足し、入力規則の参照範囲を広げれば選べるようになります。</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="39" t="inlineStr">
         <is>
           <t>出典</t>
         </is>
       </c>
     </row>
-    <row r="30" ht="36" customHeight="1">
-      <c r="A30" s="43" t="inlineStr">
+    <row r="32" ht="36" customHeight="1">
+      <c r="A32" s="40" t="inlineStr">
         <is>
           <t>LPシート</t>
         </is>
       </c>
-      <c r="B30" s="44" t="inlineStr">
+      <c r="B32" s="41" t="inlineStr">
         <is>
           <t>公開済みアーティファクト43件のうちLPに該当する22ページ（本編11＋付随11）を、1ページずつHTMLを読んで確認。ボタンの行き先・フォームの送信方法・付随ページの有無は実物ベースです。</t>
         </is>
       </c>
     </row>
-    <row r="31" ht="36" customHeight="1">
-      <c r="A31" s="43" t="inlineStr">
+    <row r="33" ht="36" customHeight="1">
+      <c r="A33" s="40" t="inlineStr">
         <is>
           <t>進捗％と担当</t>
         </is>
       </c>
-      <c r="B31" s="44" t="inlineStr">
+      <c r="B33" s="41" t="inlineStr">
         <is>
           <t>社内の「REALIZE OS 制作MASTER」(2026-09-03) と「仕事の棚卸し」(2026-09-02) の数値をそのまま引いています。</t>
         </is>
       </c>
     </row>
-    <row r="32" ht="36" customHeight="1">
-      <c r="A32" s="43" t="inlineStr">
+    <row r="34" ht="36" customHeight="1">
+      <c r="A34" s="40" t="inlineStr">
         <is>
           <t>担当の食い違い</t>
         </is>
       </c>
-      <c r="B32" s="44" t="inlineStr">
+      <c r="B34" s="41" t="inlineStr">
         <is>
           <t>広告運用の担当は2資料で記載が違います（制作MASTER＝大熊・片山／棚卸し＝池之上・片山）。広告制作は大熊・片山、広告運用は池之上・片山としています。</t>
         </is>
       </c>
     </row>
-    <row r="33" ht="36" customHeight="1">
-      <c r="A33" s="43" t="inlineStr">
+    <row r="35" ht="36" customHeight="1">
+      <c r="A35" s="40" t="inlineStr">
         <is>
           <t>未確認</t>
         </is>
       </c>
-      <c r="B33" s="44" t="inlineStr">
+      <c r="B35" s="41" t="inlineStr">
         <is>
           <t>LP付随ページ4本（RC星空案の会社概要、RCアイス案の資料請求、LMP星空案の資料請求と会社概要）は、親LPからのリンクで存在を確認しただけで中身は開いていません。</t>
         </is>
       </c>
     </row>
-    <row r="34" ht="36" customHeight="1">
-      <c r="A34" s="43" t="inlineStr">
+    <row r="36" ht="36" customHeight="1">
+      <c r="A36" s="40" t="inlineStr">
         <is>
           <t>調査日</t>
         </is>
       </c>
-      <c r="B34" s="44" t="inlineStr">
+      <c r="B36" s="41" t="inlineStr">
         <is>
           <t>2026-09-03</t>
         </is>

--- a/制作進捗ボード.xlsx
+++ b/制作進捗ボード.xlsx
@@ -14,9 +14,9 @@
     <sheet name="凡例と出典" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'LP'!$A$5:$P$16</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'eラーニング・動画'!$A$5:$I$21</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'広告'!$A$5:$I$10</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'LP'!$A$5:$M$16</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'eラーニング・動画'!$A$5:$G$21</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'広告'!$A$5:$G$10</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -24,10 +24,8 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="3">
-    <numFmt numFmtId="164" formatCode="0&quot;／4段&quot;"/>
-    <numFmt numFmtId="165" formatCode="0&quot;／11&quot;"/>
-    <numFmt numFmtId="166" formatCode="0.0&quot;／4段&quot;"/>
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="0&quot;／11&quot;"/>
   </numFmts>
   <fonts count="18">
     <font>
@@ -82,19 +80,7 @@
     </font>
     <font>
       <name val="Meiryo"/>
-      <b val="1"/>
-      <color rgb="001C6647"/>
-      <sz val="9"/>
-    </font>
-    <font>
-      <name val="Meiryo"/>
       <color rgb="000000FF"/>
-      <sz val="9"/>
-    </font>
-    <font>
-      <name val="Meiryo"/>
-      <b val="1"/>
-      <color rgb="006E747D"/>
       <sz val="9"/>
     </font>
     <font>
@@ -113,6 +99,18 @@
       <name val="Meiryo"/>
       <b val="1"/>
       <color rgb="00993124"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Meiryo"/>
+      <b val="1"/>
+      <color rgb="006E747D"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Meiryo"/>
+      <b val="1"/>
+      <color rgb="001C6647"/>
       <sz val="9"/>
     </font>
     <font>
@@ -148,17 +146,17 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="00EAF1F6"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="00FFF3C4"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00FAF8F3"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00EAF1F6"/>
       </patternFill>
     </fill>
   </fills>
@@ -193,7 +191,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="42">
+  <cellXfs count="39">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -201,25 +199,19 @@
     <xf numFmtId="0" fontId="6" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="8" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="9" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -231,56 +223,53 @@
     <xf numFmtId="0" fontId="8" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="8" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="8" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="8" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="165" fontId="13" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="164" fontId="11" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="166" fontId="13" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="9" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="8" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="9" fontId="8" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="9" fontId="8" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="9" fontId="13" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="13" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="11" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -288,7 +277,7 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="17" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -402,10 +391,10 @@
     <author>制作進捗ボード</author>
   </authors>
   <commentList>
-    <comment ref="J6" authorId="0" shapeId="0">
+    <comment ref="G6" authorId="0" shapeId="0">
       <text>
         <t>公開した本番LPのURLをここに貼ってください。
-入力すると④本番公開が○になり、到達度が上がります。</t>
+入力すると本番公開が○になります。</t>
       </text>
     </comment>
   </commentList>
@@ -418,10 +407,9 @@
     <author>制作進捗ボード</author>
   </authors>
   <commentList>
-    <comment ref="H6" authorId="0" shapeId="0">
+    <comment ref="C6" authorId="0" shapeId="0">
       <text>
-        <t>できあがったものの URL を貼ってください。
-動画なら公開URL、広告なら入稿先やアカウントのURL。</t>
+        <t>クリックすると▼が出ます。一覧から選ぶか、直接書いてください。</t>
       </text>
     </comment>
   </commentList>
@@ -434,10 +422,9 @@
     <author>制作進捗ボード</author>
   </authors>
   <commentList>
-    <comment ref="H6" authorId="0" shapeId="0">
+    <comment ref="C6" authorId="0" shapeId="0">
       <text>
-        <t>できあがったものの URL を貼ってください。
-動画なら公開URL、広告なら入稿先やアカウントのURL。</t>
+        <t>クリックすると▼が出ます。一覧から選ぶか、直接書いてください。</t>
       </text>
     </comment>
   </commentList>
@@ -733,25 +720,22 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P17"/>
+  <dimension ref="A1:M17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="22" customWidth="1" min="1" max="1"/>
-    <col width="7" customWidth="1" min="2" max="2"/>
-    <col width="30" customWidth="1" min="3" max="3"/>
-    <col width="32" customWidth="1" min="4" max="4"/>
-    <col width="13" customWidth="1" min="5" max="5"/>
-    <col width="12" customWidth="1" min="6" max="6"/>
-    <col width="14" customWidth="1" min="7" max="7"/>
-    <col width="11" customWidth="1" min="8" max="8"/>
-    <col width="10" customWidth="1" min="9" max="9"/>
-    <col width="34" customWidth="1" min="10" max="10"/>
-    <col width="52" customWidth="1" min="11" max="11"/>
-    <col width="26" customWidth="1" min="12" max="12"/>
-    <col width="26" customWidth="1" min="13" max="13"/>
-    <col width="26" customWidth="1" min="14" max="14"/>
-    <col width="10" customWidth="1" min="15" max="15"/>
-    <col width="11" customWidth="1" min="16" max="16"/>
+    <col width="24" customWidth="1" min="1" max="1"/>
+    <col width="30" customWidth="1" min="2" max="2"/>
+    <col width="32" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="15" customWidth="1" min="5" max="5"/>
+    <col width="11" customWidth="1" min="6" max="6"/>
+    <col width="34" customWidth="1" min="7" max="7"/>
+    <col width="52" customWidth="1" min="8" max="8"/>
+    <col width="26" customWidth="1" min="9" max="9"/>
+    <col width="26" customWidth="1" min="10" max="10"/>
+    <col width="26" customWidth="1" min="11" max="11"/>
+    <col width="10" customWidth="1" min="12" max="12"/>
+    <col width="11" customWidth="1" min="13" max="13"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -771,7 +755,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>黄色のJ列だけ記入してください。URLを入れると④本番公開と到達度が自動で変わります。</t>
+          <t>水色のセルはクリックすると▼が出て選べます。黄色のG列にURLを入れると、本番公開が自動で○になります。</t>
         </is>
       </c>
     </row>
@@ -783,75 +767,60 @@
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>状態</t>
+          <t>LP名</t>
         </is>
       </c>
       <c r="C5" s="4" t="inlineStr">
         <is>
-          <t>LP名</t>
+          <t>デザインの方向</t>
         </is>
       </c>
       <c r="D5" s="4" t="inlineStr">
         <is>
-          <t>デザインの方向</t>
+          <t>原稿・デザイン</t>
         </is>
       </c>
       <c r="E5" s="4" t="inlineStr">
         <is>
-          <t>①原稿・デザイン</t>
+          <t>問い合わせ導線</t>
         </is>
       </c>
       <c r="F5" s="4" t="inlineStr">
         <is>
-          <t>②付随ページ</t>
+          <t>本番公開</t>
         </is>
       </c>
       <c r="G5" s="4" t="inlineStr">
         <is>
-          <t>③問い合わせ導線</t>
+          <t>本番URL（記入欄）</t>
         </is>
       </c>
       <c r="H5" s="4" t="inlineStr">
         <is>
-          <t>④本番公開</t>
+          <t>残っていること</t>
         </is>
       </c>
       <c r="I5" s="4" t="inlineStr">
         <is>
-          <t>到達度</t>
+          <t>資料請求ページ</t>
         </is>
       </c>
       <c r="J5" s="4" t="inlineStr">
         <is>
-          <t>本番URL（記入欄）</t>
+          <t>会社概要ページ</t>
         </is>
       </c>
       <c r="K5" s="4" t="inlineStr">
         <is>
-          <t>残っていること</t>
+          <t>LPプレビュー</t>
         </is>
       </c>
       <c r="L5" s="4" t="inlineStr">
         <is>
-          <t>資料請求ページ</t>
+          <t>ID</t>
         </is>
       </c>
       <c r="M5" s="4" t="inlineStr">
-        <is>
-          <t>会社概要ページ</t>
-        </is>
-      </c>
-      <c r="N5" s="4" t="inlineStr">
-        <is>
-          <t>LPプレビュー</t>
-        </is>
-      </c>
-      <c r="O5" s="4" t="inlineStr">
-        <is>
-          <t>ID</t>
-        </is>
-      </c>
-      <c r="P5" s="4" t="inlineStr">
         <is>
           <t>更新日</t>
         </is>
@@ -865,69 +834,55 @@
       </c>
       <c r="B6" s="6" t="inlineStr">
         <is>
-          <t>現行</t>
-        </is>
-      </c>
-      <c r="C6" s="7" t="inlineStr">
-        <is>
           <t>会社が、社員の人生を守る時代へ。</t>
         </is>
       </c>
+      <c r="C6" s="6" t="inlineStr">
+        <is>
+          <t>深緑 × 和モダン／昭和と令和の対比</t>
+        </is>
+      </c>
       <c r="D6" s="7" t="inlineStr">
         <is>
-          <t>深緑 × 和モダン／昭和と令和の対比</t>
-        </is>
-      </c>
-      <c r="E6" s="8" t="inlineStr">
-        <is>
           <t>○</t>
         </is>
       </c>
-      <c r="F6" s="8" t="inlineStr">
-        <is>
-          <t>○</t>
-        </is>
-      </c>
-      <c r="G6" s="8" t="inlineStr">
+      <c r="E6" s="7" t="inlineStr">
         <is>
           <t>△</t>
         </is>
       </c>
-      <c r="H6" s="9">
-        <f>IF(J6="","×","○")</f>
+      <c r="F6" s="8">
+        <f>IF(G6="","×","○")</f>
         <v/>
       </c>
-      <c r="I6" s="10">
-        <f>COUNTIF(E6:H6,"○")+COUNTIF(E6:H6,"△")</f>
-        <v/>
-      </c>
-      <c r="J6" s="11" t="n"/>
-      <c r="K6" s="7" t="inlineStr">
+      <c r="G6" s="9" t="n"/>
+      <c r="H6" s="6" t="inlineStr">
         <is>
           <t>送信ボタンがメーラーを開くだけ。受付フォームの実装が必要／会社概要ページが未作成／本番ドメインへの公開</t>
         </is>
       </c>
+      <c r="I6" s="10" t="inlineStr">
+        <is>
+          <t>資料請求を開く</t>
+        </is>
+      </c>
+      <c r="J6" s="11" t="inlineStr">
+        <is>
+          <t>未作成</t>
+        </is>
+      </c>
+      <c r="K6" s="10" t="inlineStr">
+        <is>
+          <t>LPを開く</t>
+        </is>
+      </c>
       <c r="L6" s="12" t="inlineStr">
         <is>
-          <t>資料請求を開く</t>
-        </is>
-      </c>
-      <c r="M6" s="13" t="inlineStr">
-        <is>
-          <t>未作成</t>
-        </is>
-      </c>
-      <c r="N6" s="12" t="inlineStr">
-        <is>
-          <t>LPを開く</t>
-        </is>
-      </c>
-      <c r="O6" s="14" t="inlineStr">
-        <is>
           <t>08b479a1</t>
         </is>
       </c>
-      <c r="P6" s="9" t="inlineStr">
+      <c r="M6" s="8" t="inlineStr">
         <is>
           <t>2026-09-03</t>
         </is>
@@ -939,71 +894,57 @@
           <t>REALIZE CLUB（法人向け）</t>
         </is>
       </c>
-      <c r="B7" s="15" t="inlineStr">
-        <is>
-          <t>別案</t>
-        </is>
-      </c>
-      <c r="C7" s="16" t="inlineStr">
+      <c r="B7" s="13" t="inlineStr">
         <is>
           <t>会社が社員の人生を支える時代へ</t>
         </is>
       </c>
-      <c r="D7" s="16" t="inlineStr">
+      <c r="C7" s="13" t="inlineStr">
         <is>
           <t>星空タウン／クリーム × 濃紺のイラスト</t>
         </is>
       </c>
-      <c r="E7" s="8" t="inlineStr">
+      <c r="D7" s="7" t="inlineStr">
         <is>
           <t>○</t>
         </is>
       </c>
-      <c r="F7" s="8" t="inlineStr">
-        <is>
-          <t>○</t>
-        </is>
-      </c>
-      <c r="G7" s="8" t="inlineStr">
+      <c r="E7" s="7" t="inlineStr">
         <is>
           <t>△</t>
         </is>
       </c>
-      <c r="H7" s="17">
-        <f>IF(J7="","×","○")</f>
+      <c r="F7" s="14">
+        <f>IF(G7="","×","○")</f>
         <v/>
       </c>
-      <c r="I7" s="18">
-        <f>COUNTIF(E7:H7,"○")+COUNTIF(E7:H7,"△")</f>
-        <v/>
-      </c>
-      <c r="J7" s="11" t="n"/>
-      <c r="K7" s="16" t="inlineStr">
-        <is>
-          <t>RC案で唯一3ページ揃い。採用するかの判断／送信はメーラー起動のみ</t>
-        </is>
-      </c>
-      <c r="L7" s="19" t="inlineStr">
+      <c r="G7" s="9" t="n"/>
+      <c r="H7" s="13" t="inlineStr">
+        <is>
+          <t>3ページ揃っている唯一のRC案。採用するかの判断／送信はメーラー起動のみ</t>
+        </is>
+      </c>
+      <c r="I7" s="15" t="inlineStr">
         <is>
           <t>資料請求を開く</t>
         </is>
       </c>
-      <c r="M7" s="19" t="inlineStr">
+      <c r="J7" s="15" t="inlineStr">
         <is>
           <t>会社概要を開く</t>
         </is>
       </c>
-      <c r="N7" s="19" t="inlineStr">
+      <c r="K7" s="15" t="inlineStr">
         <is>
           <t>LPを開く</t>
         </is>
       </c>
-      <c r="O7" s="20" t="inlineStr">
+      <c r="L7" s="16" t="inlineStr">
         <is>
           <t>7355f424</t>
         </is>
       </c>
-      <c r="P7" s="17" t="inlineStr">
+      <c r="M7" s="14" t="inlineStr">
         <is>
           <t>2026-08-31</t>
         </is>
@@ -1015,71 +956,57 @@
           <t>REALIZE CLUB（法人向け）</t>
         </is>
       </c>
-      <c r="B8" s="15" t="inlineStr">
-        <is>
-          <t>別案</t>
-        </is>
-      </c>
-      <c r="C8" s="7" t="inlineStr">
+      <c r="B8" s="6" t="inlineStr">
         <is>
           <t>困る前に、灯す。</t>
         </is>
       </c>
+      <c r="C8" s="6" t="inlineStr">
+        <is>
+          <t>漆黒 × 炎のグラデーション</t>
+        </is>
+      </c>
       <c r="D8" s="7" t="inlineStr">
         <is>
-          <t>漆黒 × 炎のグラデーション</t>
-        </is>
-      </c>
-      <c r="E8" s="8" t="inlineStr">
-        <is>
           <t>○</t>
         </is>
       </c>
-      <c r="F8" s="8" t="inlineStr">
-        <is>
-          <t>△</t>
-        </is>
-      </c>
-      <c r="G8" s="8" t="inlineStr">
+      <c r="E8" s="7" t="inlineStr">
         <is>
           <t>×</t>
         </is>
       </c>
-      <c r="H8" s="9">
-        <f>IF(J8="","×","○")</f>
+      <c r="F8" s="8">
+        <f>IF(G8="","×","○")</f>
         <v/>
       </c>
-      <c r="I8" s="10">
-        <f>COUNTIF(E8:H8,"○")+COUNTIF(E8:H8,"△")</f>
-        <v/>
-      </c>
-      <c r="J8" s="11" t="n"/>
-      <c r="K8" s="7" t="inlineStr">
+      <c r="G8" s="9" t="n"/>
+      <c r="H8" s="6" t="inlineStr">
         <is>
           <t>kaisha.html ほかへの相対リンクが残り、単体では飛べない／会社概要ページの作成</t>
         </is>
       </c>
-      <c r="L8" s="13" t="inlineStr">
+      <c r="I8" s="11" t="inlineStr">
         <is>
           <t>（同ファイル内）</t>
         </is>
       </c>
-      <c r="M8" s="13" t="inlineStr">
+      <c r="J8" s="11" t="inlineStr">
         <is>
           <t>未作成</t>
         </is>
       </c>
-      <c r="N8" s="12" t="inlineStr">
+      <c r="K8" s="10" t="inlineStr">
         <is>
           <t>LPを開く</t>
         </is>
       </c>
-      <c r="O8" s="14" t="inlineStr">
+      <c r="L8" s="12" t="inlineStr">
         <is>
           <t>ded9a489</t>
         </is>
       </c>
-      <c r="P8" s="9" t="inlineStr">
+      <c r="M8" s="8" t="inlineStr">
         <is>
           <t>2026-08-31</t>
         </is>
@@ -1091,71 +1018,57 @@
           <t>REALIZE CLUB（法人向け）</t>
         </is>
       </c>
-      <c r="B9" s="15" t="inlineStr">
-        <is>
-          <t>別案</t>
-        </is>
-      </c>
-      <c r="C9" s="16" t="inlineStr">
+      <c r="B9" s="13" t="inlineStr">
         <is>
           <t>その安心、今がお得。</t>
         </is>
       </c>
-      <c r="D9" s="16" t="inlineStr">
+      <c r="C9" s="13" t="inlineStr">
         <is>
           <t>スーパーの特売ポップ／白地に赤と黄</t>
         </is>
       </c>
-      <c r="E9" s="8" t="inlineStr">
+      <c r="D9" s="7" t="inlineStr">
         <is>
           <t>○</t>
         </is>
       </c>
-      <c r="F9" s="8" t="inlineStr">
-        <is>
-          <t>△</t>
-        </is>
-      </c>
-      <c r="G9" s="8" t="inlineStr">
+      <c r="E9" s="7" t="inlineStr">
         <is>
           <t>×</t>
         </is>
       </c>
-      <c r="H9" s="17">
-        <f>IF(J9="","×","○")</f>
+      <c r="F9" s="14">
+        <f>IF(G9="","×","○")</f>
         <v/>
       </c>
-      <c r="I9" s="18">
-        <f>COUNTIF(E9:H9,"○")+COUNTIF(E9:H9,"△")</f>
-        <v/>
-      </c>
-      <c r="J9" s="11" t="n"/>
-      <c r="K9" s="16" t="inlineStr">
+      <c r="G9" s="9" t="n"/>
+      <c r="H9" s="13" t="inlineStr">
         <is>
           <t>リンクがすべてページ内アンカー。外部への導線が1本もない／会社概要ページ、送信先の設定</t>
         </is>
       </c>
-      <c r="L9" s="21" t="inlineStr">
+      <c r="I9" s="17" t="inlineStr">
         <is>
           <t>（同ページ内フォーム）</t>
         </is>
       </c>
-      <c r="M9" s="21" t="inlineStr">
+      <c r="J9" s="17" t="inlineStr">
         <is>
           <t>未作成</t>
         </is>
       </c>
-      <c r="N9" s="19" t="inlineStr">
+      <c r="K9" s="15" t="inlineStr">
         <is>
           <t>LPを開く</t>
         </is>
       </c>
-      <c r="O9" s="20" t="inlineStr">
+      <c r="L9" s="16" t="inlineStr">
         <is>
           <t>4ce48691</t>
         </is>
       </c>
-      <c r="P9" s="17" t="inlineStr">
+      <c r="M9" s="14" t="inlineStr">
         <is>
           <t>2026-08-31</t>
         </is>
@@ -1167,71 +1080,57 @@
           <t>REALIZE CLUB（法人向け）</t>
         </is>
       </c>
-      <c r="B10" s="15" t="inlineStr">
-        <is>
-          <t>別案</t>
-        </is>
-      </c>
-      <c r="C10" s="7" t="inlineStr">
+      <c r="B10" s="6" t="inlineStr">
         <is>
           <t>社員が、溶けていく前に。</t>
         </is>
       </c>
+      <c r="C10" s="6" t="inlineStr">
+        <is>
+          <t>アイスのメタファー／手描き風</t>
+        </is>
+      </c>
       <c r="D10" s="7" t="inlineStr">
         <is>
-          <t>アイスのメタファー／手描き風</t>
-        </is>
-      </c>
-      <c r="E10" s="8" t="inlineStr">
-        <is>
           <t>○</t>
         </is>
       </c>
-      <c r="F10" s="8" t="inlineStr">
-        <is>
-          <t>△</t>
-        </is>
-      </c>
-      <c r="G10" s="8" t="inlineStr">
+      <c r="E10" s="7" t="inlineStr">
         <is>
           <t>×</t>
         </is>
       </c>
-      <c r="H10" s="9">
-        <f>IF(J10="","×","○")</f>
+      <c r="F10" s="8">
+        <f>IF(G10="","×","○")</f>
         <v/>
       </c>
-      <c r="I10" s="10">
-        <f>COUNTIF(E10:H10,"○")+COUNTIF(E10:H10,"△")</f>
-        <v/>
-      </c>
-      <c r="J10" s="11" t="n"/>
-      <c r="K10" s="7" t="inlineStr">
+      <c r="G10" s="9" t="n"/>
+      <c r="H10" s="6" t="inlineStr">
         <is>
           <t>会社概要ページが未作成／送信はメーラー起動のみ</t>
         </is>
       </c>
+      <c r="I10" s="10" t="inlineStr">
+        <is>
+          <t>資料請求を開く</t>
+        </is>
+      </c>
+      <c r="J10" s="11" t="inlineStr">
+        <is>
+          <t>未作成</t>
+        </is>
+      </c>
+      <c r="K10" s="10" t="inlineStr">
+        <is>
+          <t>LPを開く</t>
+        </is>
+      </c>
       <c r="L10" s="12" t="inlineStr">
         <is>
-          <t>資料請求を開く</t>
-        </is>
-      </c>
-      <c r="M10" s="13" t="inlineStr">
-        <is>
-          <t>未作成</t>
-        </is>
-      </c>
-      <c r="N10" s="12" t="inlineStr">
-        <is>
-          <t>LPを開く</t>
-        </is>
-      </c>
-      <c r="O10" s="14" t="inlineStr">
-        <is>
           <t>b0f16478</t>
         </is>
       </c>
-      <c r="P10" s="9" t="inlineStr">
+      <c r="M10" s="8" t="inlineStr">
         <is>
           <t>2026-08-28</t>
         </is>
@@ -1243,71 +1142,57 @@
           <t>LIFE MAKE PARTNERS（加盟店募集）</t>
         </is>
       </c>
-      <c r="B11" s="6" t="inlineStr">
-        <is>
-          <t>現行</t>
-        </is>
-      </c>
-      <c r="C11" s="16" t="inlineStr">
+      <c r="B11" s="13" t="inlineStr">
         <is>
           <t>家より先に、人生の話を。</t>
         </is>
       </c>
-      <c r="D11" s="16" t="inlineStr">
+      <c r="C11" s="13" t="inlineStr">
         <is>
           <t>韓国料理店の看板／木の壁 × 生成りの横断幕</t>
         </is>
       </c>
-      <c r="E11" s="8" t="inlineStr">
+      <c r="D11" s="7" t="inlineStr">
         <is>
           <t>○</t>
         </is>
       </c>
-      <c r="F11" s="8" t="inlineStr">
+      <c r="E11" s="7" t="inlineStr">
         <is>
           <t>○</t>
         </is>
       </c>
-      <c r="G11" s="8" t="inlineStr">
-        <is>
-          <t>○</t>
-        </is>
-      </c>
-      <c r="H11" s="17">
-        <f>IF(J11="","×","○")</f>
+      <c r="F11" s="14">
+        <f>IF(G11="","×","○")</f>
         <v/>
       </c>
-      <c r="I11" s="18">
-        <f>COUNTIF(E11:H11,"○")+COUNTIF(E11:H11,"△")</f>
-        <v/>
-      </c>
-      <c r="J11" s="11" t="n"/>
-      <c r="K11" s="16" t="inlineStr">
+      <c r="G11" s="9" t="n"/>
+      <c r="H11" s="13" t="inlineStr">
         <is>
           <t>本番ドメインへの公開だけが残り。問い合わせはLINE公式（lin.ee/WHYApuM）に集約済み</t>
         </is>
       </c>
-      <c r="L11" s="19" t="inlineStr">
+      <c r="I11" s="15" t="inlineStr">
         <is>
           <t>資料請求を開く</t>
         </is>
       </c>
-      <c r="M11" s="19" t="inlineStr">
+      <c r="J11" s="15" t="inlineStr">
         <is>
           <t>会社概要を開く</t>
         </is>
       </c>
-      <c r="N11" s="19" t="inlineStr">
+      <c r="K11" s="15" t="inlineStr">
         <is>
           <t>LPを開く</t>
         </is>
       </c>
-      <c r="O11" s="20" t="inlineStr">
+      <c r="L11" s="16" t="inlineStr">
         <is>
           <t>7f212d2f</t>
         </is>
       </c>
-      <c r="P11" s="17" t="inlineStr">
+      <c r="M11" s="14" t="inlineStr">
         <is>
           <t>2026-09-03</t>
         </is>
@@ -1319,71 +1204,57 @@
           <t>LIFE MAKE PARTNERS（加盟店募集）</t>
         </is>
       </c>
-      <c r="B12" s="15" t="inlineStr">
-        <is>
-          <t>別案</t>
-        </is>
-      </c>
-      <c r="C12" s="7" t="inlineStr">
+      <c r="B12" s="6" t="inlineStr">
         <is>
           <t>いつも同じ集客ばっかやってんじゃねぇ！</t>
         </is>
       </c>
+      <c r="C12" s="6" t="inlineStr">
+        <is>
+          <t>喝・挑発ポスター／赤と黄の斜めストライプ</t>
+        </is>
+      </c>
       <c r="D12" s="7" t="inlineStr">
         <is>
-          <t>喝・挑発ポスター／赤と黄の斜めストライプ</t>
-        </is>
-      </c>
-      <c r="E12" s="8" t="inlineStr">
-        <is>
           <t>○</t>
         </is>
       </c>
-      <c r="F12" s="8" t="inlineStr">
-        <is>
-          <t>△</t>
-        </is>
-      </c>
-      <c r="G12" s="8" t="inlineStr">
+      <c r="E12" s="7" t="inlineStr">
         <is>
           <t>×</t>
         </is>
       </c>
-      <c r="H12" s="9">
-        <f>IF(J12="","×","○")</f>
+      <c r="F12" s="8">
+        <f>IF(G12="","×","○")</f>
         <v/>
       </c>
-      <c r="I12" s="10">
-        <f>COUNTIF(E12:H12,"○")+COUNTIF(E12:H12,"△")</f>
-        <v/>
-      </c>
-      <c r="J12" s="11" t="n"/>
-      <c r="K12" s="7" t="inlineStr">
+      <c r="G12" s="9" t="n"/>
+      <c r="H12" s="6" t="inlineStr">
         <is>
           <t>kaisha-katsu.html ほかへの相対リンクが残り飛べない／行き先が「#」のままのボタンが2つ</t>
         </is>
       </c>
-      <c r="L12" s="13" t="inlineStr">
+      <c r="I12" s="11" t="inlineStr">
         <is>
           <t>（同ページ内フォーム）</t>
         </is>
       </c>
-      <c r="M12" s="13" t="inlineStr">
+      <c r="J12" s="11" t="inlineStr">
         <is>
           <t>未作成</t>
         </is>
       </c>
-      <c r="N12" s="12" t="inlineStr">
+      <c r="K12" s="10" t="inlineStr">
         <is>
           <t>LPを開く</t>
         </is>
       </c>
-      <c r="O12" s="14" t="inlineStr">
+      <c r="L12" s="12" t="inlineStr">
         <is>
           <t>db82fc95</t>
         </is>
       </c>
-      <c r="P12" s="9" t="inlineStr">
+      <c r="M12" s="8" t="inlineStr">
         <is>
           <t>2026-08-28</t>
         </is>
@@ -1395,71 +1266,57 @@
           <t>LIFE MAKE PARTNERS（加盟店募集）</t>
         </is>
       </c>
-      <c r="B13" s="15" t="inlineStr">
-        <is>
-          <t>別案</t>
-        </is>
-      </c>
-      <c r="C13" s="16" t="inlineStr">
+      <c r="B13" s="13" t="inlineStr">
         <is>
           <t>加盟資格は、人生への愛。ただそれだけ。</t>
         </is>
       </c>
-      <c r="D13" s="16" t="inlineStr">
+      <c r="C13" s="13" t="inlineStr">
         <is>
           <t>星空タウン／RC星空案と同じ世界観</t>
         </is>
       </c>
-      <c r="E13" s="8" t="inlineStr">
+      <c r="D13" s="7" t="inlineStr">
         <is>
           <t>○</t>
         </is>
       </c>
-      <c r="F13" s="8" t="inlineStr">
-        <is>
-          <t>○</t>
-        </is>
-      </c>
-      <c r="G13" s="8" t="inlineStr">
+      <c r="E13" s="7" t="inlineStr">
         <is>
           <t>△</t>
         </is>
       </c>
-      <c r="H13" s="17">
-        <f>IF(J13="","×","○")</f>
+      <c r="F13" s="14">
+        <f>IF(G13="","×","○")</f>
         <v/>
       </c>
-      <c r="I13" s="18">
-        <f>COUNTIF(E13:H13,"○")+COUNTIF(E13:H13,"△")</f>
-        <v/>
-      </c>
-      <c r="J13" s="11" t="n"/>
-      <c r="K13" s="16" t="inlineStr">
-        <is>
-          <t>行き先が「#」のままのボタンが2つ／現行案との統廃合の判断</t>
-        </is>
-      </c>
-      <c r="L13" s="19" t="inlineStr">
+      <c r="G13" s="9" t="n"/>
+      <c r="H13" s="13" t="inlineStr">
+        <is>
+          <t>行き先が「#」のままのボタンが2つ／統廃合の判断</t>
+        </is>
+      </c>
+      <c r="I13" s="15" t="inlineStr">
         <is>
           <t>資料請求を開く</t>
         </is>
       </c>
-      <c r="M13" s="19" t="inlineStr">
+      <c r="J13" s="15" t="inlineStr">
         <is>
           <t>会社概要を開く</t>
         </is>
       </c>
-      <c r="N13" s="19" t="inlineStr">
+      <c r="K13" s="15" t="inlineStr">
         <is>
           <t>LPを開く</t>
         </is>
       </c>
-      <c r="O13" s="20" t="inlineStr">
+      <c r="L13" s="16" t="inlineStr">
         <is>
           <t>65b43069</t>
         </is>
       </c>
-      <c r="P13" s="17" t="inlineStr">
+      <c r="M13" s="14" t="inlineStr">
         <is>
           <t>2026-08-24</t>
         </is>
@@ -1473,69 +1330,55 @@
       </c>
       <c r="B14" s="6" t="inlineStr">
         <is>
-          <t>現行</t>
-        </is>
-      </c>
-      <c r="C14" s="7" t="inlineStr">
-        <is>
           <t>不動産屋が、まちの相談窓口になる。</t>
         </is>
       </c>
+      <c r="C14" s="6" t="inlineStr">
+        <is>
+          <t>銭湯ポスター（リソグラフ2色刷り）／LINE誘導版</t>
+        </is>
+      </c>
       <c r="D14" s="7" t="inlineStr">
         <is>
-          <t>銭湯ポスター（リソグラフ2色刷り）／LINE誘導版</t>
-        </is>
-      </c>
-      <c r="E14" s="8" t="inlineStr">
-        <is>
           <t>○</t>
         </is>
       </c>
-      <c r="F14" s="8" t="inlineStr">
-        <is>
-          <t>○</t>
-        </is>
-      </c>
-      <c r="G14" s="8" t="inlineStr">
+      <c r="E14" s="7" t="inlineStr">
         <is>
           <t>△</t>
         </is>
       </c>
-      <c r="H14" s="9">
-        <f>IF(J14="","×","○")</f>
+      <c r="F14" s="8">
+        <f>IF(G14="","×","○")</f>
         <v/>
       </c>
-      <c r="I14" s="10">
-        <f>COUNTIF(E14:H14,"○")+COUNTIF(E14:H14,"△")</f>
-        <v/>
-      </c>
-      <c r="J14" s="11" t="n"/>
-      <c r="K14" s="7" t="inlineStr">
+      <c r="G14" s="9" t="n"/>
+      <c r="H14" s="6" t="inlineStr">
         <is>
           <t>行き先が「#」のままのリンクが2つ残っている／本番ドメインへの公開</t>
         </is>
       </c>
+      <c r="I14" s="10" t="inlineStr">
+        <is>
+          <t>資料請求を開く</t>
+        </is>
+      </c>
+      <c r="J14" s="10" t="inlineStr">
+        <is>
+          <t>会社概要を開く</t>
+        </is>
+      </c>
+      <c r="K14" s="10" t="inlineStr">
+        <is>
+          <t>LPを開く</t>
+        </is>
+      </c>
       <c r="L14" s="12" t="inlineStr">
         <is>
-          <t>資料請求を開く</t>
-        </is>
-      </c>
-      <c r="M14" s="12" t="inlineStr">
-        <is>
-          <t>会社概要を開く</t>
-        </is>
-      </c>
-      <c r="N14" s="12" t="inlineStr">
-        <is>
-          <t>LPを開く</t>
-        </is>
-      </c>
-      <c r="O14" s="14" t="inlineStr">
-        <is>
           <t>1a259364</t>
         </is>
       </c>
-      <c r="P14" s="9" t="inlineStr">
+      <c r="M14" s="8" t="inlineStr">
         <is>
           <t>2026-09-03</t>
         </is>
@@ -1547,71 +1390,57 @@
           <t>まちの相談窓口</t>
         </is>
       </c>
-      <c r="B15" s="22" t="inlineStr">
-        <is>
-          <t>旧版</t>
-        </is>
-      </c>
-      <c r="C15" s="16" t="inlineStr">
+      <c r="B15" s="13" t="inlineStr">
         <is>
           <t>まちの相談窓口（フォーム版）</t>
         </is>
       </c>
-      <c r="D15" s="16" t="inlineStr">
+      <c r="C15" s="13" t="inlineStr">
         <is>
           <t>銭湯ポスター／申込フォーム内蔵</t>
         </is>
       </c>
-      <c r="E15" s="8" t="inlineStr">
+      <c r="D15" s="7" t="inlineStr">
         <is>
           <t>○</t>
         </is>
       </c>
-      <c r="F15" s="8" t="inlineStr">
-        <is>
-          <t>○</t>
-        </is>
-      </c>
-      <c r="G15" s="8" t="inlineStr">
+      <c r="E15" s="7" t="inlineStr">
         <is>
           <t>△</t>
         </is>
       </c>
-      <c r="H15" s="17">
-        <f>IF(J15="","×","○")</f>
+      <c r="F15" s="14">
+        <f>IF(G15="","×","○")</f>
         <v/>
       </c>
-      <c r="I15" s="18">
-        <f>COUNTIF(E15:H15,"○")+COUNTIF(E15:H15,"△")</f>
-        <v/>
-      </c>
-      <c r="J15" s="11" t="n"/>
-      <c r="K15" s="16" t="inlineStr">
-        <is>
-          <t>現行のLINE誘導版に置き換わっている。残すか消すかの判断</t>
-        </is>
-      </c>
-      <c r="L15" s="19" t="inlineStr">
+      <c r="G15" s="9" t="n"/>
+      <c r="H15" s="13" t="inlineStr">
+        <is>
+          <t>LINE誘導版に置き換わっている。残すか消すかの判断</t>
+        </is>
+      </c>
+      <c r="I15" s="15" t="inlineStr">
         <is>
           <t>資料請求を開く</t>
         </is>
       </c>
-      <c r="M15" s="19" t="inlineStr">
+      <c r="J15" s="15" t="inlineStr">
         <is>
           <t>会社概要を開く</t>
         </is>
       </c>
-      <c r="N15" s="19" t="inlineStr">
+      <c r="K15" s="15" t="inlineStr">
         <is>
           <t>LPを開く</t>
         </is>
       </c>
-      <c r="O15" s="20" t="inlineStr">
+      <c r="L15" s="16" t="inlineStr">
         <is>
           <t>39f0d878</t>
         </is>
       </c>
-      <c r="P15" s="17" t="inlineStr">
+      <c r="M15" s="14" t="inlineStr">
         <is>
           <t>2026-08-20</t>
         </is>
@@ -1623,110 +1452,88 @@
           <t>不動産FC加盟</t>
         </is>
       </c>
-      <c r="B16" s="22" t="inlineStr">
-        <is>
-          <t>単発</t>
-        </is>
-      </c>
-      <c r="C16" s="7" t="inlineStr">
+      <c r="B16" s="6" t="inlineStr">
         <is>
           <t>収益が積み上がる不動産FC加盟へ。</t>
         </is>
       </c>
+      <c r="C16" s="6" t="inlineStr">
+        <is>
+          <t>ボクシング／黒地 × 赤とゴールド</t>
+        </is>
+      </c>
       <c r="D16" s="7" t="inlineStr">
         <is>
-          <t>ボクシング／黒地 × 赤とゴールド</t>
-        </is>
-      </c>
-      <c r="E16" s="8" t="inlineStr">
-        <is>
           <t>○</t>
         </is>
       </c>
-      <c r="F16" s="8" t="inlineStr">
+      <c r="E16" s="7" t="inlineStr">
         <is>
           <t>×</t>
         </is>
       </c>
-      <c r="G16" s="8" t="inlineStr">
-        <is>
-          <t>×</t>
-        </is>
-      </c>
-      <c r="H16" s="9">
-        <f>IF(J16="","×","○")</f>
+      <c r="F16" s="8">
+        <f>IF(G16="","×","○")</f>
         <v/>
       </c>
-      <c r="I16" s="10">
-        <f>COUNTIF(E16:H16,"○")+COUNTIF(E16:H16,"△")</f>
+      <c r="G16" s="9" t="n"/>
+      <c r="H16" s="6" t="inlineStr">
+        <is>
+          <t>ページのタイトルタグが空。共有すると名前なしで出る／資料請求・会社概要ページ、送信先の設定</t>
+        </is>
+      </c>
+      <c r="I16" s="11" t="inlineStr">
+        <is>
+          <t>（同ページ内フォーム）</t>
+        </is>
+      </c>
+      <c r="J16" s="11" t="inlineStr">
+        <is>
+          <t>未作成</t>
+        </is>
+      </c>
+      <c r="K16" s="10" t="inlineStr">
+        <is>
+          <t>LPを開く</t>
+        </is>
+      </c>
+      <c r="L16" s="12" t="inlineStr">
+        <is>
+          <t>d5160792</t>
+        </is>
+      </c>
+      <c r="M16" s="8" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="C17" s="18" t="inlineStr">
+        <is>
+          <t>○の数</t>
+        </is>
+      </c>
+      <c r="D17" s="19">
+        <f>COUNTIF(D6:D16,"○")</f>
         <v/>
       </c>
-      <c r="J16" s="11" t="n"/>
-      <c r="K16" s="7" t="inlineStr">
-        <is>
-          <t>ページのタイトルタグが空。共有すると名前なしで出る／資料請求・会社概要ページ、送信先の設定</t>
-        </is>
-      </c>
-      <c r="L16" s="13" t="inlineStr">
-        <is>
-          <t>（同ページ内フォーム）</t>
-        </is>
-      </c>
-      <c r="M16" s="13" t="inlineStr">
-        <is>
-          <t>未作成</t>
-        </is>
-      </c>
-      <c r="N16" s="12" t="inlineStr">
-        <is>
-          <t>LPを開く</t>
-        </is>
-      </c>
-      <c r="O16" s="14" t="inlineStr">
-        <is>
-          <t>d5160792</t>
-        </is>
-      </c>
-      <c r="P16" s="9" t="inlineStr">
-        <is>
-          <t>2026-08-19</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="D17" s="23" t="inlineStr">
-        <is>
-          <t>合計 / 平均</t>
-        </is>
-      </c>
-      <c r="E17" s="24">
+      <c r="E17" s="19">
         <f>COUNTIF(E6:E16,"○")</f>
         <v/>
       </c>
-      <c r="F17" s="24">
+      <c r="F17" s="19">
         <f>COUNTIF(F6:F16,"○")</f>
         <v/>
       </c>
-      <c r="G17" s="24">
-        <f>COUNTIF(G6:G16,"○")</f>
+      <c r="G17" s="20">
+        <f>COUNTA(G6:G16)&amp;" 本 公開ずみ"</f>
         <v/>
       </c>
-      <c r="H17" s="24">
-        <f>COUNTIF(H6:H16,"○")</f>
-        <v/>
-      </c>
-      <c r="I17" s="25">
-        <f>AVERAGE(I6:I16)</f>
-        <v/>
-      </c>
-      <c r="J17" s="26">
-        <f>COUNTA(J6:J16)&amp;" 本 公開済み"</f>
-        <v/>
-      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A5:P16"/>
-  <conditionalFormatting sqref="E6:H16">
+  <autoFilter ref="A5:M16"/>
+  <conditionalFormatting sqref="D6:F16">
     <cfRule type="cellIs" priority="1" operator="equal" dxfId="0">
       <formula>"×"</formula>
     </cfRule>
@@ -1737,50 +1544,38 @@
       <formula>"○"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I6:I16">
-    <cfRule type="dataBar" priority="4">
-      <dataBar showValue="1">
-        <cfvo type="num" val="0"/>
-        <cfvo type="num" val="4"/>
-        <color rgb="001F4E6B"/>
-      </dataBar>
-    </cfRule>
-  </conditionalFormatting>
-  <dataValidations count="3">
-    <dataValidation sqref="E6:G16" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" promptTitle="選んでください" prompt="○＝できている／△＝仮づけ／×＝手つかず" type="list">
-      <formula1>"○,△,×"</formula1>
-    </dataValidation>
+  <dataValidations count="2">
     <dataValidation sqref="A6:A16" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" promptTitle="案件を選ぶ" prompt="どの案件のLPかを選びます" type="list">
       <formula1>'選択肢'!$B$2:$B$5</formula1>
     </dataValidation>
-    <dataValidation sqref="B6:B16" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" promptTitle="状態を選ぶ" prompt="現行／別案／旧版／単発" type="list">
-      <formula1>'選択肢'!$C$2:$C$5</formula1>
+    <dataValidation sqref="D6:E16" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" promptTitle="選んでください" prompt="○＝できている／△＝仮づけ／×＝手つかず" type="list">
+      <formula1>"○,△,×"</formula1>
     </dataValidation>
   </dataValidations>
   <hyperlinks>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L6" r:id="rId1"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N6" r:id="rId2"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L7" r:id="rId3"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M7" r:id="rId4"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N7" r:id="rId5"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N8" r:id="rId6"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N9" r:id="rId7"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L10" r:id="rId8"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N10" r:id="rId9"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L11" r:id="rId10"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M11" r:id="rId11"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N11" r:id="rId12"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N12" r:id="rId13"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L13" r:id="rId14"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M13" r:id="rId15"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N13" r:id="rId16"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L14" r:id="rId17"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M14" r:id="rId18"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N14" r:id="rId19"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L15" r:id="rId20"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M15" r:id="rId21"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N15" r:id="rId22"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N16" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I6" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K6" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I7" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J7" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K7" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K8" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K9" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I10" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J11" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K11" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K12" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I13" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J13" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K13" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I14" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J14" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K14" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I15" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J15" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K15" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K16" r:id="rId23"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="anysvml"/>
@@ -1793,240 +1588,253 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F22"/>
+  <dimension ref="A1:D22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="2" max="2"/>
     <col width="30" customWidth="1" min="3" max="3"/>
     <col width="30" customWidth="1" min="4" max="4"/>
-    <col width="30" customWidth="1" min="5" max="5"/>
-    <col width="30" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="27" t="inlineStr">
+      <c r="A1" s="21" t="inlineStr">
         <is>
           <t>進捗</t>
         </is>
       </c>
-      <c r="B1" s="27" t="inlineStr">
+      <c r="B1" s="21" t="inlineStr">
         <is>
           <t>案件</t>
         </is>
       </c>
-      <c r="C1" s="27" t="inlineStr">
-        <is>
-          <t>LPの状態</t>
-        </is>
-      </c>
-      <c r="D1" s="27" t="inlineStr">
-        <is>
-          <t>区分</t>
-        </is>
-      </c>
-      <c r="E1" s="27" t="inlineStr">
-        <is>
-          <t>優先</t>
-        </is>
-      </c>
-      <c r="F1" s="27" t="inlineStr">
+      <c r="C1" s="21" t="inlineStr">
         <is>
           <t>状態</t>
         </is>
       </c>
+      <c r="D1" s="21" t="inlineStr">
+        <is>
+          <t>担当</t>
+        </is>
+      </c>
     </row>
     <row r="2">
-      <c r="A2" s="28" t="n">
+      <c r="A2" s="22" t="n">
         <v>0</v>
       </c>
-      <c r="B2" s="29" t="inlineStr">
+      <c r="B2" s="23" t="inlineStr">
         <is>
           <t>REALIZE CLUB（法人向け）</t>
         </is>
       </c>
-      <c r="C2" s="29" t="inlineStr">
-        <is>
-          <t>現行</t>
-        </is>
-      </c>
-      <c r="D2" s="29" t="inlineStr">
-        <is>
-          <t>LP</t>
-        </is>
-      </c>
-      <c r="E2" s="29" t="inlineStr">
-        <is>
-          <t>P1</t>
-        </is>
-      </c>
-      <c r="F2" s="29" t="inlineStr">
+      <c r="C2" s="23" t="inlineStr">
         <is>
           <t>未着手</t>
         </is>
       </c>
+      <c r="D2" s="23" t="inlineStr">
+        <is>
+          <t>未定</t>
+        </is>
+      </c>
     </row>
     <row r="3">
-      <c r="A3" s="28" t="n">
+      <c r="A3" s="22" t="n">
         <v>0.05</v>
       </c>
-      <c r="B3" s="29" t="inlineStr">
+      <c r="B3" s="23" t="inlineStr">
         <is>
           <t>LIFE MAKE PARTNERS（加盟店募集）</t>
         </is>
       </c>
-      <c r="C3" s="29" t="inlineStr">
-        <is>
-          <t>別案</t>
-        </is>
-      </c>
-      <c r="D3" s="29" t="inlineStr">
-        <is>
-          <t>教材・ツール</t>
-        </is>
-      </c>
-      <c r="E3" s="29" t="inlineStr">
-        <is>
-          <t>P2</t>
-        </is>
-      </c>
-      <c r="F3" s="29" t="inlineStr">
+      <c r="C3" s="23" t="inlineStr">
         <is>
           <t>進行中</t>
         </is>
       </c>
+      <c r="D3" s="23" t="inlineStr">
+        <is>
+          <t>社長</t>
+        </is>
+      </c>
     </row>
     <row r="4">
-      <c r="A4" s="28" t="n">
+      <c r="A4" s="22" t="n">
         <v>0.1</v>
       </c>
-      <c r="B4" s="29" t="inlineStr">
+      <c r="B4" s="23" t="inlineStr">
         <is>
           <t>まちの相談窓口</t>
         </is>
       </c>
-      <c r="C4" s="29" t="inlineStr">
-        <is>
-          <t>旧版</t>
-        </is>
-      </c>
-      <c r="D4" s="29" t="inlineStr">
-        <is>
-          <t>動画</t>
-        </is>
-      </c>
-      <c r="E4" s="29" t="inlineStr">
-        <is>
-          <t>P3</t>
-        </is>
-      </c>
-      <c r="F4" s="29" t="inlineStr">
+      <c r="C4" s="23" t="inlineStr">
         <is>
           <t>確認待ち</t>
         </is>
       </c>
+      <c r="D4" s="23" t="inlineStr">
+        <is>
+          <t>白石</t>
+        </is>
+      </c>
     </row>
     <row r="5">
-      <c r="A5" s="28" t="n">
+      <c r="A5" s="22" t="n">
         <v>0.15</v>
       </c>
-      <c r="B5" s="29" t="inlineStr">
+      <c r="B5" s="23" t="inlineStr">
         <is>
           <t>不動産FC加盟</t>
         </is>
       </c>
-      <c r="C5" s="29" t="inlineStr">
-        <is>
-          <t>単発</t>
-        </is>
-      </c>
-      <c r="D5" s="29" t="inlineStr">
-        <is>
-          <t>広告</t>
+      <c r="D5" s="23" t="inlineStr">
+        <is>
+          <t>池之上</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="28" t="n">
+      <c r="A6" s="22" t="n">
         <v>0.2</v>
       </c>
+      <c r="D6" s="23" t="inlineStr">
+        <is>
+          <t>大熊</t>
+        </is>
+      </c>
     </row>
     <row r="7">
-      <c r="A7" s="28" t="n">
+      <c r="A7" s="22" t="n">
         <v>0.25</v>
       </c>
+      <c r="D7" s="23" t="inlineStr">
+        <is>
+          <t>片山</t>
+        </is>
+      </c>
     </row>
     <row r="8">
-      <c r="A8" s="28" t="n">
+      <c r="A8" s="22" t="n">
         <v>0.3</v>
       </c>
+      <c r="D8" s="23" t="inlineStr">
+        <is>
+          <t>寺井</t>
+        </is>
+      </c>
     </row>
     <row r="9">
-      <c r="A9" s="28" t="n">
+      <c r="A9" s="22" t="n">
         <v>0.35</v>
       </c>
+      <c r="D9" s="23" t="inlineStr">
+        <is>
+          <t>全員</t>
+        </is>
+      </c>
     </row>
     <row r="10">
-      <c r="A10" s="28" t="n">
+      <c r="A10" s="22" t="n">
         <v>0.4</v>
       </c>
+      <c r="D10" s="23" t="inlineStr">
+        <is>
+          <t>大熊・片山</t>
+        </is>
+      </c>
     </row>
     <row r="11">
-      <c r="A11" s="28" t="n">
+      <c r="A11" s="22" t="n">
         <v>0.45</v>
       </c>
+      <c r="D11" s="23" t="inlineStr">
+        <is>
+          <t>池之上・片山</t>
+        </is>
+      </c>
     </row>
     <row r="12">
-      <c r="A12" s="28" t="n">
+      <c r="A12" s="22" t="n">
         <v>0.5</v>
       </c>
+      <c r="D12" s="23" t="inlineStr">
+        <is>
+          <t>大熊・白石</t>
+        </is>
+      </c>
     </row>
     <row r="13">
-      <c r="A13" s="28" t="n">
+      <c r="A13" s="22" t="n">
         <v>0.55</v>
       </c>
+      <c r="D13" s="23" t="inlineStr">
+        <is>
+          <t>全員・池之上</t>
+        </is>
+      </c>
     </row>
     <row r="14">
-      <c r="A14" s="28" t="n">
+      <c r="A14" s="22" t="n">
         <v>0.6000000000000001</v>
       </c>
+      <c r="D14" s="23" t="inlineStr">
+        <is>
+          <t>社長・白石・片山</t>
+        </is>
+      </c>
     </row>
     <row r="15">
-      <c r="A15" s="28" t="n">
+      <c r="A15" s="22" t="n">
         <v>0.65</v>
       </c>
+      <c r="D15" s="23" t="inlineStr">
+        <is>
+          <t>白石・池之上・大熊</t>
+        </is>
+      </c>
     </row>
     <row r="16">
-      <c r="A16" s="28" t="n">
+      <c r="A16" s="22" t="n">
         <v>0.7000000000000001</v>
       </c>
+      <c r="D16" s="23" t="inlineStr">
+        <is>
+          <t>白石・片山</t>
+        </is>
+      </c>
     </row>
     <row r="17">
-      <c r="A17" s="28" t="n">
+      <c r="A17" s="22" t="n">
         <v>0.75</v>
       </c>
+      <c r="D17" s="23" t="inlineStr">
+        <is>
+          <t>社長・寺井・池之上・弁護士</t>
+        </is>
+      </c>
     </row>
     <row r="18">
-      <c r="A18" s="28" t="n">
+      <c r="A18" s="22" t="n">
         <v>0.8</v>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="28" t="n">
+      <c r="A19" s="22" t="n">
         <v>0.8500000000000001</v>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="28" t="n">
+      <c r="A20" s="22" t="n">
         <v>0.9</v>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="28" t="n">
+      <c r="A21" s="22" t="n">
         <v>0.9500000000000001</v>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="28" t="n">
+      <c r="A22" s="22" t="n">
         <v>1</v>
       </c>
     </row>
@@ -2041,18 +1849,16 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I28"/>
+  <dimension ref="A1:G28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="16" customWidth="1" min="1" max="1"/>
-    <col width="6" customWidth="1" min="2" max="2"/>
-    <col width="34" customWidth="1" min="3" max="3"/>
-    <col width="30" customWidth="1" min="4" max="4"/>
-    <col width="22" customWidth="1" min="5" max="5"/>
-    <col width="9" customWidth="1" min="6" max="6"/>
-    <col width="10" customWidth="1" min="7" max="7"/>
-    <col width="34" customWidth="1" min="8" max="8"/>
-    <col width="44" customWidth="1" min="9" max="9"/>
+    <col width="34" customWidth="1" min="1" max="1"/>
+    <col width="30" customWidth="1" min="2" max="2"/>
+    <col width="24" customWidth="1" min="3" max="3"/>
+    <col width="10" customWidth="1" min="4" max="4"/>
+    <col width="11" customWidth="1" min="5" max="5"/>
+    <col width="34" customWidth="1" min="6" max="6"/>
+    <col width="44" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -2079,795 +1885,625 @@
     <row r="5" ht="34" customHeight="1">
       <c r="A5" s="4" t="inlineStr">
         <is>
-          <t>区分</t>
+          <t>何を作るか／するか</t>
         </is>
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>優先</t>
+          <t>どこで使う</t>
         </is>
       </c>
       <c r="C5" s="4" t="inlineStr">
         <is>
-          <t>何を作るか／するか</t>
+          <t>担当</t>
         </is>
       </c>
       <c r="D5" s="4" t="inlineStr">
         <is>
-          <t>どこで使う</t>
+          <t>進捗</t>
         </is>
       </c>
       <c r="E5" s="4" t="inlineStr">
         <is>
-          <t>担当</t>
+          <t>状態</t>
         </is>
       </c>
       <c r="F5" s="4" t="inlineStr">
         <is>
-          <t>進捗</t>
+          <t>URL記入欄</t>
         </is>
       </c>
       <c r="G5" s="4" t="inlineStr">
         <is>
-          <t>状態</t>
-        </is>
-      </c>
-      <c r="H5" s="4" t="inlineStr">
-        <is>
-          <t>URL記入欄</t>
-        </is>
-      </c>
-      <c r="I5" s="4" t="inlineStr">
-        <is>
           <t>メモ</t>
         </is>
       </c>
     </row>
     <row r="6" ht="32" customHeight="1">
-      <c r="A6" s="30" t="inlineStr">
-        <is>
-          <t>教材・ツール</t>
-        </is>
-      </c>
-      <c r="B6" s="8" t="inlineStr">
-        <is>
-          <t>P2</t>
-        </is>
-      </c>
-      <c r="C6" s="7" t="inlineStr">
+      <c r="A6" s="6" t="inlineStr">
         <is>
           <t>eラーニング（ツール本体）</t>
         </is>
       </c>
-      <c r="D6" s="7" t="inlineStr">
+      <c r="B6" s="6" t="inlineStr">
         <is>
           <t>LMP事業 · Web・ツール・システム</t>
         </is>
       </c>
-      <c r="E6" s="14" t="inlineStr">
+      <c r="C6" s="24" t="inlineStr">
         <is>
           <t>社長・白石・片山</t>
         </is>
       </c>
-      <c r="F6" s="31" t="n">
+      <c r="D6" s="25" t="n">
         <v>0.5</v>
       </c>
-      <c r="G6" s="15" t="inlineStr">
+      <c r="E6" s="26" t="inlineStr">
         <is>
           <t>進行中</t>
         </is>
       </c>
-      <c r="H6" s="32" t="n"/>
-      <c r="I6" s="7" t="inlineStr">
+      <c r="F6" s="27" t="n"/>
+      <c r="G6" s="6" t="inlineStr">
         <is>
           <t>加盟店が学ぶ画面そのもの</t>
         </is>
       </c>
     </row>
     <row r="7" ht="32" customHeight="1">
-      <c r="A7" s="30" t="inlineStr">
-        <is>
-          <t>教材・ツール</t>
-        </is>
-      </c>
-      <c r="B7" s="8" t="inlineStr">
-        <is>
-          <t>P2</t>
-        </is>
-      </c>
-      <c r="C7" s="7" t="inlineStr">
+      <c r="A7" s="6" t="inlineStr">
         <is>
           <t>eラーニング動画</t>
         </is>
       </c>
-      <c r="D7" s="7" t="inlineStr">
+      <c r="B7" s="6" t="inlineStr">
         <is>
           <t>LMP事業 · Web・ツール・システム</t>
         </is>
       </c>
-      <c r="E7" s="33" t="inlineStr">
+      <c r="C7" s="28" t="inlineStr">
         <is>
           <t>未定</t>
         </is>
       </c>
-      <c r="F7" s="31" t="n">
+      <c r="D7" s="25" t="n">
         <v>0.2</v>
       </c>
-      <c r="G7" s="15" t="inlineStr">
+      <c r="E7" s="26" t="inlineStr">
         <is>
           <t>進行中</t>
         </is>
       </c>
-      <c r="H7" s="32" t="n"/>
-      <c r="I7" s="7" t="inlineStr">
+      <c r="F7" s="27" t="n"/>
+      <c r="G7" s="6" t="inlineStr">
         <is>
           <t>教材の中で流す動画。担当が決まっていない</t>
         </is>
       </c>
     </row>
     <row r="8" ht="32" customHeight="1">
-      <c r="A8" s="30" t="inlineStr">
-        <is>
-          <t>教材・ツール</t>
-        </is>
-      </c>
-      <c r="B8" s="8" t="inlineStr">
-        <is>
-          <t>P2</t>
-        </is>
-      </c>
-      <c r="C8" s="7" t="inlineStr">
+      <c r="A8" s="6" t="inlineStr">
         <is>
           <t>教育診断</t>
         </is>
       </c>
-      <c r="D8" s="7" t="inlineStr">
+      <c r="B8" s="6" t="inlineStr">
         <is>
           <t>RC事業 · Web・ツール・システム</t>
         </is>
       </c>
-      <c r="E8" s="14" t="inlineStr">
+      <c r="C8" s="24" t="inlineStr">
         <is>
           <t>白石</t>
         </is>
       </c>
-      <c r="F8" s="31" t="n">
+      <c r="D8" s="25" t="n">
         <v>0.8</v>
       </c>
-      <c r="G8" s="15" t="inlineStr">
+      <c r="E8" s="26" t="inlineStr">
         <is>
           <t>進行中</t>
         </is>
       </c>
-      <c r="H8" s="32" t="n"/>
-      <c r="I8" s="7" t="inlineStr">
+      <c r="F8" s="27" t="n"/>
+      <c r="G8" s="6" t="inlineStr">
         <is>
           <t>学ぶ前に現在地をはかる</t>
         </is>
       </c>
     </row>
     <row r="9" ht="32" customHeight="1">
-      <c r="A9" s="30" t="inlineStr">
-        <is>
-          <t>教材・ツール</t>
-        </is>
-      </c>
-      <c r="B9" s="8" t="inlineStr">
-        <is>
-          <t>P2</t>
-        </is>
-      </c>
-      <c r="C9" s="7" t="inlineStr">
+      <c r="A9" s="6" t="inlineStr">
         <is>
           <t>教科書の前段階の資料</t>
         </is>
       </c>
-      <c r="D9" s="7" t="inlineStr">
+      <c r="B9" s="6" t="inlineStr">
         <is>
           <t>RC事業 · 動画・コンテンツ</t>
         </is>
       </c>
-      <c r="E9" s="14" t="inlineStr">
+      <c r="C9" s="24" t="inlineStr">
         <is>
           <t>白石</t>
         </is>
       </c>
-      <c r="F9" s="31" t="n">
+      <c r="D9" s="25" t="n">
         <v>0.6</v>
       </c>
-      <c r="G9" s="15" t="inlineStr">
+      <c r="E9" s="26" t="inlineStr">
         <is>
           <t>進行中</t>
         </is>
       </c>
-      <c r="H9" s="32" t="n"/>
-      <c r="I9" s="7" t="inlineStr">
+      <c r="F9" s="27" t="n"/>
+      <c r="G9" s="6" t="inlineStr">
         <is>
           <t>教材のもとになる原稿</t>
         </is>
       </c>
     </row>
     <row r="10" ht="32" customHeight="1">
-      <c r="A10" s="30" t="inlineStr">
-        <is>
-          <t>教材・ツール</t>
-        </is>
-      </c>
-      <c r="B10" s="8" t="inlineStr">
-        <is>
-          <t>P2</t>
-        </is>
-      </c>
-      <c r="C10" s="7" t="inlineStr">
+      <c r="A10" s="6" t="inlineStr">
         <is>
           <t>各ツールマニュアル作成</t>
         </is>
       </c>
-      <c r="D10" s="7" t="inlineStr">
+      <c r="B10" s="6" t="inlineStr">
         <is>
           <t>LMP事業 · 営業・資料</t>
         </is>
       </c>
-      <c r="E10" s="33" t="inlineStr">
+      <c r="C10" s="28" t="inlineStr">
         <is>
           <t>未定</t>
         </is>
       </c>
-      <c r="F10" s="31" t="n">
+      <c r="D10" s="25" t="n">
         <v>0</v>
       </c>
-      <c r="G10" s="22" t="inlineStr">
+      <c r="E10" s="29" t="inlineStr">
         <is>
           <t>未着手</t>
         </is>
       </c>
-      <c r="H10" s="32" t="n"/>
-      <c r="I10" s="7" t="inlineStr">
+      <c r="F10" s="27" t="n"/>
+      <c r="G10" s="6" t="inlineStr">
         <is>
           <t>担当が決まっていない</t>
         </is>
       </c>
     </row>
     <row r="11" ht="32" customHeight="1">
-      <c r="A11" s="30" t="inlineStr">
-        <is>
-          <t>教材・ツール</t>
-        </is>
-      </c>
-      <c r="B11" s="8" t="inlineStr">
-        <is>
-          <t>P2</t>
-        </is>
-      </c>
-      <c r="C11" s="7" t="inlineStr">
+      <c r="A11" s="6" t="inlineStr">
         <is>
           <t>研修会準備</t>
         </is>
       </c>
-      <c r="D11" s="7" t="inlineStr">
+      <c r="B11" s="6" t="inlineStr">
         <is>
           <t>LMP事業 · 加盟開発</t>
         </is>
       </c>
-      <c r="E11" s="14" t="inlineStr">
+      <c r="C11" s="24" t="inlineStr">
         <is>
           <t>白石・池之上・大熊</t>
         </is>
       </c>
-      <c r="F11" s="31" t="n">
+      <c r="D11" s="25" t="n">
         <v>0</v>
       </c>
-      <c r="G11" s="22" t="inlineStr">
+      <c r="E11" s="29" t="inlineStr">
         <is>
           <t>未着手</t>
         </is>
       </c>
-      <c r="H11" s="32" t="n"/>
-      <c r="I11" s="7" t="inlineStr"/>
+      <c r="F11" s="27" t="n"/>
+      <c r="G11" s="6" t="inlineStr"/>
     </row>
     <row r="12" ht="32" customHeight="1">
-      <c r="A12" s="30" t="inlineStr">
-        <is>
-          <t>教材・ツール</t>
-        </is>
-      </c>
-      <c r="B12" s="8" t="inlineStr">
-        <is>
-          <t>P2</t>
-        </is>
-      </c>
-      <c r="C12" s="7" t="inlineStr">
+      <c r="A12" s="6" t="inlineStr">
         <is>
           <t>eラーニング接続・設計</t>
         </is>
       </c>
-      <c r="D12" s="7" t="inlineStr">
+      <c r="B12" s="6" t="inlineStr">
         <is>
           <t>RCP事業 · Web・ツール・システム</t>
         </is>
       </c>
-      <c r="E12" s="14" t="inlineStr">
+      <c r="C12" s="24" t="inlineStr">
         <is>
           <t>白石</t>
         </is>
       </c>
-      <c r="F12" s="31" t="n">
+      <c r="D12" s="25" t="n">
         <v>0</v>
       </c>
-      <c r="G12" s="22" t="inlineStr">
+      <c r="E12" s="29" t="inlineStr">
         <is>
           <t>未着手</t>
         </is>
       </c>
-      <c r="H12" s="32" t="n"/>
-      <c r="I12" s="7" t="inlineStr"/>
+      <c r="F12" s="27" t="n"/>
+      <c r="G12" s="6" t="inlineStr"/>
     </row>
     <row r="13" ht="32" customHeight="1">
-      <c r="A13" s="30" t="inlineStr">
-        <is>
-          <t>教材・ツール</t>
-        </is>
-      </c>
-      <c r="B13" s="8" t="inlineStr">
-        <is>
-          <t>P2</t>
-        </is>
-      </c>
-      <c r="C13" s="7" t="inlineStr">
+      <c r="A13" s="6" t="inlineStr">
         <is>
           <t>AIロープレ（アオ先生）</t>
         </is>
       </c>
-      <c r="D13" s="7" t="inlineStr">
+      <c r="B13" s="6" t="inlineStr">
         <is>
           <t>AIアオ先生 · 営業コーチ</t>
         </is>
       </c>
-      <c r="E13" s="14" t="inlineStr">
+      <c r="C13" s="24" t="inlineStr">
         <is>
           <t>池之上</t>
         </is>
       </c>
-      <c r="F13" s="31" t="n">
+      <c r="D13" s="25" t="n">
         <v>0.9</v>
       </c>
+      <c r="E13" s="30" t="inlineStr">
+        <is>
+          <t>確認待ち</t>
+        </is>
+      </c>
+      <c r="F13" s="27" t="n"/>
       <c r="G13" s="6" t="inlineStr">
         <is>
-          <t>確認待ち</t>
-        </is>
-      </c>
-      <c r="H13" s="32" t="n"/>
-      <c r="I13" s="7" t="inlineStr">
-        <is>
           <t>制作MASTERのみに記載</t>
         </is>
       </c>
     </row>
     <row r="14" ht="32" customHeight="1">
-      <c r="A14" s="30" t="inlineStr">
-        <is>
-          <t>動画</t>
-        </is>
-      </c>
-      <c r="B14" s="8" t="inlineStr">
-        <is>
-          <t>P2</t>
-        </is>
-      </c>
-      <c r="C14" s="7" t="inlineStr">
+      <c r="A14" s="6" t="inlineStr">
         <is>
           <t>結婚後の暮らしと人生設計動画</t>
         </is>
       </c>
-      <c r="D14" s="7" t="inlineStr">
+      <c r="B14" s="6" t="inlineStr">
         <is>
           <t>RC事業 · 動画・コンテンツ</t>
         </is>
       </c>
-      <c r="E14" s="14" t="inlineStr">
+      <c r="C14" s="24" t="inlineStr">
         <is>
           <t>白石</t>
         </is>
       </c>
-      <c r="F14" s="31" t="n">
+      <c r="D14" s="25" t="n">
         <v>0.7</v>
       </c>
-      <c r="G14" s="15" t="inlineStr">
+      <c r="E14" s="26" t="inlineStr">
         <is>
           <t>進行中</t>
         </is>
       </c>
-      <c r="H14" s="32" t="n"/>
-      <c r="I14" s="7" t="inlineStr">
+      <c r="F14" s="27" t="n"/>
+      <c r="G14" s="6" t="inlineStr">
         <is>
           <t>動画で唯一動いている1本</t>
         </is>
       </c>
     </row>
     <row r="15" ht="32" customHeight="1">
-      <c r="A15" s="30" t="inlineStr">
-        <is>
-          <t>動画</t>
-        </is>
-      </c>
-      <c r="B15" s="8" t="inlineStr">
-        <is>
-          <t>P2</t>
-        </is>
-      </c>
-      <c r="C15" s="7" t="inlineStr">
+      <c r="A15" s="6" t="inlineStr">
         <is>
           <t>サービス説明動画</t>
         </is>
       </c>
-      <c r="D15" s="7" t="inlineStr">
+      <c r="B15" s="6" t="inlineStr">
         <is>
           <t>RC事業 · 動画・コンテンツ</t>
         </is>
       </c>
-      <c r="E15" s="14" t="inlineStr">
+      <c r="C15" s="24" t="inlineStr">
         <is>
           <t>白石</t>
         </is>
       </c>
-      <c r="F15" s="31" t="n">
+      <c r="D15" s="25" t="n">
         <v>0</v>
       </c>
-      <c r="G15" s="22" t="inlineStr">
+      <c r="E15" s="29" t="inlineStr">
         <is>
           <t>未着手</t>
         </is>
       </c>
-      <c r="H15" s="32" t="n"/>
-      <c r="I15" s="7" t="inlineStr"/>
+      <c r="F15" s="27" t="n"/>
+      <c r="G15" s="6" t="inlineStr"/>
     </row>
     <row r="16" ht="32" customHeight="1">
-      <c r="A16" s="30" t="inlineStr">
-        <is>
-          <t>動画</t>
-        </is>
-      </c>
-      <c r="B16" s="8" t="inlineStr">
-        <is>
-          <t>P2</t>
-        </is>
-      </c>
-      <c r="C16" s="7" t="inlineStr">
+      <c r="A16" s="6" t="inlineStr">
         <is>
           <t>toC動画</t>
         </is>
       </c>
-      <c r="D16" s="7" t="inlineStr">
+      <c r="B16" s="6" t="inlineStr">
         <is>
           <t>RC事業 · 動画・コンテンツ</t>
         </is>
       </c>
-      <c r="E16" s="14" t="inlineStr">
+      <c r="C16" s="24" t="inlineStr">
         <is>
           <t>白石</t>
         </is>
       </c>
-      <c r="F16" s="31" t="n">
+      <c r="D16" s="25" t="n">
         <v>0</v>
       </c>
-      <c r="G16" s="22" t="inlineStr">
+      <c r="E16" s="29" t="inlineStr">
         <is>
           <t>未着手</t>
         </is>
       </c>
-      <c r="H16" s="32" t="n"/>
-      <c r="I16" s="7" t="inlineStr"/>
+      <c r="F16" s="27" t="n"/>
+      <c r="G16" s="6" t="inlineStr"/>
     </row>
     <row r="17" ht="32" customHeight="1">
-      <c r="A17" s="30" t="inlineStr">
-        <is>
-          <t>動画</t>
-        </is>
-      </c>
-      <c r="B17" s="8" t="inlineStr">
-        <is>
-          <t>P2</t>
-        </is>
-      </c>
-      <c r="C17" s="7" t="inlineStr">
+      <c r="A17" s="6" t="inlineStr">
         <is>
           <t>サービスデモ動画</t>
         </is>
       </c>
-      <c r="D17" s="7" t="inlineStr">
+      <c r="B17" s="6" t="inlineStr">
         <is>
           <t>RCP事業 · 動画・コンテンツ</t>
         </is>
       </c>
-      <c r="E17" s="14" t="inlineStr">
+      <c r="C17" s="24" t="inlineStr">
         <is>
           <t>白石</t>
         </is>
       </c>
-      <c r="F17" s="31" t="n">
+      <c r="D17" s="25" t="n">
         <v>0</v>
       </c>
-      <c r="G17" s="22" t="inlineStr">
+      <c r="E17" s="29" t="inlineStr">
         <is>
           <t>未着手</t>
         </is>
       </c>
-      <c r="H17" s="32" t="n"/>
-      <c r="I17" s="7" t="inlineStr"/>
+      <c r="F17" s="27" t="n"/>
+      <c r="G17" s="6" t="inlineStr"/>
     </row>
     <row r="18" ht="32" customHeight="1">
-      <c r="A18" s="30" t="inlineStr">
-        <is>
-          <t>動画</t>
-        </is>
-      </c>
-      <c r="B18" s="8" t="inlineStr">
-        <is>
-          <t>P2</t>
-        </is>
-      </c>
-      <c r="C18" s="7" t="inlineStr">
+      <c r="A18" s="6" t="inlineStr">
         <is>
           <t>水谷先生の本の動画</t>
         </is>
       </c>
-      <c r="D18" s="7" t="inlineStr">
+      <c r="B18" s="6" t="inlineStr">
         <is>
           <t>RCP事業 · 動画・コンテンツ</t>
         </is>
       </c>
-      <c r="E18" s="14" t="inlineStr">
+      <c r="C18" s="24" t="inlineStr">
         <is>
           <t>白石</t>
         </is>
       </c>
-      <c r="F18" s="31" t="n">
+      <c r="D18" s="25" t="n">
         <v>0</v>
       </c>
-      <c r="G18" s="22" t="inlineStr">
+      <c r="E18" s="29" t="inlineStr">
         <is>
           <t>未着手</t>
         </is>
       </c>
-      <c r="H18" s="32" t="n"/>
-      <c r="I18" s="7" t="inlineStr"/>
+      <c r="F18" s="27" t="n"/>
+      <c r="G18" s="6" t="inlineStr"/>
     </row>
     <row r="19" ht="32" customHeight="1">
-      <c r="A19" s="30" t="inlineStr">
-        <is>
-          <t>動画</t>
-        </is>
-      </c>
-      <c r="B19" s="8" t="inlineStr">
-        <is>
-          <t>P3</t>
-        </is>
-      </c>
-      <c r="C19" s="7" t="inlineStr">
+      <c r="A19" s="6" t="inlineStr">
         <is>
           <t>OEM各先生の宣伝動画（5本）</t>
         </is>
       </c>
-      <c r="D19" s="7" t="inlineStr">
+      <c r="B19" s="6" t="inlineStr">
         <is>
           <t>RCP PPモデル · OEM</t>
         </is>
       </c>
-      <c r="E19" s="14" t="inlineStr">
+      <c r="C19" s="24" t="inlineStr">
         <is>
           <t>白石</t>
         </is>
       </c>
-      <c r="F19" s="31" t="n">
+      <c r="D19" s="25" t="n">
         <v>0</v>
       </c>
-      <c r="G19" s="22" t="inlineStr">
+      <c r="E19" s="29" t="inlineStr">
         <is>
           <t>未着手</t>
         </is>
       </c>
-      <c r="H19" s="32" t="n"/>
-      <c r="I19" s="7" t="inlineStr">
+      <c r="F19" s="27" t="n"/>
+      <c r="G19" s="6" t="inlineStr">
         <is>
           <t>AKさん・大橋会長・木原さん・水谷先生・藤田先生</t>
         </is>
       </c>
     </row>
     <row r="20" ht="32" customHeight="1">
-      <c r="A20" s="30" t="inlineStr">
-        <is>
-          <t>動画</t>
-        </is>
-      </c>
-      <c r="B20" s="8" t="inlineStr">
-        <is>
-          <t>P3</t>
-        </is>
-      </c>
-      <c r="C20" s="7" t="inlineStr">
+      <c r="A20" s="6" t="inlineStr">
         <is>
           <t>宣伝動画・PV ロング／ショート（7本）</t>
         </is>
       </c>
-      <c r="D20" s="7" t="inlineStr">
+      <c r="B20" s="6" t="inlineStr">
         <is>
           <t>RC／RCP／HI／PP · REALIZE QUEST</t>
         </is>
       </c>
-      <c r="E20" s="14" t="inlineStr">
+      <c r="C20" s="24" t="inlineStr">
         <is>
           <t>白石・片山</t>
         </is>
       </c>
-      <c r="F20" s="31" t="n">
+      <c r="D20" s="25" t="n">
         <v>0</v>
       </c>
-      <c r="G20" s="22" t="inlineStr">
+      <c r="E20" s="29" t="inlineStr">
         <is>
           <t>未着手</t>
         </is>
       </c>
-      <c r="H20" s="32" t="n"/>
-      <c r="I20" s="7" t="inlineStr"/>
+      <c r="F20" s="27" t="n"/>
+      <c r="G20" s="6" t="inlineStr"/>
     </row>
     <row r="21" ht="32" customHeight="1">
-      <c r="A21" s="30" t="inlineStr">
-        <is>
-          <t>動画</t>
-        </is>
-      </c>
-      <c r="B21" s="8" t="inlineStr">
-        <is>
-          <t>P3</t>
-        </is>
-      </c>
-      <c r="C21" s="7" t="inlineStr">
+      <c r="A21" s="6" t="inlineStr">
         <is>
           <t>採用まわりの動画（2本）</t>
         </is>
       </c>
-      <c r="D21" s="7" t="inlineStr">
+      <c r="B21" s="6" t="inlineStr">
         <is>
           <t>採用 · 学生募集</t>
         </is>
       </c>
-      <c r="E21" s="14" t="inlineStr">
+      <c r="C21" s="24" t="inlineStr">
         <is>
           <t>白石・片山</t>
         </is>
       </c>
-      <c r="F21" s="31" t="n">
+      <c r="D21" s="25" t="n">
         <v>0</v>
       </c>
-      <c r="G21" s="22" t="inlineStr">
+      <c r="E21" s="29" t="inlineStr">
         <is>
           <t>未着手</t>
         </is>
       </c>
-      <c r="H21" s="32" t="n"/>
-      <c r="I21" s="7" t="inlineStr">
+      <c r="F21" s="27" t="n"/>
+      <c r="G21" s="6" t="inlineStr">
         <is>
           <t>PR動画・SNS採用募集動画</t>
         </is>
       </c>
     </row>
     <row r="22">
-      <c r="E22" s="23" t="inlineStr">
+      <c r="C22" s="18" t="inlineStr">
         <is>
           <t>平均</t>
         </is>
       </c>
-      <c r="F22" s="34">
-        <f>AVERAGE(F6:F21)</f>
+      <c r="D22" s="31">
+        <f>AVERAGE(D6:D21)</f>
         <v/>
       </c>
-      <c r="G22" s="26">
-        <f>COUNTIF(G6:G21,"未着手")&amp;" 件未着手"</f>
+      <c r="E22" s="20">
+        <f>COUNTIF(E6:E21,"未着手")&amp;" 件未着手"</f>
         <v/>
       </c>
-      <c r="H22" s="26">
-        <f>COUNTA(H6:H21)&amp;" 件 登録済み"</f>
+      <c r="F22" s="20">
+        <f>COUNTA(F6:F21)&amp;" 件 登録ずみ"</f>
         <v/>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="35" t="inlineStr">
+      <c r="A24" s="32" t="inlineStr">
         <is>
           <t>できている設計書・ガイド</t>
         </is>
       </c>
     </row>
     <row r="25">
-      <c r="C25" s="36" t="inlineStr">
+      <c r="A25" s="33" t="inlineStr">
         <is>
           <t>LIFE CHECK42 Eラーニング画面設計書</t>
         </is>
       </c>
-      <c r="D25" s="2" t="inlineStr">
+      <c r="B25" s="2" t="inlineStr">
         <is>
           <t>画面設計</t>
         </is>
       </c>
-      <c r="E25" s="2" t="inlineStr">
+      <c r="C25" s="2" t="inlineStr">
         <is>
           <t>2026-08-31</t>
         </is>
       </c>
-      <c r="I25" s="37" t="inlineStr">
+      <c r="G25" s="34" t="inlineStr">
         <is>
           <t>開く</t>
         </is>
       </c>
     </row>
     <row r="26">
-      <c r="C26" s="36" t="inlineStr">
+      <c r="A26" s="33" t="inlineStr">
         <is>
           <t>RCP ノーマル版 eラーニング｜UI提案 v1</t>
         </is>
       </c>
-      <c r="D26" s="2" t="inlineStr">
+      <c r="B26" s="2" t="inlineStr">
         <is>
           <t>UI提案</t>
         </is>
       </c>
-      <c r="E26" s="2" t="inlineStr">
+      <c r="C26" s="2" t="inlineStr">
         <is>
           <t>2026-08-05</t>
         </is>
       </c>
-      <c r="I26" s="37" t="inlineStr">
+      <c r="G26" s="34" t="inlineStr">
         <is>
           <t>開く</t>
         </is>
       </c>
     </row>
     <row r="27">
-      <c r="C27" s="36" t="inlineStr">
+      <c r="A27" s="33" t="inlineStr">
         <is>
           <t>AIロープレ 操作ガイド</t>
         </is>
       </c>
-      <c r="D27" s="2" t="inlineStr">
+      <c r="B27" s="2" t="inlineStr">
         <is>
           <t>操作ガイド</t>
         </is>
       </c>
-      <c r="E27" s="2" t="inlineStr">
+      <c r="C27" s="2" t="inlineStr">
         <is>
           <t>2026-08-31</t>
         </is>
       </c>
-      <c r="I27" s="37" t="inlineStr">
+      <c r="G27" s="34" t="inlineStr">
         <is>
           <t>開く</t>
         </is>
       </c>
     </row>
     <row r="28">
-      <c r="C28" s="36" t="inlineStr">
+      <c r="A28" s="33" t="inlineStr">
         <is>
           <t>生成AI動画講座 比較検討</t>
         </is>
       </c>
-      <c r="D28" s="2" t="inlineStr">
+      <c r="B28" s="2" t="inlineStr">
         <is>
           <t>比較検討</t>
         </is>
       </c>
-      <c r="E28" s="2" t="inlineStr">
+      <c r="C28" s="2" t="inlineStr">
         <is>
           <t>2026-08-21</t>
         </is>
       </c>
-      <c r="I28" s="37" t="inlineStr">
+      <c r="G28" s="34" t="inlineStr">
         <is>
           <t>開く</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A5:I21"/>
-  <conditionalFormatting sqref="F6:F21">
+  <autoFilter ref="A5:G21"/>
+  <conditionalFormatting sqref="D6:D21">
     <cfRule type="dataBar" priority="1">
       <dataBar showValue="1">
         <cfvo type="num" val="0"/>
@@ -2876,25 +2512,22 @@
       </dataBar>
     </cfRule>
   </conditionalFormatting>
-  <dataValidations count="4">
-    <dataValidation sqref="F6:F21" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" promptTitle="進捗を選ぶ" prompt="5%きざみで選べます。直接入力もできます。" type="list">
+  <dataValidations count="3">
+    <dataValidation sqref="C6:C21" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" promptTitle="担当を選ぶ" prompt="一覧にない場合は直接入力もできます" type="list">
+      <formula1>'選択肢'!$D$2:$D$17</formula1>
+    </dataValidation>
+    <dataValidation sqref="D6:D21" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" promptTitle="進捗を選ぶ" prompt="5%きざみで選べます。直接入力もできます。" type="list">
       <formula1>'選択肢'!$A$2:$A$22</formula1>
     </dataValidation>
-    <dataValidation sqref="A6:A21" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" promptTitle="区分を選ぶ" prompt="LP／教材・ツール／動画／広告" type="list">
-      <formula1>'選択肢'!$D$2:$D$5</formula1>
-    </dataValidation>
-    <dataValidation sqref="B6:B21" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" promptTitle="優先を選ぶ" prompt="工程表の優先度" type="list">
-      <formula1>'選択肢'!$E$2:$E$4</formula1>
-    </dataValidation>
-    <dataValidation sqref="G6:G21" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" promptTitle="状態を選ぶ" prompt="未着手／進行中／確認待ち" type="list">
-      <formula1>'選択肢'!$F$2:$F$4</formula1>
+    <dataValidation sqref="E6:E21" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" promptTitle="状態を選ぶ" prompt="未着手／進行中／確認待ち" type="list">
+      <formula1>'選択肢'!$C$2:$C$4</formula1>
     </dataValidation>
   </dataValidations>
   <hyperlinks>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I25" r:id="rId1"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I26" r:id="rId2"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I27" r:id="rId3"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I28" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G25" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G26" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G27" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G28" r:id="rId4"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="anysvml"/>
@@ -2907,18 +2540,16 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I11"/>
+  <dimension ref="A1:G11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="16" customWidth="1" min="1" max="1"/>
-    <col width="6" customWidth="1" min="2" max="2"/>
-    <col width="34" customWidth="1" min="3" max="3"/>
-    <col width="30" customWidth="1" min="4" max="4"/>
-    <col width="22" customWidth="1" min="5" max="5"/>
-    <col width="9" customWidth="1" min="6" max="6"/>
-    <col width="10" customWidth="1" min="7" max="7"/>
-    <col width="34" customWidth="1" min="8" max="8"/>
-    <col width="44" customWidth="1" min="9" max="9"/>
+    <col width="34" customWidth="1" min="1" max="1"/>
+    <col width="30" customWidth="1" min="2" max="2"/>
+    <col width="24" customWidth="1" min="3" max="3"/>
+    <col width="10" customWidth="1" min="4" max="4"/>
+    <col width="11" customWidth="1" min="5" max="5"/>
+    <col width="34" customWidth="1" min="6" max="6"/>
+    <col width="44" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -2945,273 +2576,213 @@
     <row r="5" ht="34" customHeight="1">
       <c r="A5" s="4" t="inlineStr">
         <is>
-          <t>区分</t>
+          <t>何を作るか／するか</t>
         </is>
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>優先</t>
+          <t>どこで使う</t>
         </is>
       </c>
       <c r="C5" s="4" t="inlineStr">
         <is>
-          <t>何を作るか／するか</t>
+          <t>担当</t>
         </is>
       </c>
       <c r="D5" s="4" t="inlineStr">
         <is>
-          <t>どこで使う</t>
+          <t>進捗</t>
         </is>
       </c>
       <c r="E5" s="4" t="inlineStr">
         <is>
-          <t>担当</t>
+          <t>状態</t>
         </is>
       </c>
       <c r="F5" s="4" t="inlineStr">
         <is>
-          <t>進捗</t>
+          <t>URL記入欄</t>
         </is>
       </c>
       <c r="G5" s="4" t="inlineStr">
         <is>
-          <t>状態</t>
-        </is>
-      </c>
-      <c r="H5" s="4" t="inlineStr">
-        <is>
-          <t>URL記入欄</t>
-        </is>
-      </c>
-      <c r="I5" s="4" t="inlineStr">
-        <is>
           <t>メモ</t>
         </is>
       </c>
     </row>
     <row r="6" ht="32" customHeight="1">
-      <c r="A6" s="30" t="inlineStr">
-        <is>
-          <t>広告</t>
-        </is>
-      </c>
-      <c r="B6" s="8" t="inlineStr">
-        <is>
-          <t>P2</t>
-        </is>
-      </c>
-      <c r="C6" s="7" t="inlineStr">
+      <c r="A6" s="6" t="inlineStr">
         <is>
           <t>広告制作</t>
         </is>
       </c>
-      <c r="D6" s="7" t="inlineStr">
+      <c r="B6" s="6" t="inlineStr">
         <is>
           <t>RC法人開拓 · 地域企業への入口</t>
         </is>
       </c>
-      <c r="E6" s="14" t="inlineStr">
+      <c r="C6" s="24" t="inlineStr">
         <is>
           <t>大熊・片山</t>
         </is>
       </c>
-      <c r="F6" s="31" t="n">
+      <c r="D6" s="25" t="n">
         <v>0</v>
       </c>
-      <c r="G6" s="22" t="inlineStr">
+      <c r="E6" s="29" t="inlineStr">
         <is>
           <t>未着手</t>
         </is>
       </c>
-      <c r="H6" s="32" t="n"/>
-      <c r="I6" s="7" t="inlineStr">
+      <c r="F6" s="27" t="n"/>
+      <c r="G6" s="6" t="inlineStr">
         <is>
           <t>バナー・原稿などのクリエイティブ</t>
         </is>
       </c>
     </row>
     <row r="7" ht="32" customHeight="1">
-      <c r="A7" s="30" t="inlineStr">
-        <is>
-          <t>広告</t>
-        </is>
-      </c>
-      <c r="B7" s="8" t="inlineStr">
-        <is>
-          <t>P2</t>
-        </is>
-      </c>
-      <c r="C7" s="7" t="inlineStr">
+      <c r="A7" s="6" t="inlineStr">
         <is>
           <t>広告運用</t>
         </is>
       </c>
-      <c r="D7" s="7" t="inlineStr">
+      <c r="B7" s="6" t="inlineStr">
         <is>
           <t>RC法人開拓／LMP加盟開発</t>
         </is>
       </c>
-      <c r="E7" s="14" t="inlineStr">
+      <c r="C7" s="24" t="inlineStr">
         <is>
           <t>池之上・片山</t>
         </is>
       </c>
-      <c r="F7" s="31" t="n">
+      <c r="D7" s="25" t="n">
         <v>0</v>
       </c>
-      <c r="G7" s="22" t="inlineStr">
+      <c r="E7" s="29" t="inlineStr">
         <is>
           <t>未着手</t>
         </is>
       </c>
-      <c r="H7" s="32" t="n"/>
-      <c r="I7" s="7" t="inlineStr">
+      <c r="F7" s="27" t="n"/>
+      <c r="G7" s="6" t="inlineStr">
         <is>
           <t>出稿・予算・改善</t>
         </is>
       </c>
     </row>
     <row r="8" ht="32" customHeight="1">
-      <c r="A8" s="30" t="inlineStr">
-        <is>
-          <t>広告</t>
-        </is>
-      </c>
-      <c r="B8" s="8" t="inlineStr">
-        <is>
-          <t>P2</t>
-        </is>
-      </c>
-      <c r="C8" s="7" t="inlineStr">
+      <c r="A8" s="6" t="inlineStr">
         <is>
           <t>広告クリエイティブチェック</t>
         </is>
       </c>
-      <c r="D8" s="7" t="inlineStr">
+      <c r="B8" s="6" t="inlineStr">
         <is>
           <t>LMP事業 · 全体品質確認</t>
         </is>
       </c>
-      <c r="E8" s="14" t="inlineStr">
+      <c r="C8" s="24" t="inlineStr">
         <is>
           <t>白石</t>
         </is>
       </c>
-      <c r="F8" s="31" t="n">
+      <c r="D8" s="25" t="n">
         <v>0</v>
       </c>
-      <c r="G8" s="22" t="inlineStr">
+      <c r="E8" s="29" t="inlineStr">
         <is>
           <t>未着手</t>
         </is>
       </c>
-      <c r="H8" s="32" t="n"/>
-      <c r="I8" s="7" t="inlineStr">
+      <c r="F8" s="27" t="n"/>
+      <c r="G8" s="6" t="inlineStr">
         <is>
           <t>出す前の品質確認</t>
         </is>
       </c>
     </row>
     <row r="9" ht="32" customHeight="1">
-      <c r="A9" s="30" t="inlineStr">
-        <is>
-          <t>広告</t>
-        </is>
-      </c>
-      <c r="B9" s="8" t="inlineStr">
-        <is>
-          <t>P3</t>
-        </is>
-      </c>
-      <c r="C9" s="7" t="inlineStr">
+      <c r="A9" s="6" t="inlineStr">
         <is>
           <t>広告表示のチェック（景表法）</t>
         </is>
       </c>
-      <c r="D9" s="7" t="inlineStr">
+      <c r="B9" s="6" t="inlineStr">
         <is>
           <t>社内業務 · 法務・業法</t>
         </is>
       </c>
-      <c r="E9" s="14" t="inlineStr">
+      <c r="C9" s="24" t="inlineStr">
         <is>
           <t>社長・寺井・池之上・弁護士</t>
         </is>
       </c>
-      <c r="F9" s="31" t="n">
+      <c r="D9" s="25" t="n">
         <v>0</v>
       </c>
-      <c r="G9" s="22" t="inlineStr">
+      <c r="E9" s="29" t="inlineStr">
         <is>
           <t>未着手</t>
         </is>
       </c>
-      <c r="H9" s="32" t="n"/>
-      <c r="I9" s="7" t="inlineStr">
+      <c r="F9" s="27" t="n"/>
+      <c r="G9" s="6" t="inlineStr">
         <is>
           <t>言い切り表現・実績表示の法務確認</t>
         </is>
       </c>
     </row>
     <row r="10" ht="32" customHeight="1">
-      <c r="A10" s="30" t="inlineStr">
-        <is>
-          <t>広告</t>
-        </is>
-      </c>
-      <c r="B10" s="8" t="inlineStr">
-        <is>
-          <t>P3</t>
-        </is>
-      </c>
-      <c r="C10" s="7" t="inlineStr">
+      <c r="A10" s="6" t="inlineStr">
         <is>
           <t>広報・告知（LP・SNS）4件</t>
         </is>
       </c>
-      <c r="D10" s="7" t="inlineStr">
+      <c r="B10" s="6" t="inlineStr">
         <is>
           <t>RC／RCP／HI／PP · REALIZE QUEST</t>
         </is>
       </c>
-      <c r="E10" s="14" t="inlineStr">
+      <c r="C10" s="24" t="inlineStr">
         <is>
           <t>白石</t>
         </is>
       </c>
-      <c r="F10" s="31" t="n">
+      <c r="D10" s="25" t="n">
         <v>0</v>
       </c>
-      <c r="G10" s="22" t="inlineStr">
+      <c r="E10" s="29" t="inlineStr">
         <is>
           <t>未着手</t>
         </is>
       </c>
-      <c r="H10" s="32" t="n"/>
-      <c r="I10" s="7" t="inlineStr"/>
+      <c r="F10" s="27" t="n"/>
+      <c r="G10" s="6" t="inlineStr"/>
     </row>
     <row r="11">
-      <c r="E11" s="23" t="inlineStr">
+      <c r="C11" s="18" t="inlineStr">
         <is>
           <t>平均</t>
         </is>
       </c>
-      <c r="F11" s="34">
-        <f>AVERAGE(F6:F10)</f>
+      <c r="D11" s="31">
+        <f>AVERAGE(D6:D10)</f>
         <v/>
       </c>
-      <c r="G11" s="26">
-        <f>COUNTIF(G6:G10,"未着手")&amp;" 件未着手"</f>
+      <c r="E11" s="20">
+        <f>COUNTIF(E6:E10,"未着手")&amp;" 件未着手"</f>
         <v/>
       </c>
-      <c r="H11" s="26">
-        <f>COUNTA(H6:H10)&amp;" 件 登録済み"</f>
+      <c r="F11" s="20">
+        <f>COUNTA(F6:F10)&amp;" 件 登録ずみ"</f>
         <v/>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A5:I10"/>
-  <conditionalFormatting sqref="F6:F10">
+  <autoFilter ref="A5:G10"/>
+  <conditionalFormatting sqref="D6:D10">
     <cfRule type="dataBar" priority="1">
       <dataBar showValue="1">
         <cfvo type="num" val="0"/>
@@ -3220,18 +2791,15 @@
       </dataBar>
     </cfRule>
   </conditionalFormatting>
-  <dataValidations count="4">
-    <dataValidation sqref="F6:F10" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" promptTitle="進捗を選ぶ" prompt="5%きざみで選べます。直接入力もできます。" type="list">
+  <dataValidations count="3">
+    <dataValidation sqref="C6:C10" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" promptTitle="担当を選ぶ" prompt="一覧にない場合は直接入力もできます" type="list">
+      <formula1>'選択肢'!$D$2:$D$17</formula1>
+    </dataValidation>
+    <dataValidation sqref="D6:D10" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" promptTitle="進捗を選ぶ" prompt="5%きざみで選べます。直接入力もできます。" type="list">
       <formula1>'選択肢'!$A$2:$A$22</formula1>
     </dataValidation>
-    <dataValidation sqref="A6:A10" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" promptTitle="区分を選ぶ" prompt="LP／教材・ツール／動画／広告" type="list">
-      <formula1>'選択肢'!$D$2:$D$5</formula1>
-    </dataValidation>
-    <dataValidation sqref="B6:B10" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" promptTitle="優先を選ぶ" prompt="工程表の優先度" type="list">
-      <formula1>'選択肢'!$E$2:$E$4</formula1>
-    </dataValidation>
-    <dataValidation sqref="G6:G10" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" promptTitle="状態を選ぶ" prompt="未着手／進行中／確認待ち" type="list">
-      <formula1>'選択肢'!$F$2:$F$4</formula1>
+    <dataValidation sqref="E6:E10" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" promptTitle="状態を選ぶ" prompt="未着手／進行中／確認待ち" type="list">
+      <formula1>'選択肢'!$C$2:$C$4</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -3245,350 +2813,326 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B36"/>
+  <dimension ref="A1:B34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="24" customWidth="1" min="1" max="1"/>
+    <col width="26" customWidth="1" min="1" max="1"/>
     <col width="98" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="38" t="inlineStr">
+      <c r="A1" s="35" t="inlineStr">
         <is>
           <t>凡例と出典</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="39" t="inlineStr">
-        <is>
-          <t>LPシートの4段</t>
+      <c r="A3" s="36" t="inlineStr">
+        <is>
+          <t>LPの3段</t>
         </is>
       </c>
     </row>
     <row r="4" ht="36" customHeight="1">
-      <c r="A4" s="40" t="inlineStr">
-        <is>
-          <t>①原稿・デザイン</t>
-        </is>
-      </c>
-      <c r="B4" s="41" t="inlineStr">
+      <c r="A4" s="37" t="inlineStr">
+        <is>
+          <t>原稿・デザイン</t>
+        </is>
+      </c>
+      <c r="B4" s="38" t="inlineStr">
         <is>
           <t>本編の文章とデザインが最後まで通っている</t>
         </is>
       </c>
     </row>
     <row r="5" ht="36" customHeight="1">
-      <c r="A5" s="40" t="inlineStr">
-        <is>
-          <t>②付随ページ</t>
-        </is>
-      </c>
-      <c r="B5" s="41" t="inlineStr">
-        <is>
-          <t>資料請求・会社概要など、必要な付随ページが揃っている</t>
+      <c r="A5" s="37" t="inlineStr">
+        <is>
+          <t>問い合わせ導線</t>
+        </is>
+      </c>
+      <c r="B5" s="38" t="inlineStr">
+        <is>
+          <t>ボタンの行き先が実在し、問い合わせが届く先につながっている</t>
         </is>
       </c>
     </row>
     <row r="6" ht="36" customHeight="1">
-      <c r="A6" s="40" t="inlineStr">
-        <is>
-          <t>③問い合わせ導線</t>
-        </is>
-      </c>
-      <c r="B6" s="41" t="inlineStr">
-        <is>
-          <t>ボタンの行き先が実在し、問い合わせが届く先につながっている</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="36" customHeight="1">
-      <c r="A7" s="40" t="inlineStr">
-        <is>
-          <t>④本番公開</t>
-        </is>
-      </c>
-      <c r="B7" s="41" t="inlineStr">
-        <is>
-          <t>独自ドメインで公開され、J列に本番URLが入っている（自動判定）</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="39" t="inlineStr">
+      <c r="A6" s="37" t="inlineStr">
+        <is>
+          <t>本番公開</t>
+        </is>
+      </c>
+      <c r="B6" s="38" t="inlineStr">
+        <is>
+          <t>独自ドメインで公開され、G列に本番URLが入っている（自動判定）</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="36" t="inlineStr">
         <is>
           <t>記号</t>
         </is>
       </c>
     </row>
+    <row r="9" ht="36" customHeight="1">
+      <c r="A9" s="37" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+      <c r="B9" s="38" t="inlineStr">
+        <is>
+          <t>できている</t>
+        </is>
+      </c>
+    </row>
     <row r="10" ht="36" customHeight="1">
-      <c r="A10" s="40" t="inlineStr">
-        <is>
-          <t>○</t>
-        </is>
-      </c>
-      <c r="B10" s="41" t="inlineStr">
-        <is>
-          <t>できている</t>
+      <c r="A10" s="37" t="inlineStr">
+        <is>
+          <t>△</t>
+        </is>
+      </c>
+      <c r="B10" s="38" t="inlineStr">
+        <is>
+          <t>仮づけ。メーラーを開くだけ、または行き先が「#」のまま</t>
         </is>
       </c>
     </row>
     <row r="11" ht="36" customHeight="1">
-      <c r="A11" s="40" t="inlineStr">
-        <is>
-          <t>△</t>
-        </is>
-      </c>
-      <c r="B11" s="41" t="inlineStr">
-        <is>
-          <t>仮づけ。メーラーを開くだけ、または行き先が「#」のまま</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="36" customHeight="1">
-      <c r="A12" s="40" t="inlineStr">
+      <c r="A11" s="37" t="inlineStr">
         <is>
           <t>×</t>
         </is>
       </c>
-      <c r="B12" s="41" t="inlineStr">
+      <c r="B11" s="38" t="inlineStr">
         <is>
           <t>手つかず／ページが存在しない</t>
         </is>
       </c>
     </row>
-    <row r="14">
-      <c r="A14" s="39" t="inlineStr">
-        <is>
-          <t>状態（eラーニング・動画／広告シート）</t>
+    <row r="13">
+      <c r="A13" s="36" t="inlineStr">
+        <is>
+          <t>状態</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="36" customHeight="1">
+      <c r="A14" s="37" t="inlineStr">
+        <is>
+          <t>確認待ち</t>
+        </is>
+      </c>
+      <c r="B14" s="38" t="inlineStr">
+        <is>
+          <t>作業は終わり、誰かの確認を待っている</t>
         </is>
       </c>
     </row>
     <row r="15" ht="36" customHeight="1">
-      <c r="A15" s="40" t="inlineStr">
-        <is>
-          <t>確認待ち</t>
-        </is>
-      </c>
-      <c r="B15" s="41" t="inlineStr">
-        <is>
-          <t>作業は終わり、誰かの確認を待っている</t>
+      <c r="A15" s="37" t="inlineStr">
+        <is>
+          <t>進行中</t>
+        </is>
+      </c>
+      <c r="B15" s="38" t="inlineStr">
+        <is>
+          <t>いま手が動いている</t>
         </is>
       </c>
     </row>
     <row r="16" ht="36" customHeight="1">
-      <c r="A16" s="40" t="inlineStr">
-        <is>
-          <t>進行中</t>
-        </is>
-      </c>
-      <c r="B16" s="41" t="inlineStr">
-        <is>
-          <t>いま手が動いている</t>
+      <c r="A16" s="37" t="inlineStr">
+        <is>
+          <t>未着手</t>
+        </is>
+      </c>
+      <c r="B16" s="38" t="inlineStr">
+        <is>
+          <t>まだ始まっていない</t>
         </is>
       </c>
     </row>
     <row r="17" ht="36" customHeight="1">
-      <c r="A17" s="40" t="inlineStr">
-        <is>
-          <t>未着手</t>
-        </is>
-      </c>
-      <c r="B17" s="41" t="inlineStr">
-        <is>
-          <t>まだ始まっていない</t>
-        </is>
-      </c>
-    </row>
-    <row r="18" ht="36" customHeight="1">
-      <c r="A18" s="40" t="inlineStr">
-        <is>
-          <t>P2／P3</t>
-        </is>
-      </c>
-      <c r="B18" s="41" t="inlineStr">
-        <is>
-          <t>工程表の優先度。P3は「中核が回り出してから戻ってくる」もの</t>
-        </is>
-      </c>
-    </row>
-    <row r="19" ht="36" customHeight="1">
-      <c r="A19" s="40" t="inlineStr">
+      <c r="A17" s="37" t="inlineStr">
         <is>
           <t>赤い担当名</t>
         </is>
       </c>
-      <c r="B19" s="41" t="inlineStr">
+      <c r="B17" s="38" t="inlineStr">
         <is>
           <t>担当が「未定」の仕事。誰かを決めないと進みません</t>
         </is>
       </c>
     </row>
-    <row r="21">
-      <c r="A21" s="39" t="inlineStr">
-        <is>
-          <t>使い方</t>
+    <row r="19">
+      <c r="A19" s="36" t="inlineStr">
+        <is>
+          <t>クリックして選べるところ（水色のセル）</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="36" customHeight="1">
+      <c r="A20" s="37" t="inlineStr">
+        <is>
+          <t>案件</t>
+        </is>
+      </c>
+      <c r="B20" s="38" t="inlineStr">
+        <is>
+          <t>LPシートのA列。どの案件のLPかを選びます。</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="36" customHeight="1">
+      <c r="A21" s="37" t="inlineStr">
+        <is>
+          <t>担当</t>
+        </is>
+      </c>
+      <c r="B21" s="38" t="inlineStr">
+        <is>
+          <t>タスクシートのC列。一覧から選ぶか、直接書き換えます。</t>
         </is>
       </c>
     </row>
     <row r="22" ht="36" customHeight="1">
-      <c r="A22" s="40" t="inlineStr">
-        <is>
-          <t>案件・区分のセル（水色）</t>
-        </is>
-      </c>
-      <c r="B22" s="41" t="inlineStr">
-        <is>
-          <t>LPシートのA列（案件）とB列（状態）、他シートのA列（区分）とB列（優先）は、クリックすると▼が出て選べます。行の並べ替えをしなくても、絞り込みで見たい案件だけ出せます。</t>
+      <c r="A22" s="37" t="inlineStr">
+        <is>
+          <t>進捗</t>
+        </is>
+      </c>
+      <c r="B22" s="38" t="inlineStr">
+        <is>
+          <t>タスクシートのD列。0%〜100%を5%きざみで選べます。選ぶとセルの中のバーが伸び縮みします。</t>
         </is>
       </c>
     </row>
     <row r="23" ht="36" customHeight="1">
-      <c r="A23" s="40" t="inlineStr">
-        <is>
-          <t>進捗のセル（水色）</t>
-        </is>
-      </c>
-      <c r="B23" s="41" t="inlineStr">
-        <is>
-          <t>クリックすると右に▼が出ます。0%〜100%を5%きざみで選べます（直接入力も可）。選ぶとセルの中のバーがその長さに変わります。</t>
+      <c r="A23" s="37" t="inlineStr">
+        <is>
+          <t>状態</t>
+        </is>
+      </c>
+      <c r="B23" s="38" t="inlineStr">
+        <is>
+          <t>タスクシートのE列。未着手／進行中／確認待ち。</t>
         </is>
       </c>
     </row>
     <row r="24" ht="36" customHeight="1">
-      <c r="A24" s="40" t="inlineStr">
-        <is>
-          <t>状態のセル（水色）</t>
-        </is>
-      </c>
-      <c r="B24" s="41" t="inlineStr">
-        <is>
-          <t>クリックして 未着手／進行中／確認待ち を選びます。</t>
+      <c r="A24" s="37" t="inlineStr">
+        <is>
+          <t>LPの○△×</t>
+        </is>
+      </c>
+      <c r="B24" s="38" t="inlineStr">
+        <is>
+          <t>LPシートのD・E列。本番公開（F列）はG列のURL有無から自動で決まります。</t>
         </is>
       </c>
     </row>
     <row r="25" ht="36" customHeight="1">
-      <c r="A25" s="40" t="inlineStr">
-        <is>
-          <t>LPの○△×（水色）</t>
-        </is>
-      </c>
-      <c r="B25" s="41" t="inlineStr">
-        <is>
-          <t>E〜G列。クリックして選び直せます。H列の④本番公開はJ列のURL有無から自動で決まります。</t>
+      <c r="A25" s="37" t="inlineStr">
+        <is>
+          <t>黄色の記入欄</t>
+        </is>
+      </c>
+      <c r="B25" s="38" t="inlineStr">
+        <is>
+          <t>公開したURL・動画URL・広告の入稿先を貼ります。</t>
         </is>
       </c>
     </row>
     <row r="26" ht="36" customHeight="1">
-      <c r="A26" s="40" t="inlineStr">
+      <c r="A26" s="37" t="inlineStr">
         <is>
           <t>列見出しの▼</t>
         </is>
       </c>
-      <c r="B26" s="41" t="inlineStr">
-        <is>
-          <t>各シートの見出し行にオートフィルタが付いています。▼から値を選ぶと、その行だけ表示されます。複数の列を組み合わせられます。</t>
+      <c r="B26" s="38" t="inlineStr">
+        <is>
+          <t>オートフィルタです。値を選ぶとその行だけ表示されます。複数の列を組み合わせられます。</t>
         </is>
       </c>
     </row>
     <row r="27" ht="36" customHeight="1">
-      <c r="A27" s="40" t="inlineStr">
-        <is>
-          <t>黄色の記入欄</t>
-        </is>
-      </c>
-      <c r="B27" s="41" t="inlineStr">
-        <is>
-          <t>公開したURL・動画URL・広告の入稿先を貼ります。</t>
-        </is>
-      </c>
-    </row>
-    <row r="28" ht="36" customHeight="1">
-      <c r="A28" s="40" t="inlineStr">
-        <is>
-          <t>自動で動く数字</t>
-        </is>
-      </c>
-      <c r="B28" s="41" t="inlineStr">
-        <is>
-          <t>LPシートは④と到達度、各シートの最下段の平均・件数が数式です。手で書き換えないでください。</t>
-        </is>
-      </c>
-    </row>
-    <row r="29" ht="36" customHeight="1">
-      <c r="A29" s="40" t="inlineStr">
+      <c r="A27" s="37" t="inlineStr">
         <is>
           <t>選択肢を増やしたいとき</t>
         </is>
       </c>
-      <c r="B29" s="41" t="inlineStr">
-        <is>
-          <t>非表示シート「選択肢」に一覧が入っています。表示して値を足し、入力規則の参照範囲を広げれば選べるようになります。</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" s="39" t="inlineStr">
+      <c r="B27" s="38" t="inlineStr">
+        <is>
+          <t>非表示シート「選択肢」に一覧があります。値を足し、入力規則の参照範囲を広げれば選べるようになります。</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="36" t="inlineStr">
         <is>
           <t>出典</t>
         </is>
       </c>
     </row>
+    <row r="30" ht="36" customHeight="1">
+      <c r="A30" s="37" t="inlineStr">
+        <is>
+          <t>LPシート</t>
+        </is>
+      </c>
+      <c r="B30" s="38" t="inlineStr">
+        <is>
+          <t>公開済みアーティファクト43件のうちLPに該当する22ページ（本編11＋付随11）を、1ページずつHTMLを読んで確認。ボタンの行き先・フォームの送信方法・付随ページの有無は実物ベースです。</t>
+        </is>
+      </c>
+    </row>
+    <row r="31" ht="36" customHeight="1">
+      <c r="A31" s="37" t="inlineStr">
+        <is>
+          <t>進捗％と担当</t>
+        </is>
+      </c>
+      <c r="B31" s="38" t="inlineStr">
+        <is>
+          <t>社内の「REALIZE OS 制作MASTER」(2026-09-03) と「仕事の棚卸し」(2026-09-02) の数値をそのまま引いています。</t>
+        </is>
+      </c>
+    </row>
     <row r="32" ht="36" customHeight="1">
-      <c r="A32" s="40" t="inlineStr">
-        <is>
-          <t>LPシート</t>
-        </is>
-      </c>
-      <c r="B32" s="41" t="inlineStr">
-        <is>
-          <t>公開済みアーティファクト43件のうちLPに該当する22ページ（本編11＋付随11）を、1ページずつHTMLを読んで確認。ボタンの行き先・フォームの送信方法・付随ページの有無は実物ベースです。</t>
+      <c r="A32" s="37" t="inlineStr">
+        <is>
+          <t>担当の食い違い</t>
+        </is>
+      </c>
+      <c r="B32" s="38" t="inlineStr">
+        <is>
+          <t>広告運用の担当は2資料で記載が違います（制作MASTER＝大熊・片山／棚卸し＝池之上・片山）。広告制作は大熊・片山、広告運用は池之上・片山としています。</t>
         </is>
       </c>
     </row>
     <row r="33" ht="36" customHeight="1">
-      <c r="A33" s="40" t="inlineStr">
-        <is>
-          <t>進捗％と担当</t>
-        </is>
-      </c>
-      <c r="B33" s="41" t="inlineStr">
-        <is>
-          <t>社内の「REALIZE OS 制作MASTER」(2026-09-03) と「仕事の棚卸し」(2026-09-02) の数値をそのまま引いています。</t>
+      <c r="A33" s="37" t="inlineStr">
+        <is>
+          <t>未確認</t>
+        </is>
+      </c>
+      <c r="B33" s="38" t="inlineStr">
+        <is>
+          <t>LP付随ページ4本（RC星空案の会社概要、RCアイス案の資料請求、LMP星空案の資料請求と会社概要）は、親LPからのリンクで存在を確認しただけで中身は開いていません。</t>
         </is>
       </c>
     </row>
     <row r="34" ht="36" customHeight="1">
-      <c r="A34" s="40" t="inlineStr">
-        <is>
-          <t>担当の食い違い</t>
-        </is>
-      </c>
-      <c r="B34" s="41" t="inlineStr">
-        <is>
-          <t>広告運用の担当は2資料で記載が違います（制作MASTER＝大熊・片山／棚卸し＝池之上・片山）。広告制作は大熊・片山、広告運用は池之上・片山としています。</t>
-        </is>
-      </c>
-    </row>
-    <row r="35" ht="36" customHeight="1">
-      <c r="A35" s="40" t="inlineStr">
-        <is>
-          <t>未確認</t>
-        </is>
-      </c>
-      <c r="B35" s="41" t="inlineStr">
-        <is>
-          <t>LP付随ページ4本（RC星空案の会社概要、RCアイス案の資料請求、LMP星空案の資料請求と会社概要）は、親LPからのリンクで存在を確認しただけで中身は開いていません。</t>
-        </is>
-      </c>
-    </row>
-    <row r="36" ht="36" customHeight="1">
-      <c r="A36" s="40" t="inlineStr">
+      <c r="A34" s="37" t="inlineStr">
         <is>
           <t>調査日</t>
         </is>
       </c>
-      <c r="B36" s="41" t="inlineStr">
+      <c r="B34" s="38" t="inlineStr">
         <is>
           <t>2026-09-03</t>
         </is>

--- a/制作進捗ボード.xlsx
+++ b/制作進捗ボード.xlsx
@@ -14,7 +14,7 @@
     <sheet name="凡例と出典" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'LP'!$A$5:$M$16</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'LP'!$A$5:$I$16</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'eラーニング・動画'!$A$5:$G$21</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'広告'!$A$5:$G$10</definedName>
   </definedNames>
@@ -69,12 +69,6 @@
     </font>
     <font>
       <name val="Meiryo"/>
-      <color rgb="001F4E6B"/>
-      <sz val="9"/>
-      <u val="single"/>
-    </font>
-    <font>
-      <name val="Meiryo"/>
       <color rgb="001B2330"/>
       <sz val="9"/>
     </font>
@@ -118,6 +112,12 @@
       <b val="1"/>
       <color rgb="001F4E6B"/>
       <sz val="11"/>
+    </font>
+    <font>
+      <name val="Meiryo"/>
+      <color rgb="001F4E6B"/>
+      <sz val="9"/>
+      <u val="single"/>
     </font>
     <font>
       <name val="Meiryo"/>
@@ -191,7 +191,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="39">
+  <cellXfs count="33">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -199,88 +199,70 @@
     <xf numFmtId="0" fontId="6" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="164" fontId="11" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="164" fontId="10" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="9" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="9" fontId="8" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="9" fontId="7" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="11" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="9" fontId="10" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="17" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -720,22 +702,18 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M17"/>
+  <dimension ref="A1:I17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
-    <col width="30" customWidth="1" min="2" max="2"/>
-    <col width="32" customWidth="1" min="3" max="3"/>
+    <col width="32" customWidth="1" min="2" max="2"/>
+    <col width="34" customWidth="1" min="3" max="3"/>
     <col width="14" customWidth="1" min="4" max="4"/>
     <col width="15" customWidth="1" min="5" max="5"/>
     <col width="11" customWidth="1" min="6" max="6"/>
-    <col width="34" customWidth="1" min="7" max="7"/>
-    <col width="52" customWidth="1" min="8" max="8"/>
-    <col width="26" customWidth="1" min="9" max="9"/>
-    <col width="26" customWidth="1" min="10" max="10"/>
-    <col width="26" customWidth="1" min="11" max="11"/>
-    <col width="10" customWidth="1" min="12" max="12"/>
-    <col width="11" customWidth="1" min="13" max="13"/>
+    <col width="36" customWidth="1" min="7" max="7"/>
+    <col width="58" customWidth="1" min="8" max="8"/>
+    <col width="11" customWidth="1" min="9" max="9"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -802,26 +780,6 @@
       </c>
       <c r="I5" s="4" t="inlineStr">
         <is>
-          <t>資料請求ページ</t>
-        </is>
-      </c>
-      <c r="J5" s="4" t="inlineStr">
-        <is>
-          <t>会社概要ページ</t>
-        </is>
-      </c>
-      <c r="K5" s="4" t="inlineStr">
-        <is>
-          <t>LPプレビュー</t>
-        </is>
-      </c>
-      <c r="L5" s="4" t="inlineStr">
-        <is>
-          <t>ID</t>
-        </is>
-      </c>
-      <c r="M5" s="4" t="inlineStr">
-        <is>
           <t>更新日</t>
         </is>
       </c>
@@ -862,27 +820,7 @@
           <t>送信ボタンがメーラーを開くだけ。受付フォームの実装が必要／会社概要ページが未作成／本番ドメインへの公開</t>
         </is>
       </c>
-      <c r="I6" s="10" t="inlineStr">
-        <is>
-          <t>資料請求を開く</t>
-        </is>
-      </c>
-      <c r="J6" s="11" t="inlineStr">
-        <is>
-          <t>未作成</t>
-        </is>
-      </c>
-      <c r="K6" s="10" t="inlineStr">
-        <is>
-          <t>LPを開く</t>
-        </is>
-      </c>
-      <c r="L6" s="12" t="inlineStr">
-        <is>
-          <t>08b479a1</t>
-        </is>
-      </c>
-      <c r="M6" s="8" t="inlineStr">
+      <c r="I6" s="8" t="inlineStr">
         <is>
           <t>2026-09-03</t>
         </is>
@@ -894,12 +832,12 @@
           <t>REALIZE CLUB（法人向け）</t>
         </is>
       </c>
-      <c r="B7" s="13" t="inlineStr">
+      <c r="B7" s="10" t="inlineStr">
         <is>
           <t>会社が社員の人生を支える時代へ</t>
         </is>
       </c>
-      <c r="C7" s="13" t="inlineStr">
+      <c r="C7" s="10" t="inlineStr">
         <is>
           <t>星空タウン／クリーム × 濃紺のイラスト</t>
         </is>
@@ -914,37 +852,17 @@
           <t>△</t>
         </is>
       </c>
-      <c r="F7" s="14">
+      <c r="F7" s="11">
         <f>IF(G7="","×","○")</f>
         <v/>
       </c>
       <c r="G7" s="9" t="n"/>
-      <c r="H7" s="13" t="inlineStr">
+      <c r="H7" s="10" t="inlineStr">
         <is>
           <t>3ページ揃っている唯一のRC案。採用するかの判断／送信はメーラー起動のみ</t>
         </is>
       </c>
-      <c r="I7" s="15" t="inlineStr">
-        <is>
-          <t>資料請求を開く</t>
-        </is>
-      </c>
-      <c r="J7" s="15" t="inlineStr">
-        <is>
-          <t>会社概要を開く</t>
-        </is>
-      </c>
-      <c r="K7" s="15" t="inlineStr">
-        <is>
-          <t>LPを開く</t>
-        </is>
-      </c>
-      <c r="L7" s="16" t="inlineStr">
-        <is>
-          <t>7355f424</t>
-        </is>
-      </c>
-      <c r="M7" s="14" t="inlineStr">
+      <c r="I7" s="11" t="inlineStr">
         <is>
           <t>2026-08-31</t>
         </is>
@@ -986,27 +904,7 @@
           <t>kaisha.html ほかへの相対リンクが残り、単体では飛べない／会社概要ページの作成</t>
         </is>
       </c>
-      <c r="I8" s="11" t="inlineStr">
-        <is>
-          <t>（同ファイル内）</t>
-        </is>
-      </c>
-      <c r="J8" s="11" t="inlineStr">
-        <is>
-          <t>未作成</t>
-        </is>
-      </c>
-      <c r="K8" s="10" t="inlineStr">
-        <is>
-          <t>LPを開く</t>
-        </is>
-      </c>
-      <c r="L8" s="12" t="inlineStr">
-        <is>
-          <t>ded9a489</t>
-        </is>
-      </c>
-      <c r="M8" s="8" t="inlineStr">
+      <c r="I8" s="8" t="inlineStr">
         <is>
           <t>2026-08-31</t>
         </is>
@@ -1018,12 +916,12 @@
           <t>REALIZE CLUB（法人向け）</t>
         </is>
       </c>
-      <c r="B9" s="13" t="inlineStr">
+      <c r="B9" s="10" t="inlineStr">
         <is>
           <t>その安心、今がお得。</t>
         </is>
       </c>
-      <c r="C9" s="13" t="inlineStr">
+      <c r="C9" s="10" t="inlineStr">
         <is>
           <t>スーパーの特売ポップ／白地に赤と黄</t>
         </is>
@@ -1038,37 +936,17 @@
           <t>×</t>
         </is>
       </c>
-      <c r="F9" s="14">
+      <c r="F9" s="11">
         <f>IF(G9="","×","○")</f>
         <v/>
       </c>
       <c r="G9" s="9" t="n"/>
-      <c r="H9" s="13" t="inlineStr">
+      <c r="H9" s="10" t="inlineStr">
         <is>
           <t>リンクがすべてページ内アンカー。外部への導線が1本もない／会社概要ページ、送信先の設定</t>
         </is>
       </c>
-      <c r="I9" s="17" t="inlineStr">
-        <is>
-          <t>（同ページ内フォーム）</t>
-        </is>
-      </c>
-      <c r="J9" s="17" t="inlineStr">
-        <is>
-          <t>未作成</t>
-        </is>
-      </c>
-      <c r="K9" s="15" t="inlineStr">
-        <is>
-          <t>LPを開く</t>
-        </is>
-      </c>
-      <c r="L9" s="16" t="inlineStr">
-        <is>
-          <t>4ce48691</t>
-        </is>
-      </c>
-      <c r="M9" s="14" t="inlineStr">
+      <c r="I9" s="11" t="inlineStr">
         <is>
           <t>2026-08-31</t>
         </is>
@@ -1110,27 +988,7 @@
           <t>会社概要ページが未作成／送信はメーラー起動のみ</t>
         </is>
       </c>
-      <c r="I10" s="10" t="inlineStr">
-        <is>
-          <t>資料請求を開く</t>
-        </is>
-      </c>
-      <c r="J10" s="11" t="inlineStr">
-        <is>
-          <t>未作成</t>
-        </is>
-      </c>
-      <c r="K10" s="10" t="inlineStr">
-        <is>
-          <t>LPを開く</t>
-        </is>
-      </c>
-      <c r="L10" s="12" t="inlineStr">
-        <is>
-          <t>b0f16478</t>
-        </is>
-      </c>
-      <c r="M10" s="8" t="inlineStr">
+      <c r="I10" s="8" t="inlineStr">
         <is>
           <t>2026-08-28</t>
         </is>
@@ -1142,12 +1000,12 @@
           <t>LIFE MAKE PARTNERS（加盟店募集）</t>
         </is>
       </c>
-      <c r="B11" s="13" t="inlineStr">
+      <c r="B11" s="10" t="inlineStr">
         <is>
           <t>家より先に、人生の話を。</t>
         </is>
       </c>
-      <c r="C11" s="13" t="inlineStr">
+      <c r="C11" s="10" t="inlineStr">
         <is>
           <t>韓国料理店の看板／木の壁 × 生成りの横断幕</t>
         </is>
@@ -1162,37 +1020,17 @@
           <t>○</t>
         </is>
       </c>
-      <c r="F11" s="14">
+      <c r="F11" s="11">
         <f>IF(G11="","×","○")</f>
         <v/>
       </c>
       <c r="G11" s="9" t="n"/>
-      <c r="H11" s="13" t="inlineStr">
+      <c r="H11" s="10" t="inlineStr">
         <is>
           <t>本番ドメインへの公開だけが残り。問い合わせはLINE公式（lin.ee/WHYApuM）に集約済み</t>
         </is>
       </c>
-      <c r="I11" s="15" t="inlineStr">
-        <is>
-          <t>資料請求を開く</t>
-        </is>
-      </c>
-      <c r="J11" s="15" t="inlineStr">
-        <is>
-          <t>会社概要を開く</t>
-        </is>
-      </c>
-      <c r="K11" s="15" t="inlineStr">
-        <is>
-          <t>LPを開く</t>
-        </is>
-      </c>
-      <c r="L11" s="16" t="inlineStr">
-        <is>
-          <t>7f212d2f</t>
-        </is>
-      </c>
-      <c r="M11" s="14" t="inlineStr">
+      <c r="I11" s="11" t="inlineStr">
         <is>
           <t>2026-09-03</t>
         </is>
@@ -1234,27 +1072,7 @@
           <t>kaisha-katsu.html ほかへの相対リンクが残り飛べない／行き先が「#」のままのボタンが2つ</t>
         </is>
       </c>
-      <c r="I12" s="11" t="inlineStr">
-        <is>
-          <t>（同ページ内フォーム）</t>
-        </is>
-      </c>
-      <c r="J12" s="11" t="inlineStr">
-        <is>
-          <t>未作成</t>
-        </is>
-      </c>
-      <c r="K12" s="10" t="inlineStr">
-        <is>
-          <t>LPを開く</t>
-        </is>
-      </c>
-      <c r="L12" s="12" t="inlineStr">
-        <is>
-          <t>db82fc95</t>
-        </is>
-      </c>
-      <c r="M12" s="8" t="inlineStr">
+      <c r="I12" s="8" t="inlineStr">
         <is>
           <t>2026-08-28</t>
         </is>
@@ -1266,12 +1084,12 @@
           <t>LIFE MAKE PARTNERS（加盟店募集）</t>
         </is>
       </c>
-      <c r="B13" s="13" t="inlineStr">
+      <c r="B13" s="10" t="inlineStr">
         <is>
           <t>加盟資格は、人生への愛。ただそれだけ。</t>
         </is>
       </c>
-      <c r="C13" s="13" t="inlineStr">
+      <c r="C13" s="10" t="inlineStr">
         <is>
           <t>星空タウン／RC星空案と同じ世界観</t>
         </is>
@@ -1286,37 +1104,17 @@
           <t>△</t>
         </is>
       </c>
-      <c r="F13" s="14">
+      <c r="F13" s="11">
         <f>IF(G13="","×","○")</f>
         <v/>
       </c>
       <c r="G13" s="9" t="n"/>
-      <c r="H13" s="13" t="inlineStr">
+      <c r="H13" s="10" t="inlineStr">
         <is>
           <t>行き先が「#」のままのボタンが2つ／統廃合の判断</t>
         </is>
       </c>
-      <c r="I13" s="15" t="inlineStr">
-        <is>
-          <t>資料請求を開く</t>
-        </is>
-      </c>
-      <c r="J13" s="15" t="inlineStr">
-        <is>
-          <t>会社概要を開く</t>
-        </is>
-      </c>
-      <c r="K13" s="15" t="inlineStr">
-        <is>
-          <t>LPを開く</t>
-        </is>
-      </c>
-      <c r="L13" s="16" t="inlineStr">
-        <is>
-          <t>65b43069</t>
-        </is>
-      </c>
-      <c r="M13" s="14" t="inlineStr">
+      <c r="I13" s="11" t="inlineStr">
         <is>
           <t>2026-08-24</t>
         </is>
@@ -1358,27 +1156,7 @@
           <t>行き先が「#」のままのリンクが2つ残っている／本番ドメインへの公開</t>
         </is>
       </c>
-      <c r="I14" s="10" t="inlineStr">
-        <is>
-          <t>資料請求を開く</t>
-        </is>
-      </c>
-      <c r="J14" s="10" t="inlineStr">
-        <is>
-          <t>会社概要を開く</t>
-        </is>
-      </c>
-      <c r="K14" s="10" t="inlineStr">
-        <is>
-          <t>LPを開く</t>
-        </is>
-      </c>
-      <c r="L14" s="12" t="inlineStr">
-        <is>
-          <t>1a259364</t>
-        </is>
-      </c>
-      <c r="M14" s="8" t="inlineStr">
+      <c r="I14" s="8" t="inlineStr">
         <is>
           <t>2026-09-03</t>
         </is>
@@ -1390,12 +1168,12 @@
           <t>まちの相談窓口</t>
         </is>
       </c>
-      <c r="B15" s="13" t="inlineStr">
+      <c r="B15" s="10" t="inlineStr">
         <is>
           <t>まちの相談窓口（フォーム版）</t>
         </is>
       </c>
-      <c r="C15" s="13" t="inlineStr">
+      <c r="C15" s="10" t="inlineStr">
         <is>
           <t>銭湯ポスター／申込フォーム内蔵</t>
         </is>
@@ -1410,37 +1188,17 @@
           <t>△</t>
         </is>
       </c>
-      <c r="F15" s="14">
+      <c r="F15" s="11">
         <f>IF(G15="","×","○")</f>
         <v/>
       </c>
       <c r="G15" s="9" t="n"/>
-      <c r="H15" s="13" t="inlineStr">
+      <c r="H15" s="10" t="inlineStr">
         <is>
           <t>LINE誘導版に置き換わっている。残すか消すかの判断</t>
         </is>
       </c>
-      <c r="I15" s="15" t="inlineStr">
-        <is>
-          <t>資料請求を開く</t>
-        </is>
-      </c>
-      <c r="J15" s="15" t="inlineStr">
-        <is>
-          <t>会社概要を開く</t>
-        </is>
-      </c>
-      <c r="K15" s="15" t="inlineStr">
-        <is>
-          <t>LPを開く</t>
-        </is>
-      </c>
-      <c r="L15" s="16" t="inlineStr">
-        <is>
-          <t>39f0d878</t>
-        </is>
-      </c>
-      <c r="M15" s="14" t="inlineStr">
+      <c r="I15" s="11" t="inlineStr">
         <is>
           <t>2026-08-20</t>
         </is>
@@ -1482,57 +1240,37 @@
           <t>ページのタイトルタグが空。共有すると名前なしで出る／資料請求・会社概要ページ、送信先の設定</t>
         </is>
       </c>
-      <c r="I16" s="11" t="inlineStr">
-        <is>
-          <t>（同ページ内フォーム）</t>
-        </is>
-      </c>
-      <c r="J16" s="11" t="inlineStr">
-        <is>
-          <t>未作成</t>
-        </is>
-      </c>
-      <c r="K16" s="10" t="inlineStr">
-        <is>
-          <t>LPを開く</t>
-        </is>
-      </c>
-      <c r="L16" s="12" t="inlineStr">
-        <is>
-          <t>d5160792</t>
-        </is>
-      </c>
-      <c r="M16" s="8" t="inlineStr">
+      <c r="I16" s="8" t="inlineStr">
         <is>
           <t>2026-08-19</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="C17" s="18" t="inlineStr">
+      <c r="C17" s="12" t="inlineStr">
         <is>
           <t>○の数</t>
         </is>
       </c>
-      <c r="D17" s="19">
+      <c r="D17" s="13">
         <f>COUNTIF(D6:D16,"○")</f>
         <v/>
       </c>
-      <c r="E17" s="19">
+      <c r="E17" s="13">
         <f>COUNTIF(E6:E16,"○")</f>
         <v/>
       </c>
-      <c r="F17" s="19">
+      <c r="F17" s="13">
         <f>COUNTIF(F6:F16,"○")</f>
         <v/>
       </c>
-      <c r="G17" s="20">
+      <c r="G17" s="14">
         <f>COUNTA(G6:G16)&amp;" 本 公開ずみ"</f>
         <v/>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A5:M16"/>
+  <autoFilter ref="A5:I16"/>
   <conditionalFormatting sqref="D6:F16">
     <cfRule type="cellIs" priority="1" operator="equal" dxfId="0">
       <formula>"×"</formula>
@@ -1552,31 +1290,6 @@
       <formula1>"○,△,×"</formula1>
     </dataValidation>
   </dataValidations>
-  <hyperlinks>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I6" r:id="rId1"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K6" r:id="rId2"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I7" r:id="rId3"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J7" r:id="rId4"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K7" r:id="rId5"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K8" r:id="rId6"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K9" r:id="rId7"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I10" r:id="rId8"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K10" r:id="rId9"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I11" r:id="rId10"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J11" r:id="rId11"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K11" r:id="rId12"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K12" r:id="rId13"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I13" r:id="rId14"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J13" r:id="rId15"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K13" r:id="rId16"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I14" r:id="rId17"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J14" r:id="rId18"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K14" r:id="rId19"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I15" r:id="rId20"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J15" r:id="rId21"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K15" r:id="rId22"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K16" r:id="rId23"/>
-  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="anysvml"/>
 </worksheet>
@@ -1597,244 +1310,244 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="21" t="inlineStr">
+      <c r="A1" s="15" t="inlineStr">
         <is>
           <t>進捗</t>
         </is>
       </c>
-      <c r="B1" s="21" t="inlineStr">
+      <c r="B1" s="15" t="inlineStr">
         <is>
           <t>案件</t>
         </is>
       </c>
-      <c r="C1" s="21" t="inlineStr">
+      <c r="C1" s="15" t="inlineStr">
         <is>
           <t>状態</t>
         </is>
       </c>
-      <c r="D1" s="21" t="inlineStr">
+      <c r="D1" s="15" t="inlineStr">
         <is>
           <t>担当</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="22" t="n">
+      <c r="A2" s="16" t="n">
         <v>0</v>
       </c>
-      <c r="B2" s="23" t="inlineStr">
+      <c r="B2" s="17" t="inlineStr">
         <is>
           <t>REALIZE CLUB（法人向け）</t>
         </is>
       </c>
-      <c r="C2" s="23" t="inlineStr">
+      <c r="C2" s="17" t="inlineStr">
         <is>
           <t>未着手</t>
         </is>
       </c>
-      <c r="D2" s="23" t="inlineStr">
+      <c r="D2" s="17" t="inlineStr">
         <is>
           <t>未定</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="22" t="n">
+      <c r="A3" s="16" t="n">
         <v>0.05</v>
       </c>
-      <c r="B3" s="23" t="inlineStr">
+      <c r="B3" s="17" t="inlineStr">
         <is>
           <t>LIFE MAKE PARTNERS（加盟店募集）</t>
         </is>
       </c>
-      <c r="C3" s="23" t="inlineStr">
+      <c r="C3" s="17" t="inlineStr">
         <is>
           <t>進行中</t>
         </is>
       </c>
-      <c r="D3" s="23" t="inlineStr">
+      <c r="D3" s="17" t="inlineStr">
         <is>
           <t>社長</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="22" t="n">
+      <c r="A4" s="16" t="n">
         <v>0.1</v>
       </c>
-      <c r="B4" s="23" t="inlineStr">
+      <c r="B4" s="17" t="inlineStr">
         <is>
           <t>まちの相談窓口</t>
         </is>
       </c>
-      <c r="C4" s="23" t="inlineStr">
+      <c r="C4" s="17" t="inlineStr">
         <is>
           <t>確認待ち</t>
         </is>
       </c>
-      <c r="D4" s="23" t="inlineStr">
+      <c r="D4" s="17" t="inlineStr">
         <is>
           <t>白石</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="22" t="n">
+      <c r="A5" s="16" t="n">
         <v>0.15</v>
       </c>
-      <c r="B5" s="23" t="inlineStr">
+      <c r="B5" s="17" t="inlineStr">
         <is>
           <t>不動産FC加盟</t>
         </is>
       </c>
-      <c r="D5" s="23" t="inlineStr">
+      <c r="D5" s="17" t="inlineStr">
         <is>
           <t>池之上</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="22" t="n">
+      <c r="A6" s="16" t="n">
         <v>0.2</v>
       </c>
-      <c r="D6" s="23" t="inlineStr">
+      <c r="D6" s="17" t="inlineStr">
         <is>
           <t>大熊</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="22" t="n">
+      <c r="A7" s="16" t="n">
         <v>0.25</v>
       </c>
-      <c r="D7" s="23" t="inlineStr">
+      <c r="D7" s="17" t="inlineStr">
         <is>
           <t>片山</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="22" t="n">
+      <c r="A8" s="16" t="n">
         <v>0.3</v>
       </c>
-      <c r="D8" s="23" t="inlineStr">
+      <c r="D8" s="17" t="inlineStr">
         <is>
           <t>寺井</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="22" t="n">
+      <c r="A9" s="16" t="n">
         <v>0.35</v>
       </c>
-      <c r="D9" s="23" t="inlineStr">
+      <c r="D9" s="17" t="inlineStr">
         <is>
           <t>全員</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="22" t="n">
+      <c r="A10" s="16" t="n">
         <v>0.4</v>
       </c>
-      <c r="D10" s="23" t="inlineStr">
+      <c r="D10" s="17" t="inlineStr">
         <is>
           <t>大熊・片山</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="22" t="n">
+      <c r="A11" s="16" t="n">
         <v>0.45</v>
       </c>
-      <c r="D11" s="23" t="inlineStr">
+      <c r="D11" s="17" t="inlineStr">
         <is>
           <t>池之上・片山</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="22" t="n">
+      <c r="A12" s="16" t="n">
         <v>0.5</v>
       </c>
-      <c r="D12" s="23" t="inlineStr">
+      <c r="D12" s="17" t="inlineStr">
         <is>
           <t>大熊・白石</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="22" t="n">
+      <c r="A13" s="16" t="n">
         <v>0.55</v>
       </c>
-      <c r="D13" s="23" t="inlineStr">
+      <c r="D13" s="17" t="inlineStr">
         <is>
           <t>全員・池之上</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="22" t="n">
+      <c r="A14" s="16" t="n">
         <v>0.6000000000000001</v>
       </c>
-      <c r="D14" s="23" t="inlineStr">
+      <c r="D14" s="17" t="inlineStr">
         <is>
           <t>社長・白石・片山</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="22" t="n">
+      <c r="A15" s="16" t="n">
         <v>0.65</v>
       </c>
-      <c r="D15" s="23" t="inlineStr">
+      <c r="D15" s="17" t="inlineStr">
         <is>
           <t>白石・池之上・大熊</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="22" t="n">
+      <c r="A16" s="16" t="n">
         <v>0.7000000000000001</v>
       </c>
-      <c r="D16" s="23" t="inlineStr">
+      <c r="D16" s="17" t="inlineStr">
         <is>
           <t>白石・片山</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="22" t="n">
+      <c r="A17" s="16" t="n">
         <v>0.75</v>
       </c>
-      <c r="D17" s="23" t="inlineStr">
+      <c r="D17" s="17" t="inlineStr">
         <is>
           <t>社長・寺井・池之上・弁護士</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="22" t="n">
+      <c r="A18" s="16" t="n">
         <v>0.8</v>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="22" t="n">
+      <c r="A19" s="16" t="n">
         <v>0.8500000000000001</v>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="22" t="n">
+      <c r="A20" s="16" t="n">
         <v>0.9</v>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="22" t="n">
+      <c r="A21" s="16" t="n">
         <v>0.9500000000000001</v>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="22" t="n">
+      <c r="A22" s="16" t="n">
         <v>1</v>
       </c>
     </row>
@@ -1930,20 +1643,20 @@
           <t>LMP事業 · Web・ツール・システム</t>
         </is>
       </c>
-      <c r="C6" s="24" t="inlineStr">
+      <c r="C6" s="18" t="inlineStr">
         <is>
           <t>社長・白石・片山</t>
         </is>
       </c>
-      <c r="D6" s="25" t="n">
+      <c r="D6" s="19" t="n">
         <v>0.5</v>
       </c>
-      <c r="E6" s="26" t="inlineStr">
+      <c r="E6" s="20" t="inlineStr">
         <is>
           <t>進行中</t>
         </is>
       </c>
-      <c r="F6" s="27" t="n"/>
+      <c r="F6" s="21" t="n"/>
       <c r="G6" s="6" t="inlineStr">
         <is>
           <t>加盟店が学ぶ画面そのもの</t>
@@ -1961,20 +1674,20 @@
           <t>LMP事業 · Web・ツール・システム</t>
         </is>
       </c>
-      <c r="C7" s="28" t="inlineStr">
+      <c r="C7" s="22" t="inlineStr">
         <is>
           <t>未定</t>
         </is>
       </c>
-      <c r="D7" s="25" t="n">
+      <c r="D7" s="19" t="n">
         <v>0.2</v>
       </c>
-      <c r="E7" s="26" t="inlineStr">
+      <c r="E7" s="20" t="inlineStr">
         <is>
           <t>進行中</t>
         </is>
       </c>
-      <c r="F7" s="27" t="n"/>
+      <c r="F7" s="21" t="n"/>
       <c r="G7" s="6" t="inlineStr">
         <is>
           <t>教材の中で流す動画。担当が決まっていない</t>
@@ -1992,20 +1705,20 @@
           <t>RC事業 · Web・ツール・システム</t>
         </is>
       </c>
-      <c r="C8" s="24" t="inlineStr">
+      <c r="C8" s="18" t="inlineStr">
         <is>
           <t>白石</t>
         </is>
       </c>
-      <c r="D8" s="25" t="n">
+      <c r="D8" s="19" t="n">
         <v>0.8</v>
       </c>
-      <c r="E8" s="26" t="inlineStr">
+      <c r="E8" s="20" t="inlineStr">
         <is>
           <t>進行中</t>
         </is>
       </c>
-      <c r="F8" s="27" t="n"/>
+      <c r="F8" s="21" t="n"/>
       <c r="G8" s="6" t="inlineStr">
         <is>
           <t>学ぶ前に現在地をはかる</t>
@@ -2023,20 +1736,20 @@
           <t>RC事業 · 動画・コンテンツ</t>
         </is>
       </c>
-      <c r="C9" s="24" t="inlineStr">
+      <c r="C9" s="18" t="inlineStr">
         <is>
           <t>白石</t>
         </is>
       </c>
-      <c r="D9" s="25" t="n">
+      <c r="D9" s="19" t="n">
         <v>0.6</v>
       </c>
-      <c r="E9" s="26" t="inlineStr">
+      <c r="E9" s="20" t="inlineStr">
         <is>
           <t>進行中</t>
         </is>
       </c>
-      <c r="F9" s="27" t="n"/>
+      <c r="F9" s="21" t="n"/>
       <c r="G9" s="6" t="inlineStr">
         <is>
           <t>教材のもとになる原稿</t>
@@ -2054,20 +1767,20 @@
           <t>LMP事業 · 営業・資料</t>
         </is>
       </c>
-      <c r="C10" s="28" t="inlineStr">
+      <c r="C10" s="22" t="inlineStr">
         <is>
           <t>未定</t>
         </is>
       </c>
-      <c r="D10" s="25" t="n">
+      <c r="D10" s="19" t="n">
         <v>0</v>
       </c>
-      <c r="E10" s="29" t="inlineStr">
+      <c r="E10" s="23" t="inlineStr">
         <is>
           <t>未着手</t>
         </is>
       </c>
-      <c r="F10" s="27" t="n"/>
+      <c r="F10" s="21" t="n"/>
       <c r="G10" s="6" t="inlineStr">
         <is>
           <t>担当が決まっていない</t>
@@ -2085,20 +1798,20 @@
           <t>LMP事業 · 加盟開発</t>
         </is>
       </c>
-      <c r="C11" s="24" t="inlineStr">
+      <c r="C11" s="18" t="inlineStr">
         <is>
           <t>白石・池之上・大熊</t>
         </is>
       </c>
-      <c r="D11" s="25" t="n">
+      <c r="D11" s="19" t="n">
         <v>0</v>
       </c>
-      <c r="E11" s="29" t="inlineStr">
+      <c r="E11" s="23" t="inlineStr">
         <is>
           <t>未着手</t>
         </is>
       </c>
-      <c r="F11" s="27" t="n"/>
+      <c r="F11" s="21" t="n"/>
       <c r="G11" s="6" t="inlineStr"/>
     </row>
     <row r="12" ht="32" customHeight="1">
@@ -2112,20 +1825,20 @@
           <t>RCP事業 · Web・ツール・システム</t>
         </is>
       </c>
-      <c r="C12" s="24" t="inlineStr">
+      <c r="C12" s="18" t="inlineStr">
         <is>
           <t>白石</t>
         </is>
       </c>
-      <c r="D12" s="25" t="n">
+      <c r="D12" s="19" t="n">
         <v>0</v>
       </c>
-      <c r="E12" s="29" t="inlineStr">
+      <c r="E12" s="23" t="inlineStr">
         <is>
           <t>未着手</t>
         </is>
       </c>
-      <c r="F12" s="27" t="n"/>
+      <c r="F12" s="21" t="n"/>
       <c r="G12" s="6" t="inlineStr"/>
     </row>
     <row r="13" ht="32" customHeight="1">
@@ -2139,20 +1852,20 @@
           <t>AIアオ先生 · 営業コーチ</t>
         </is>
       </c>
-      <c r="C13" s="24" t="inlineStr">
+      <c r="C13" s="18" t="inlineStr">
         <is>
           <t>池之上</t>
         </is>
       </c>
-      <c r="D13" s="25" t="n">
+      <c r="D13" s="19" t="n">
         <v>0.9</v>
       </c>
-      <c r="E13" s="30" t="inlineStr">
+      <c r="E13" s="24" t="inlineStr">
         <is>
           <t>確認待ち</t>
         </is>
       </c>
-      <c r="F13" s="27" t="n"/>
+      <c r="F13" s="21" t="n"/>
       <c r="G13" s="6" t="inlineStr">
         <is>
           <t>制作MASTERのみに記載</t>
@@ -2170,20 +1883,20 @@
           <t>RC事業 · 動画・コンテンツ</t>
         </is>
       </c>
-      <c r="C14" s="24" t="inlineStr">
+      <c r="C14" s="18" t="inlineStr">
         <is>
           <t>白石</t>
         </is>
       </c>
-      <c r="D14" s="25" t="n">
+      <c r="D14" s="19" t="n">
         <v>0.7</v>
       </c>
-      <c r="E14" s="26" t="inlineStr">
+      <c r="E14" s="20" t="inlineStr">
         <is>
           <t>進行中</t>
         </is>
       </c>
-      <c r="F14" s="27" t="n"/>
+      <c r="F14" s="21" t="n"/>
       <c r="G14" s="6" t="inlineStr">
         <is>
           <t>動画で唯一動いている1本</t>
@@ -2201,20 +1914,20 @@
           <t>RC事業 · 動画・コンテンツ</t>
         </is>
       </c>
-      <c r="C15" s="24" t="inlineStr">
+      <c r="C15" s="18" t="inlineStr">
         <is>
           <t>白石</t>
         </is>
       </c>
-      <c r="D15" s="25" t="n">
+      <c r="D15" s="19" t="n">
         <v>0</v>
       </c>
-      <c r="E15" s="29" t="inlineStr">
+      <c r="E15" s="23" t="inlineStr">
         <is>
           <t>未着手</t>
         </is>
       </c>
-      <c r="F15" s="27" t="n"/>
+      <c r="F15" s="21" t="n"/>
       <c r="G15" s="6" t="inlineStr"/>
     </row>
     <row r="16" ht="32" customHeight="1">
@@ -2228,20 +1941,20 @@
           <t>RC事業 · 動画・コンテンツ</t>
         </is>
       </c>
-      <c r="C16" s="24" t="inlineStr">
+      <c r="C16" s="18" t="inlineStr">
         <is>
           <t>白石</t>
         </is>
       </c>
-      <c r="D16" s="25" t="n">
+      <c r="D16" s="19" t="n">
         <v>0</v>
       </c>
-      <c r="E16" s="29" t="inlineStr">
+      <c r="E16" s="23" t="inlineStr">
         <is>
           <t>未着手</t>
         </is>
       </c>
-      <c r="F16" s="27" t="n"/>
+      <c r="F16" s="21" t="n"/>
       <c r="G16" s="6" t="inlineStr"/>
     </row>
     <row r="17" ht="32" customHeight="1">
@@ -2255,20 +1968,20 @@
           <t>RCP事業 · 動画・コンテンツ</t>
         </is>
       </c>
-      <c r="C17" s="24" t="inlineStr">
+      <c r="C17" s="18" t="inlineStr">
         <is>
           <t>白石</t>
         </is>
       </c>
-      <c r="D17" s="25" t="n">
+      <c r="D17" s="19" t="n">
         <v>0</v>
       </c>
-      <c r="E17" s="29" t="inlineStr">
+      <c r="E17" s="23" t="inlineStr">
         <is>
           <t>未着手</t>
         </is>
       </c>
-      <c r="F17" s="27" t="n"/>
+      <c r="F17" s="21" t="n"/>
       <c r="G17" s="6" t="inlineStr"/>
     </row>
     <row r="18" ht="32" customHeight="1">
@@ -2282,20 +1995,20 @@
           <t>RCP事業 · 動画・コンテンツ</t>
         </is>
       </c>
-      <c r="C18" s="24" t="inlineStr">
+      <c r="C18" s="18" t="inlineStr">
         <is>
           <t>白石</t>
         </is>
       </c>
-      <c r="D18" s="25" t="n">
+      <c r="D18" s="19" t="n">
         <v>0</v>
       </c>
-      <c r="E18" s="29" t="inlineStr">
+      <c r="E18" s="23" t="inlineStr">
         <is>
           <t>未着手</t>
         </is>
       </c>
-      <c r="F18" s="27" t="n"/>
+      <c r="F18" s="21" t="n"/>
       <c r="G18" s="6" t="inlineStr"/>
     </row>
     <row r="19" ht="32" customHeight="1">
@@ -2309,20 +2022,20 @@
           <t>RCP PPモデル · OEM</t>
         </is>
       </c>
-      <c r="C19" s="24" t="inlineStr">
+      <c r="C19" s="18" t="inlineStr">
         <is>
           <t>白石</t>
         </is>
       </c>
-      <c r="D19" s="25" t="n">
+      <c r="D19" s="19" t="n">
         <v>0</v>
       </c>
-      <c r="E19" s="29" t="inlineStr">
+      <c r="E19" s="23" t="inlineStr">
         <is>
           <t>未着手</t>
         </is>
       </c>
-      <c r="F19" s="27" t="n"/>
+      <c r="F19" s="21" t="n"/>
       <c r="G19" s="6" t="inlineStr">
         <is>
           <t>AKさん・大橋会長・木原さん・水谷先生・藤田先生</t>
@@ -2340,20 +2053,20 @@
           <t>RC／RCP／HI／PP · REALIZE QUEST</t>
         </is>
       </c>
-      <c r="C20" s="24" t="inlineStr">
+      <c r="C20" s="18" t="inlineStr">
         <is>
           <t>白石・片山</t>
         </is>
       </c>
-      <c r="D20" s="25" t="n">
+      <c r="D20" s="19" t="n">
         <v>0</v>
       </c>
-      <c r="E20" s="29" t="inlineStr">
+      <c r="E20" s="23" t="inlineStr">
         <is>
           <t>未着手</t>
         </is>
       </c>
-      <c r="F20" s="27" t="n"/>
+      <c r="F20" s="21" t="n"/>
       <c r="G20" s="6" t="inlineStr"/>
     </row>
     <row r="21" ht="32" customHeight="1">
@@ -2367,20 +2080,20 @@
           <t>採用 · 学生募集</t>
         </is>
       </c>
-      <c r="C21" s="24" t="inlineStr">
+      <c r="C21" s="18" t="inlineStr">
         <is>
           <t>白石・片山</t>
         </is>
       </c>
-      <c r="D21" s="25" t="n">
+      <c r="D21" s="19" t="n">
         <v>0</v>
       </c>
-      <c r="E21" s="29" t="inlineStr">
+      <c r="E21" s="23" t="inlineStr">
         <is>
           <t>未着手</t>
         </is>
       </c>
-      <c r="F21" s="27" t="n"/>
+      <c r="F21" s="21" t="n"/>
       <c r="G21" s="6" t="inlineStr">
         <is>
           <t>PR動画・SNS採用募集動画</t>
@@ -2388,33 +2101,33 @@
       </c>
     </row>
     <row r="22">
-      <c r="C22" s="18" t="inlineStr">
+      <c r="C22" s="12" t="inlineStr">
         <is>
           <t>平均</t>
         </is>
       </c>
-      <c r="D22" s="31">
+      <c r="D22" s="25">
         <f>AVERAGE(D6:D21)</f>
         <v/>
       </c>
-      <c r="E22" s="20">
+      <c r="E22" s="14">
         <f>COUNTIF(E6:E21,"未着手")&amp;" 件未着手"</f>
         <v/>
       </c>
-      <c r="F22" s="20">
+      <c r="F22" s="14">
         <f>COUNTA(F6:F21)&amp;" 件 登録ずみ"</f>
         <v/>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="32" t="inlineStr">
+      <c r="A24" s="26" t="inlineStr">
         <is>
           <t>できている設計書・ガイド</t>
         </is>
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="33" t="inlineStr">
+      <c r="A25" s="27" t="inlineStr">
         <is>
           <t>LIFE CHECK42 Eラーニング画面設計書</t>
         </is>
@@ -2429,14 +2142,14 @@
           <t>2026-08-31</t>
         </is>
       </c>
-      <c r="G25" s="34" t="inlineStr">
+      <c r="G25" s="28" t="inlineStr">
         <is>
           <t>開く</t>
         </is>
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="33" t="inlineStr">
+      <c r="A26" s="27" t="inlineStr">
         <is>
           <t>RCP ノーマル版 eラーニング｜UI提案 v1</t>
         </is>
@@ -2451,14 +2164,14 @@
           <t>2026-08-05</t>
         </is>
       </c>
-      <c r="G26" s="34" t="inlineStr">
+      <c r="G26" s="28" t="inlineStr">
         <is>
           <t>開く</t>
         </is>
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="33" t="inlineStr">
+      <c r="A27" s="27" t="inlineStr">
         <is>
           <t>AIロープレ 操作ガイド</t>
         </is>
@@ -2473,14 +2186,14 @@
           <t>2026-08-31</t>
         </is>
       </c>
-      <c r="G27" s="34" t="inlineStr">
+      <c r="G27" s="28" t="inlineStr">
         <is>
           <t>開く</t>
         </is>
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="33" t="inlineStr">
+      <c r="A28" s="27" t="inlineStr">
         <is>
           <t>生成AI動画講座 比較検討</t>
         </is>
@@ -2495,7 +2208,7 @@
           <t>2026-08-21</t>
         </is>
       </c>
-      <c r="G28" s="34" t="inlineStr">
+      <c r="G28" s="28" t="inlineStr">
         <is>
           <t>開く</t>
         </is>
@@ -2621,20 +2334,20 @@
           <t>RC法人開拓 · 地域企業への入口</t>
         </is>
       </c>
-      <c r="C6" s="24" t="inlineStr">
+      <c r="C6" s="18" t="inlineStr">
         <is>
           <t>大熊・片山</t>
         </is>
       </c>
-      <c r="D6" s="25" t="n">
+      <c r="D6" s="19" t="n">
         <v>0</v>
       </c>
-      <c r="E6" s="29" t="inlineStr">
+      <c r="E6" s="23" t="inlineStr">
         <is>
           <t>未着手</t>
         </is>
       </c>
-      <c r="F6" s="27" t="n"/>
+      <c r="F6" s="21" t="n"/>
       <c r="G6" s="6" t="inlineStr">
         <is>
           <t>バナー・原稿などのクリエイティブ</t>
@@ -2652,20 +2365,20 @@
           <t>RC法人開拓／LMP加盟開発</t>
         </is>
       </c>
-      <c r="C7" s="24" t="inlineStr">
+      <c r="C7" s="18" t="inlineStr">
         <is>
           <t>池之上・片山</t>
         </is>
       </c>
-      <c r="D7" s="25" t="n">
+      <c r="D7" s="19" t="n">
         <v>0</v>
       </c>
-      <c r="E7" s="29" t="inlineStr">
+      <c r="E7" s="23" t="inlineStr">
         <is>
           <t>未着手</t>
         </is>
       </c>
-      <c r="F7" s="27" t="n"/>
+      <c r="F7" s="21" t="n"/>
       <c r="G7" s="6" t="inlineStr">
         <is>
           <t>出稿・予算・改善</t>
@@ -2683,20 +2396,20 @@
           <t>LMP事業 · 全体品質確認</t>
         </is>
       </c>
-      <c r="C8" s="24" t="inlineStr">
+      <c r="C8" s="18" t="inlineStr">
         <is>
           <t>白石</t>
         </is>
       </c>
-      <c r="D8" s="25" t="n">
+      <c r="D8" s="19" t="n">
         <v>0</v>
       </c>
-      <c r="E8" s="29" t="inlineStr">
+      <c r="E8" s="23" t="inlineStr">
         <is>
           <t>未着手</t>
         </is>
       </c>
-      <c r="F8" s="27" t="n"/>
+      <c r="F8" s="21" t="n"/>
       <c r="G8" s="6" t="inlineStr">
         <is>
           <t>出す前の品質確認</t>
@@ -2714,20 +2427,20 @@
           <t>社内業務 · 法務・業法</t>
         </is>
       </c>
-      <c r="C9" s="24" t="inlineStr">
+      <c r="C9" s="18" t="inlineStr">
         <is>
           <t>社長・寺井・池之上・弁護士</t>
         </is>
       </c>
-      <c r="D9" s="25" t="n">
+      <c r="D9" s="19" t="n">
         <v>0</v>
       </c>
-      <c r="E9" s="29" t="inlineStr">
+      <c r="E9" s="23" t="inlineStr">
         <is>
           <t>未着手</t>
         </is>
       </c>
-      <c r="F9" s="27" t="n"/>
+      <c r="F9" s="21" t="n"/>
       <c r="G9" s="6" t="inlineStr">
         <is>
           <t>言い切り表現・実績表示の法務確認</t>
@@ -2745,37 +2458,37 @@
           <t>RC／RCP／HI／PP · REALIZE QUEST</t>
         </is>
       </c>
-      <c r="C10" s="24" t="inlineStr">
+      <c r="C10" s="18" t="inlineStr">
         <is>
           <t>白石</t>
         </is>
       </c>
-      <c r="D10" s="25" t="n">
+      <c r="D10" s="19" t="n">
         <v>0</v>
       </c>
-      <c r="E10" s="29" t="inlineStr">
+      <c r="E10" s="23" t="inlineStr">
         <is>
           <t>未着手</t>
         </is>
       </c>
-      <c r="F10" s="27" t="n"/>
+      <c r="F10" s="21" t="n"/>
       <c r="G10" s="6" t="inlineStr"/>
     </row>
     <row r="11">
-      <c r="C11" s="18" t="inlineStr">
+      <c r="C11" s="12" t="inlineStr">
         <is>
           <t>平均</t>
         </is>
       </c>
-      <c r="D11" s="31">
+      <c r="D11" s="25">
         <f>AVERAGE(D6:D10)</f>
         <v/>
       </c>
-      <c r="E11" s="20">
+      <c r="E11" s="14">
         <f>COUNTIF(E6:E10,"未着手")&amp;" 件未着手"</f>
         <v/>
       </c>
-      <c r="F11" s="20">
+      <c r="F11" s="14">
         <f>COUNTA(F6:F10)&amp;" 件 登録ずみ"</f>
         <v/>
       </c>
@@ -2821,318 +2534,318 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="35" t="inlineStr">
+      <c r="A1" s="29" t="inlineStr">
         <is>
           <t>凡例と出典</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="36" t="inlineStr">
+      <c r="A3" s="30" t="inlineStr">
         <is>
           <t>LPの3段</t>
         </is>
       </c>
     </row>
     <row r="4" ht="36" customHeight="1">
-      <c r="A4" s="37" t="inlineStr">
+      <c r="A4" s="31" t="inlineStr">
         <is>
           <t>原稿・デザイン</t>
         </is>
       </c>
-      <c r="B4" s="38" t="inlineStr">
+      <c r="B4" s="32" t="inlineStr">
         <is>
           <t>本編の文章とデザインが最後まで通っている</t>
         </is>
       </c>
     </row>
     <row r="5" ht="36" customHeight="1">
-      <c r="A5" s="37" t="inlineStr">
+      <c r="A5" s="31" t="inlineStr">
         <is>
           <t>問い合わせ導線</t>
         </is>
       </c>
-      <c r="B5" s="38" t="inlineStr">
+      <c r="B5" s="32" t="inlineStr">
         <is>
           <t>ボタンの行き先が実在し、問い合わせが届く先につながっている</t>
         </is>
       </c>
     </row>
     <row r="6" ht="36" customHeight="1">
-      <c r="A6" s="37" t="inlineStr">
+      <c r="A6" s="31" t="inlineStr">
         <is>
           <t>本番公開</t>
         </is>
       </c>
-      <c r="B6" s="38" t="inlineStr">
+      <c r="B6" s="32" t="inlineStr">
         <is>
           <t>独自ドメインで公開され、G列に本番URLが入っている（自動判定）</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="36" t="inlineStr">
+      <c r="A8" s="30" t="inlineStr">
         <is>
           <t>記号</t>
         </is>
       </c>
     </row>
     <row r="9" ht="36" customHeight="1">
-      <c r="A9" s="37" t="inlineStr">
+      <c r="A9" s="31" t="inlineStr">
         <is>
           <t>○</t>
         </is>
       </c>
-      <c r="B9" s="38" t="inlineStr">
+      <c r="B9" s="32" t="inlineStr">
         <is>
           <t>できている</t>
         </is>
       </c>
     </row>
     <row r="10" ht="36" customHeight="1">
-      <c r="A10" s="37" t="inlineStr">
+      <c r="A10" s="31" t="inlineStr">
         <is>
           <t>△</t>
         </is>
       </c>
-      <c r="B10" s="38" t="inlineStr">
+      <c r="B10" s="32" t="inlineStr">
         <is>
           <t>仮づけ。メーラーを開くだけ、または行き先が「#」のまま</t>
         </is>
       </c>
     </row>
     <row r="11" ht="36" customHeight="1">
-      <c r="A11" s="37" t="inlineStr">
+      <c r="A11" s="31" t="inlineStr">
         <is>
           <t>×</t>
         </is>
       </c>
-      <c r="B11" s="38" t="inlineStr">
+      <c r="B11" s="32" t="inlineStr">
         <is>
           <t>手つかず／ページが存在しない</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="36" t="inlineStr">
+      <c r="A13" s="30" t="inlineStr">
         <is>
           <t>状態</t>
         </is>
       </c>
     </row>
     <row r="14" ht="36" customHeight="1">
-      <c r="A14" s="37" t="inlineStr">
+      <c r="A14" s="31" t="inlineStr">
         <is>
           <t>確認待ち</t>
         </is>
       </c>
-      <c r="B14" s="38" t="inlineStr">
+      <c r="B14" s="32" t="inlineStr">
         <is>
           <t>作業は終わり、誰かの確認を待っている</t>
         </is>
       </c>
     </row>
     <row r="15" ht="36" customHeight="1">
-      <c r="A15" s="37" t="inlineStr">
+      <c r="A15" s="31" t="inlineStr">
         <is>
           <t>進行中</t>
         </is>
       </c>
-      <c r="B15" s="38" t="inlineStr">
+      <c r="B15" s="32" t="inlineStr">
         <is>
           <t>いま手が動いている</t>
         </is>
       </c>
     </row>
     <row r="16" ht="36" customHeight="1">
-      <c r="A16" s="37" t="inlineStr">
+      <c r="A16" s="31" t="inlineStr">
         <is>
           <t>未着手</t>
         </is>
       </c>
-      <c r="B16" s="38" t="inlineStr">
+      <c r="B16" s="32" t="inlineStr">
         <is>
           <t>まだ始まっていない</t>
         </is>
       </c>
     </row>
     <row r="17" ht="36" customHeight="1">
-      <c r="A17" s="37" t="inlineStr">
+      <c r="A17" s="31" t="inlineStr">
         <is>
           <t>赤い担当名</t>
         </is>
       </c>
-      <c r="B17" s="38" t="inlineStr">
+      <c r="B17" s="32" t="inlineStr">
         <is>
           <t>担当が「未定」の仕事。誰かを決めないと進みません</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="36" t="inlineStr">
+      <c r="A19" s="30" t="inlineStr">
         <is>
           <t>クリックして選べるところ（水色のセル）</t>
         </is>
       </c>
     </row>
     <row r="20" ht="36" customHeight="1">
-      <c r="A20" s="37" t="inlineStr">
+      <c r="A20" s="31" t="inlineStr">
         <is>
           <t>案件</t>
         </is>
       </c>
-      <c r="B20" s="38" t="inlineStr">
+      <c r="B20" s="32" t="inlineStr">
         <is>
           <t>LPシートのA列。どの案件のLPかを選びます。</t>
         </is>
       </c>
     </row>
     <row r="21" ht="36" customHeight="1">
-      <c r="A21" s="37" t="inlineStr">
+      <c r="A21" s="31" t="inlineStr">
         <is>
           <t>担当</t>
         </is>
       </c>
-      <c r="B21" s="38" t="inlineStr">
+      <c r="B21" s="32" t="inlineStr">
         <is>
           <t>タスクシートのC列。一覧から選ぶか、直接書き換えます。</t>
         </is>
       </c>
     </row>
     <row r="22" ht="36" customHeight="1">
-      <c r="A22" s="37" t="inlineStr">
+      <c r="A22" s="31" t="inlineStr">
         <is>
           <t>進捗</t>
         </is>
       </c>
-      <c r="B22" s="38" t="inlineStr">
+      <c r="B22" s="32" t="inlineStr">
         <is>
           <t>タスクシートのD列。0%〜100%を5%きざみで選べます。選ぶとセルの中のバーが伸び縮みします。</t>
         </is>
       </c>
     </row>
     <row r="23" ht="36" customHeight="1">
-      <c r="A23" s="37" t="inlineStr">
+      <c r="A23" s="31" t="inlineStr">
         <is>
           <t>状態</t>
         </is>
       </c>
-      <c r="B23" s="38" t="inlineStr">
+      <c r="B23" s="32" t="inlineStr">
         <is>
           <t>タスクシートのE列。未着手／進行中／確認待ち。</t>
         </is>
       </c>
     </row>
     <row r="24" ht="36" customHeight="1">
-      <c r="A24" s="37" t="inlineStr">
+      <c r="A24" s="31" t="inlineStr">
         <is>
           <t>LPの○△×</t>
         </is>
       </c>
-      <c r="B24" s="38" t="inlineStr">
+      <c r="B24" s="32" t="inlineStr">
         <is>
           <t>LPシートのD・E列。本番公開（F列）はG列のURL有無から自動で決まります。</t>
         </is>
       </c>
     </row>
     <row r="25" ht="36" customHeight="1">
-      <c r="A25" s="37" t="inlineStr">
+      <c r="A25" s="31" t="inlineStr">
         <is>
           <t>黄色の記入欄</t>
         </is>
       </c>
-      <c r="B25" s="38" t="inlineStr">
+      <c r="B25" s="32" t="inlineStr">
         <is>
           <t>公開したURL・動画URL・広告の入稿先を貼ります。</t>
         </is>
       </c>
     </row>
     <row r="26" ht="36" customHeight="1">
-      <c r="A26" s="37" t="inlineStr">
+      <c r="A26" s="31" t="inlineStr">
         <is>
           <t>列見出しの▼</t>
         </is>
       </c>
-      <c r="B26" s="38" t="inlineStr">
+      <c r="B26" s="32" t="inlineStr">
         <is>
           <t>オートフィルタです。値を選ぶとその行だけ表示されます。複数の列を組み合わせられます。</t>
         </is>
       </c>
     </row>
     <row r="27" ht="36" customHeight="1">
-      <c r="A27" s="37" t="inlineStr">
+      <c r="A27" s="31" t="inlineStr">
         <is>
           <t>選択肢を増やしたいとき</t>
         </is>
       </c>
-      <c r="B27" s="38" t="inlineStr">
+      <c r="B27" s="32" t="inlineStr">
         <is>
           <t>非表示シート「選択肢」に一覧があります。値を足し、入力規則の参照範囲を広げれば選べるようになります。</t>
         </is>
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="36" t="inlineStr">
+      <c r="A29" s="30" t="inlineStr">
         <is>
           <t>出典</t>
         </is>
       </c>
     </row>
     <row r="30" ht="36" customHeight="1">
-      <c r="A30" s="37" t="inlineStr">
+      <c r="A30" s="31" t="inlineStr">
         <is>
           <t>LPシート</t>
         </is>
       </c>
-      <c r="B30" s="38" t="inlineStr">
+      <c r="B30" s="32" t="inlineStr">
         <is>
           <t>公開済みアーティファクト43件のうちLPに該当する22ページ（本編11＋付随11）を、1ページずつHTMLを読んで確認。ボタンの行き先・フォームの送信方法・付随ページの有無は実物ベースです。</t>
         </is>
       </c>
     </row>
     <row r="31" ht="36" customHeight="1">
-      <c r="A31" s="37" t="inlineStr">
+      <c r="A31" s="31" t="inlineStr">
         <is>
           <t>進捗％と担当</t>
         </is>
       </c>
-      <c r="B31" s="38" t="inlineStr">
+      <c r="B31" s="32" t="inlineStr">
         <is>
           <t>社内の「REALIZE OS 制作MASTER」(2026-09-03) と「仕事の棚卸し」(2026-09-02) の数値をそのまま引いています。</t>
         </is>
       </c>
     </row>
     <row r="32" ht="36" customHeight="1">
-      <c r="A32" s="37" t="inlineStr">
+      <c r="A32" s="31" t="inlineStr">
         <is>
           <t>担当の食い違い</t>
         </is>
       </c>
-      <c r="B32" s="38" t="inlineStr">
+      <c r="B32" s="32" t="inlineStr">
         <is>
           <t>広告運用の担当は2資料で記載が違います（制作MASTER＝大熊・片山／棚卸し＝池之上・片山）。広告制作は大熊・片山、広告運用は池之上・片山としています。</t>
         </is>
       </c>
     </row>
     <row r="33" ht="36" customHeight="1">
-      <c r="A33" s="37" t="inlineStr">
+      <c r="A33" s="31" t="inlineStr">
         <is>
           <t>未確認</t>
         </is>
       </c>
-      <c r="B33" s="38" t="inlineStr">
+      <c r="B33" s="32" t="inlineStr">
         <is>
           <t>LP付随ページ4本（RC星空案の会社概要、RCアイス案の資料請求、LMP星空案の資料請求と会社概要）は、親LPからのリンクで存在を確認しただけで中身は開いていません。</t>
         </is>
       </c>
     </row>
     <row r="34" ht="36" customHeight="1">
-      <c r="A34" s="37" t="inlineStr">
+      <c r="A34" s="31" t="inlineStr">
         <is>
           <t>調査日</t>
         </is>
       </c>
-      <c r="B34" s="38" t="inlineStr">
+      <c r="B34" s="32" t="inlineStr">
         <is>
           <t>2026-09-03</t>
         </is>

--- a/制作進捗ボード.xlsx
+++ b/制作進捗ボード.xlsx
@@ -811,7 +811,7 @@
         </is>
       </c>
       <c r="F6" s="8">
-        <f>IF(G6="","×","○")</f>
+        <f>IF(G6="","×",HYPERLINK(G6,"○"))</f>
         <v/>
       </c>
       <c r="G6" s="9" t="n"/>
@@ -853,7 +853,7 @@
         </is>
       </c>
       <c r="F7" s="11">
-        <f>IF(G7="","×","○")</f>
+        <f>IF(G7="","×",HYPERLINK(G7,"○"))</f>
         <v/>
       </c>
       <c r="G7" s="9" t="n"/>
@@ -895,7 +895,7 @@
         </is>
       </c>
       <c r="F8" s="8">
-        <f>IF(G8="","×","○")</f>
+        <f>IF(G8="","×",HYPERLINK(G8,"○"))</f>
         <v/>
       </c>
       <c r="G8" s="9" t="n"/>
@@ -937,7 +937,7 @@
         </is>
       </c>
       <c r="F9" s="11">
-        <f>IF(G9="","×","○")</f>
+        <f>IF(G9="","×",HYPERLINK(G9,"○"))</f>
         <v/>
       </c>
       <c r="G9" s="9" t="n"/>
@@ -979,7 +979,7 @@
         </is>
       </c>
       <c r="F10" s="8">
-        <f>IF(G10="","×","○")</f>
+        <f>IF(G10="","×",HYPERLINK(G10,"○"))</f>
         <v/>
       </c>
       <c r="G10" s="9" t="n"/>
@@ -1021,7 +1021,7 @@
         </is>
       </c>
       <c r="F11" s="11">
-        <f>IF(G11="","×","○")</f>
+        <f>IF(G11="","×",HYPERLINK(G11,"○"))</f>
         <v/>
       </c>
       <c r="G11" s="9" t="n"/>
@@ -1063,7 +1063,7 @@
         </is>
       </c>
       <c r="F12" s="8">
-        <f>IF(G12="","×","○")</f>
+        <f>IF(G12="","×",HYPERLINK(G12,"○"))</f>
         <v/>
       </c>
       <c r="G12" s="9" t="n"/>
@@ -1105,7 +1105,7 @@
         </is>
       </c>
       <c r="F13" s="11">
-        <f>IF(G13="","×","○")</f>
+        <f>IF(G13="","×",HYPERLINK(G13,"○"))</f>
         <v/>
       </c>
       <c r="G13" s="9" t="n"/>
@@ -1147,7 +1147,7 @@
         </is>
       </c>
       <c r="F14" s="8">
-        <f>IF(G14="","×","○")</f>
+        <f>IF(G14="","×",HYPERLINK(G14,"○"))</f>
         <v/>
       </c>
       <c r="G14" s="9" t="n"/>
@@ -1189,7 +1189,7 @@
         </is>
       </c>
       <c r="F15" s="11">
-        <f>IF(G15="","×","○")</f>
+        <f>IF(G15="","×",HYPERLINK(G15,"○"))</f>
         <v/>
       </c>
       <c r="G15" s="9" t="n"/>
@@ -1231,7 +1231,7 @@
         </is>
       </c>
       <c r="F16" s="8">
-        <f>IF(G16="","×","○")</f>
+        <f>IF(G16="","×",HYPERLINK(G16,"○"))</f>
         <v/>
       </c>
       <c r="G16" s="9" t="n"/>
@@ -2579,7 +2579,7 @@
       </c>
       <c r="B6" s="32" t="inlineStr">
         <is>
-          <t>独自ドメインで公開され、G列に本番URLが入っている（自動判定）</t>
+          <t>独自ドメインで公開され、G列に本番URLが入っている（自動判定）。○はそのページへのリンクになり、クリックすると開きます。</t>
         </is>
       </c>
     </row>
@@ -2756,7 +2756,7 @@
       </c>
       <c r="B25" s="32" t="inlineStr">
         <is>
-          <t>公開したURL・動画URL・広告の入稿先を貼ります。</t>
+          <t>公開したURL・動画URL・広告の入稿先を貼ります。LPシートは、貼るとF列の○がそのページへのリンクになります。</t>
         </is>
       </c>
     </row>

--- a/制作進捗ボード.xlsx
+++ b/制作進捗ボード.xlsx
@@ -74,8 +74,9 @@
     </font>
     <font>
       <name val="Meiryo"/>
-      <color rgb="000000FF"/>
+      <color rgb="000563C1"/>
       <sz val="9"/>
+      <u val="single"/>
     </font>
     <font>
       <name val="Meiryo"/>
@@ -733,7 +734,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>水色のセルはクリックすると▼が出て選べます。黄色のG列にURLを入れると、本番公開が自動で○になります。</t>
+          <t>水色のセルはクリックすると▼が出て選べます。黄色のG列にURLを貼ると本番公開が○になり、そのセルがページへのリンクになります。</t>
         </is>
       </c>
     </row>
@@ -811,7 +812,7 @@
         </is>
       </c>
       <c r="F6" s="8">
-        <f>IF(G6="","×",HYPERLINK(G6,"○"))</f>
+        <f>IF(G6="","×","○")</f>
         <v/>
       </c>
       <c r="G6" s="9" t="n"/>
@@ -853,7 +854,7 @@
         </is>
       </c>
       <c r="F7" s="11">
-        <f>IF(G7="","×",HYPERLINK(G7,"○"))</f>
+        <f>IF(G7="","×","○")</f>
         <v/>
       </c>
       <c r="G7" s="9" t="n"/>
@@ -895,7 +896,7 @@
         </is>
       </c>
       <c r="F8" s="8">
-        <f>IF(G8="","×",HYPERLINK(G8,"○"))</f>
+        <f>IF(G8="","×","○")</f>
         <v/>
       </c>
       <c r="G8" s="9" t="n"/>
@@ -937,7 +938,7 @@
         </is>
       </c>
       <c r="F9" s="11">
-        <f>IF(G9="","×",HYPERLINK(G9,"○"))</f>
+        <f>IF(G9="","×","○")</f>
         <v/>
       </c>
       <c r="G9" s="9" t="n"/>
@@ -979,7 +980,7 @@
         </is>
       </c>
       <c r="F10" s="8">
-        <f>IF(G10="","×",HYPERLINK(G10,"○"))</f>
+        <f>IF(G10="","×","○")</f>
         <v/>
       </c>
       <c r="G10" s="9" t="n"/>
@@ -1021,7 +1022,7 @@
         </is>
       </c>
       <c r="F11" s="11">
-        <f>IF(G11="","×",HYPERLINK(G11,"○"))</f>
+        <f>IF(G11="","×","○")</f>
         <v/>
       </c>
       <c r="G11" s="9" t="n"/>
@@ -1063,7 +1064,7 @@
         </is>
       </c>
       <c r="F12" s="8">
-        <f>IF(G12="","×",HYPERLINK(G12,"○"))</f>
+        <f>IF(G12="","×","○")</f>
         <v/>
       </c>
       <c r="G12" s="9" t="n"/>
@@ -1105,7 +1106,7 @@
         </is>
       </c>
       <c r="F13" s="11">
-        <f>IF(G13="","×",HYPERLINK(G13,"○"))</f>
+        <f>IF(G13="","×","○")</f>
         <v/>
       </c>
       <c r="G13" s="9" t="n"/>
@@ -1147,7 +1148,7 @@
         </is>
       </c>
       <c r="F14" s="8">
-        <f>IF(G14="","×",HYPERLINK(G14,"○"))</f>
+        <f>IF(G14="","×","○")</f>
         <v/>
       </c>
       <c r="G14" s="9" t="n"/>
@@ -1189,7 +1190,7 @@
         </is>
       </c>
       <c r="F15" s="11">
-        <f>IF(G15="","×",HYPERLINK(G15,"○"))</f>
+        <f>IF(G15="","×","○")</f>
         <v/>
       </c>
       <c r="G15" s="9" t="n"/>
@@ -1231,7 +1232,7 @@
         </is>
       </c>
       <c r="F16" s="8">
-        <f>IF(G16="","×",HYPERLINK(G16,"○"))</f>
+        <f>IF(G16="","×","○")</f>
         <v/>
       </c>
       <c r="G16" s="9" t="n"/>
@@ -1591,7 +1592,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>ツールの箱は50%まで来ていますが、中に入れる動画が20%で止まっています。赤い担当名は「未定」です。</t>
+          <t>ツールの箱は50%まで来ていますが、中に入れる動画が20%で止まっています。赤い担当名は「未定」です。黄色のF列にURLを貼るとリンクになります。</t>
         </is>
       </c>
     </row>
@@ -2579,7 +2580,7 @@
       </c>
       <c r="B6" s="32" t="inlineStr">
         <is>
-          <t>独自ドメインで公開され、G列に本番URLが入っている（自動判定）。○はそのページへのリンクになり、クリックすると開きます。</t>
+          <t>独自ドメインで公開され、G列に本番URLが入っている（自動判定）。</t>
         </is>
       </c>
     </row>
@@ -2751,12 +2752,12 @@
     <row r="25" ht="36" customHeight="1">
       <c r="A25" s="31" t="inlineStr">
         <is>
-          <t>黄色の記入欄</t>
+          <t>黄色の記入欄（本番URL）</t>
         </is>
       </c>
       <c r="B25" s="32" t="inlineStr">
         <is>
-          <t>公開したURL・動画URL・広告の入稿先を貼ります。LPシートは、貼るとF列の○がそのページへのリンクになります。</t>
+          <t>公開したURL・動画URL・広告の入稿先を貼ります。貼ってEnterを押すと、そのセルがそのページへのリンクになり、クリックで開きます。リンクにならないときは、そのセルを右クリック→「リンク」で設定できます。</t>
         </is>
       </c>
     </row>

--- a/制作進捗ボード.xlsx
+++ b/制作進捗ボード.xlsx
@@ -14,9 +14,9 @@
     <sheet name="凡例と出典" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'LP'!$A$5:$I$16</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'eラーニング・動画'!$A$5:$G$21</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'広告'!$A$5:$G$10</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'LP'!$A$5:$J$16</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'eラーニング・動画'!$A$5:$H$21</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'広告'!$A$5:$H$10</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -69,14 +69,14 @@
     </font>
     <font>
       <name val="Meiryo"/>
-      <color rgb="001B2330"/>
+      <color rgb="000563C1"/>
       <sz val="9"/>
+      <u val="single"/>
     </font>
     <font>
       <name val="Meiryo"/>
-      <color rgb="000563C1"/>
+      <color rgb="001B2330"/>
       <sz val="9"/>
-      <u val="single"/>
     </font>
     <font>
       <name val="Meiryo"/>
@@ -192,7 +192,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="33">
+  <cellXfs count="35">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -200,23 +200,29 @@
     <xf numFmtId="0" fontId="6" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
+    <xf numFmtId="0" fontId="8" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="8" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -231,16 +237,16 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="9" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="9" fontId="7" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="9" fontId="8" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -256,14 +262,14 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="17" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -703,7 +709,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I17"/>
+  <dimension ref="A1:J17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -713,8 +719,9 @@
     <col width="15" customWidth="1" min="5" max="5"/>
     <col width="11" customWidth="1" min="6" max="6"/>
     <col width="36" customWidth="1" min="7" max="7"/>
-    <col width="58" customWidth="1" min="8" max="8"/>
-    <col width="11" customWidth="1" min="9" max="9"/>
+    <col width="8" customWidth="1" min="8" max="8"/>
+    <col width="56" customWidth="1" min="9" max="9"/>
+    <col width="11" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -734,7 +741,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>水色のセルはクリックすると▼が出て選べます。黄色のG列にURLを貼ると本番公開が○になり、そのセルがページへのリンクになります。</t>
+          <t>水色のセルはクリックすると▼が出て選べます。黄色のG列にURLを貼ると、本番公開が○になり、H列の「開く」からそのページへ飛べます。</t>
         </is>
       </c>
     </row>
@@ -776,10 +783,15 @@
       </c>
       <c r="H5" s="4" t="inlineStr">
         <is>
+          <t>開く</t>
+        </is>
+      </c>
+      <c r="I5" s="4" t="inlineStr">
+        <is>
           <t>残っていること</t>
         </is>
       </c>
-      <c r="I5" s="4" t="inlineStr">
+      <c r="J5" s="4" t="inlineStr">
         <is>
           <t>更新日</t>
         </is>
@@ -816,12 +828,16 @@
         <v/>
       </c>
       <c r="G6" s="9" t="n"/>
-      <c r="H6" s="6" t="inlineStr">
+      <c r="H6" s="10">
+        <f>IF(G6="","",HYPERLINK(G6,"開く"))</f>
+        <v/>
+      </c>
+      <c r="I6" s="6" t="inlineStr">
         <is>
           <t>送信ボタンがメーラーを開くだけ。受付フォームの実装が必要／会社概要ページが未作成／本番ドメインへの公開</t>
         </is>
       </c>
-      <c r="I6" s="8" t="inlineStr">
+      <c r="J6" s="8" t="inlineStr">
         <is>
           <t>2026-09-03</t>
         </is>
@@ -833,12 +849,12 @@
           <t>REALIZE CLUB（法人向け）</t>
         </is>
       </c>
-      <c r="B7" s="10" t="inlineStr">
+      <c r="B7" s="11" t="inlineStr">
         <is>
           <t>会社が社員の人生を支える時代へ</t>
         </is>
       </c>
-      <c r="C7" s="10" t="inlineStr">
+      <c r="C7" s="11" t="inlineStr">
         <is>
           <t>星空タウン／クリーム × 濃紺のイラスト</t>
         </is>
@@ -853,17 +869,21 @@
           <t>△</t>
         </is>
       </c>
-      <c r="F7" s="11">
+      <c r="F7" s="12">
         <f>IF(G7="","×","○")</f>
         <v/>
       </c>
       <c r="G7" s="9" t="n"/>
-      <c r="H7" s="10" t="inlineStr">
+      <c r="H7" s="13">
+        <f>IF(G7="","",HYPERLINK(G7,"開く"))</f>
+        <v/>
+      </c>
+      <c r="I7" s="11" t="inlineStr">
         <is>
           <t>3ページ揃っている唯一のRC案。採用するかの判断／送信はメーラー起動のみ</t>
         </is>
       </c>
-      <c r="I7" s="11" t="inlineStr">
+      <c r="J7" s="12" t="inlineStr">
         <is>
           <t>2026-08-31</t>
         </is>
@@ -900,12 +920,16 @@
         <v/>
       </c>
       <c r="G8" s="9" t="n"/>
-      <c r="H8" s="6" t="inlineStr">
+      <c r="H8" s="10">
+        <f>IF(G8="","",HYPERLINK(G8,"開く"))</f>
+        <v/>
+      </c>
+      <c r="I8" s="6" t="inlineStr">
         <is>
           <t>kaisha.html ほかへの相対リンクが残り、単体では飛べない／会社概要ページの作成</t>
         </is>
       </c>
-      <c r="I8" s="8" t="inlineStr">
+      <c r="J8" s="8" t="inlineStr">
         <is>
           <t>2026-08-31</t>
         </is>
@@ -917,12 +941,12 @@
           <t>REALIZE CLUB（法人向け）</t>
         </is>
       </c>
-      <c r="B9" s="10" t="inlineStr">
+      <c r="B9" s="11" t="inlineStr">
         <is>
           <t>その安心、今がお得。</t>
         </is>
       </c>
-      <c r="C9" s="10" t="inlineStr">
+      <c r="C9" s="11" t="inlineStr">
         <is>
           <t>スーパーの特売ポップ／白地に赤と黄</t>
         </is>
@@ -937,17 +961,21 @@
           <t>×</t>
         </is>
       </c>
-      <c r="F9" s="11">
+      <c r="F9" s="12">
         <f>IF(G9="","×","○")</f>
         <v/>
       </c>
       <c r="G9" s="9" t="n"/>
-      <c r="H9" s="10" t="inlineStr">
+      <c r="H9" s="13">
+        <f>IF(G9="","",HYPERLINK(G9,"開く"))</f>
+        <v/>
+      </c>
+      <c r="I9" s="11" t="inlineStr">
         <is>
           <t>リンクがすべてページ内アンカー。外部への導線が1本もない／会社概要ページ、送信先の設定</t>
         </is>
       </c>
-      <c r="I9" s="11" t="inlineStr">
+      <c r="J9" s="12" t="inlineStr">
         <is>
           <t>2026-08-31</t>
         </is>
@@ -984,12 +1012,16 @@
         <v/>
       </c>
       <c r="G10" s="9" t="n"/>
-      <c r="H10" s="6" t="inlineStr">
+      <c r="H10" s="10">
+        <f>IF(G10="","",HYPERLINK(G10,"開く"))</f>
+        <v/>
+      </c>
+      <c r="I10" s="6" t="inlineStr">
         <is>
           <t>会社概要ページが未作成／送信はメーラー起動のみ</t>
         </is>
       </c>
-      <c r="I10" s="8" t="inlineStr">
+      <c r="J10" s="8" t="inlineStr">
         <is>
           <t>2026-08-28</t>
         </is>
@@ -1001,12 +1033,12 @@
           <t>LIFE MAKE PARTNERS（加盟店募集）</t>
         </is>
       </c>
-      <c r="B11" s="10" t="inlineStr">
+      <c r="B11" s="11" t="inlineStr">
         <is>
           <t>家より先に、人生の話を。</t>
         </is>
       </c>
-      <c r="C11" s="10" t="inlineStr">
+      <c r="C11" s="11" t="inlineStr">
         <is>
           <t>韓国料理店の看板／木の壁 × 生成りの横断幕</t>
         </is>
@@ -1021,17 +1053,21 @@
           <t>○</t>
         </is>
       </c>
-      <c r="F11" s="11">
+      <c r="F11" s="12">
         <f>IF(G11="","×","○")</f>
         <v/>
       </c>
       <c r="G11" s="9" t="n"/>
-      <c r="H11" s="10" t="inlineStr">
+      <c r="H11" s="13">
+        <f>IF(G11="","",HYPERLINK(G11,"開く"))</f>
+        <v/>
+      </c>
+      <c r="I11" s="11" t="inlineStr">
         <is>
           <t>本番ドメインへの公開だけが残り。問い合わせはLINE公式（lin.ee/WHYApuM）に集約済み</t>
         </is>
       </c>
-      <c r="I11" s="11" t="inlineStr">
+      <c r="J11" s="12" t="inlineStr">
         <is>
           <t>2026-09-03</t>
         </is>
@@ -1068,12 +1104,16 @@
         <v/>
       </c>
       <c r="G12" s="9" t="n"/>
-      <c r="H12" s="6" t="inlineStr">
+      <c r="H12" s="10">
+        <f>IF(G12="","",HYPERLINK(G12,"開く"))</f>
+        <v/>
+      </c>
+      <c r="I12" s="6" t="inlineStr">
         <is>
           <t>kaisha-katsu.html ほかへの相対リンクが残り飛べない／行き先が「#」のままのボタンが2つ</t>
         </is>
       </c>
-      <c r="I12" s="8" t="inlineStr">
+      <c r="J12" s="8" t="inlineStr">
         <is>
           <t>2026-08-28</t>
         </is>
@@ -1085,12 +1125,12 @@
           <t>LIFE MAKE PARTNERS（加盟店募集）</t>
         </is>
       </c>
-      <c r="B13" s="10" t="inlineStr">
+      <c r="B13" s="11" t="inlineStr">
         <is>
           <t>加盟資格は、人生への愛。ただそれだけ。</t>
         </is>
       </c>
-      <c r="C13" s="10" t="inlineStr">
+      <c r="C13" s="11" t="inlineStr">
         <is>
           <t>星空タウン／RC星空案と同じ世界観</t>
         </is>
@@ -1105,17 +1145,21 @@
           <t>△</t>
         </is>
       </c>
-      <c r="F13" s="11">
+      <c r="F13" s="12">
         <f>IF(G13="","×","○")</f>
         <v/>
       </c>
       <c r="G13" s="9" t="n"/>
-      <c r="H13" s="10" t="inlineStr">
+      <c r="H13" s="13">
+        <f>IF(G13="","",HYPERLINK(G13,"開く"))</f>
+        <v/>
+      </c>
+      <c r="I13" s="11" t="inlineStr">
         <is>
           <t>行き先が「#」のままのボタンが2つ／統廃合の判断</t>
         </is>
       </c>
-      <c r="I13" s="11" t="inlineStr">
+      <c r="J13" s="12" t="inlineStr">
         <is>
           <t>2026-08-24</t>
         </is>
@@ -1152,12 +1196,16 @@
         <v/>
       </c>
       <c r="G14" s="9" t="n"/>
-      <c r="H14" s="6" t="inlineStr">
+      <c r="H14" s="10">
+        <f>IF(G14="","",HYPERLINK(G14,"開く"))</f>
+        <v/>
+      </c>
+      <c r="I14" s="6" t="inlineStr">
         <is>
           <t>行き先が「#」のままのリンクが2つ残っている／本番ドメインへの公開</t>
         </is>
       </c>
-      <c r="I14" s="8" t="inlineStr">
+      <c r="J14" s="8" t="inlineStr">
         <is>
           <t>2026-09-03</t>
         </is>
@@ -1169,12 +1217,12 @@
           <t>まちの相談窓口</t>
         </is>
       </c>
-      <c r="B15" s="10" t="inlineStr">
+      <c r="B15" s="11" t="inlineStr">
         <is>
           <t>まちの相談窓口（フォーム版）</t>
         </is>
       </c>
-      <c r="C15" s="10" t="inlineStr">
+      <c r="C15" s="11" t="inlineStr">
         <is>
           <t>銭湯ポスター／申込フォーム内蔵</t>
         </is>
@@ -1189,17 +1237,21 @@
           <t>△</t>
         </is>
       </c>
-      <c r="F15" s="11">
+      <c r="F15" s="12">
         <f>IF(G15="","×","○")</f>
         <v/>
       </c>
       <c r="G15" s="9" t="n"/>
-      <c r="H15" s="10" t="inlineStr">
+      <c r="H15" s="13">
+        <f>IF(G15="","",HYPERLINK(G15,"開く"))</f>
+        <v/>
+      </c>
+      <c r="I15" s="11" t="inlineStr">
         <is>
           <t>LINE誘導版に置き換わっている。残すか消すかの判断</t>
         </is>
       </c>
-      <c r="I15" s="11" t="inlineStr">
+      <c r="J15" s="12" t="inlineStr">
         <is>
           <t>2026-08-20</t>
         </is>
@@ -1236,42 +1288,46 @@
         <v/>
       </c>
       <c r="G16" s="9" t="n"/>
-      <c r="H16" s="6" t="inlineStr">
+      <c r="H16" s="10">
+        <f>IF(G16="","",HYPERLINK(G16,"開く"))</f>
+        <v/>
+      </c>
+      <c r="I16" s="6" t="inlineStr">
         <is>
           <t>ページのタイトルタグが空。共有すると名前なしで出る／資料請求・会社概要ページ、送信先の設定</t>
         </is>
       </c>
-      <c r="I16" s="8" t="inlineStr">
+      <c r="J16" s="8" t="inlineStr">
         <is>
           <t>2026-08-19</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="C17" s="12" t="inlineStr">
+      <c r="C17" s="14" t="inlineStr">
         <is>
           <t>○の数</t>
         </is>
       </c>
-      <c r="D17" s="13">
+      <c r="D17" s="15">
         <f>COUNTIF(D6:D16,"○")</f>
         <v/>
       </c>
-      <c r="E17" s="13">
+      <c r="E17" s="15">
         <f>COUNTIF(E6:E16,"○")</f>
         <v/>
       </c>
-      <c r="F17" s="13">
+      <c r="F17" s="15">
         <f>COUNTIF(F6:F16,"○")</f>
         <v/>
       </c>
-      <c r="G17" s="14">
+      <c r="G17" s="16">
         <f>COUNTA(G6:G16)&amp;" 本 公開ずみ"</f>
         <v/>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A5:I16"/>
+  <autoFilter ref="A5:J16"/>
   <conditionalFormatting sqref="D6:F16">
     <cfRule type="cellIs" priority="1" operator="equal" dxfId="0">
       <formula>"×"</formula>
@@ -1311,244 +1367,244 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="15" t="inlineStr">
+      <c r="A1" s="17" t="inlineStr">
         <is>
           <t>進捗</t>
         </is>
       </c>
-      <c r="B1" s="15" t="inlineStr">
+      <c r="B1" s="17" t="inlineStr">
         <is>
           <t>案件</t>
         </is>
       </c>
-      <c r="C1" s="15" t="inlineStr">
+      <c r="C1" s="17" t="inlineStr">
         <is>
           <t>状態</t>
         </is>
       </c>
-      <c r="D1" s="15" t="inlineStr">
+      <c r="D1" s="17" t="inlineStr">
         <is>
           <t>担当</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="16" t="n">
+      <c r="A2" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="B2" s="17" t="inlineStr">
+      <c r="B2" s="19" t="inlineStr">
         <is>
           <t>REALIZE CLUB（法人向け）</t>
         </is>
       </c>
-      <c r="C2" s="17" t="inlineStr">
+      <c r="C2" s="19" t="inlineStr">
         <is>
           <t>未着手</t>
         </is>
       </c>
-      <c r="D2" s="17" t="inlineStr">
+      <c r="D2" s="19" t="inlineStr">
         <is>
           <t>未定</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="16" t="n">
+      <c r="A3" s="18" t="n">
         <v>0.05</v>
       </c>
-      <c r="B3" s="17" t="inlineStr">
+      <c r="B3" s="19" t="inlineStr">
         <is>
           <t>LIFE MAKE PARTNERS（加盟店募集）</t>
         </is>
       </c>
-      <c r="C3" s="17" t="inlineStr">
+      <c r="C3" s="19" t="inlineStr">
         <is>
           <t>進行中</t>
         </is>
       </c>
-      <c r="D3" s="17" t="inlineStr">
+      <c r="D3" s="19" t="inlineStr">
         <is>
           <t>社長</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="16" t="n">
+      <c r="A4" s="18" t="n">
         <v>0.1</v>
       </c>
-      <c r="B4" s="17" t="inlineStr">
+      <c r="B4" s="19" t="inlineStr">
         <is>
           <t>まちの相談窓口</t>
         </is>
       </c>
-      <c r="C4" s="17" t="inlineStr">
+      <c r="C4" s="19" t="inlineStr">
         <is>
           <t>確認待ち</t>
         </is>
       </c>
-      <c r="D4" s="17" t="inlineStr">
+      <c r="D4" s="19" t="inlineStr">
         <is>
           <t>白石</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="16" t="n">
+      <c r="A5" s="18" t="n">
         <v>0.15</v>
       </c>
-      <c r="B5" s="17" t="inlineStr">
+      <c r="B5" s="19" t="inlineStr">
         <is>
           <t>不動産FC加盟</t>
         </is>
       </c>
-      <c r="D5" s="17" t="inlineStr">
+      <c r="D5" s="19" t="inlineStr">
         <is>
           <t>池之上</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="16" t="n">
+      <c r="A6" s="18" t="n">
         <v>0.2</v>
       </c>
-      <c r="D6" s="17" t="inlineStr">
+      <c r="D6" s="19" t="inlineStr">
         <is>
           <t>大熊</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="16" t="n">
+      <c r="A7" s="18" t="n">
         <v>0.25</v>
       </c>
-      <c r="D7" s="17" t="inlineStr">
+      <c r="D7" s="19" t="inlineStr">
         <is>
           <t>片山</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="16" t="n">
+      <c r="A8" s="18" t="n">
         <v>0.3</v>
       </c>
-      <c r="D8" s="17" t="inlineStr">
+      <c r="D8" s="19" t="inlineStr">
         <is>
           <t>寺井</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="16" t="n">
+      <c r="A9" s="18" t="n">
         <v>0.35</v>
       </c>
-      <c r="D9" s="17" t="inlineStr">
+      <c r="D9" s="19" t="inlineStr">
         <is>
           <t>全員</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="16" t="n">
+      <c r="A10" s="18" t="n">
         <v>0.4</v>
       </c>
-      <c r="D10" s="17" t="inlineStr">
+      <c r="D10" s="19" t="inlineStr">
         <is>
           <t>大熊・片山</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="16" t="n">
+      <c r="A11" s="18" t="n">
         <v>0.45</v>
       </c>
-      <c r="D11" s="17" t="inlineStr">
+      <c r="D11" s="19" t="inlineStr">
         <is>
           <t>池之上・片山</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="16" t="n">
+      <c r="A12" s="18" t="n">
         <v>0.5</v>
       </c>
-      <c r="D12" s="17" t="inlineStr">
+      <c r="D12" s="19" t="inlineStr">
         <is>
           <t>大熊・白石</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="16" t="n">
+      <c r="A13" s="18" t="n">
         <v>0.55</v>
       </c>
-      <c r="D13" s="17" t="inlineStr">
+      <c r="D13" s="19" t="inlineStr">
         <is>
           <t>全員・池之上</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="16" t="n">
+      <c r="A14" s="18" t="n">
         <v>0.6000000000000001</v>
       </c>
-      <c r="D14" s="17" t="inlineStr">
+      <c r="D14" s="19" t="inlineStr">
         <is>
           <t>社長・白石・片山</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="16" t="n">
+      <c r="A15" s="18" t="n">
         <v>0.65</v>
       </c>
-      <c r="D15" s="17" t="inlineStr">
+      <c r="D15" s="19" t="inlineStr">
         <is>
           <t>白石・池之上・大熊</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="16" t="n">
+      <c r="A16" s="18" t="n">
         <v>0.7000000000000001</v>
       </c>
-      <c r="D16" s="17" t="inlineStr">
+      <c r="D16" s="19" t="inlineStr">
         <is>
           <t>白石・片山</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="16" t="n">
+      <c r="A17" s="18" t="n">
         <v>0.75</v>
       </c>
-      <c r="D17" s="17" t="inlineStr">
+      <c r="D17" s="19" t="inlineStr">
         <is>
           <t>社長・寺井・池之上・弁護士</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="16" t="n">
+      <c r="A18" s="18" t="n">
         <v>0.8</v>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="16" t="n">
+      <c r="A19" s="18" t="n">
         <v>0.8500000000000001</v>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="16" t="n">
+      <c r="A20" s="18" t="n">
         <v>0.9</v>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="16" t="n">
+      <c r="A21" s="18" t="n">
         <v>0.9500000000000001</v>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="16" t="n">
+      <c r="A22" s="18" t="n">
         <v>1</v>
       </c>
     </row>
@@ -1563,7 +1619,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G28"/>
+  <dimension ref="A1:H28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -1572,7 +1628,8 @@
     <col width="10" customWidth="1" min="4" max="4"/>
     <col width="11" customWidth="1" min="5" max="5"/>
     <col width="34" customWidth="1" min="6" max="6"/>
-    <col width="44" customWidth="1" min="7" max="7"/>
+    <col width="8" customWidth="1" min="7" max="7"/>
+    <col width="42" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1592,7 +1649,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>ツールの箱は50%まで来ていますが、中に入れる動画が20%で止まっています。赤い担当名は「未定」です。黄色のF列にURLを貼るとリンクになります。</t>
+          <t>ツールの箱は50%まで来ていますが、中に入れる動画が20%で止まっています。赤い担当名は「未定」です。黄色のF列にURLを貼ると、G列の「開く」からそのページへ飛べます。</t>
         </is>
       </c>
     </row>
@@ -1629,6 +1686,11 @@
       </c>
       <c r="G5" s="4" t="inlineStr">
         <is>
+          <t>開く</t>
+        </is>
+      </c>
+      <c r="H5" s="4" t="inlineStr">
+        <is>
           <t>メモ</t>
         </is>
       </c>
@@ -1644,21 +1706,25 @@
           <t>LMP事業 · Web・ツール・システム</t>
         </is>
       </c>
-      <c r="C6" s="18" t="inlineStr">
+      <c r="C6" s="20" t="inlineStr">
         <is>
           <t>社長・白石・片山</t>
         </is>
       </c>
-      <c r="D6" s="19" t="n">
+      <c r="D6" s="21" t="n">
         <v>0.5</v>
       </c>
-      <c r="E6" s="20" t="inlineStr">
+      <c r="E6" s="22" t="inlineStr">
         <is>
           <t>進行中</t>
         </is>
       </c>
-      <c r="F6" s="21" t="n"/>
-      <c r="G6" s="6" t="inlineStr">
+      <c r="F6" s="23" t="n"/>
+      <c r="G6" s="10">
+        <f>IF(F6="","",HYPERLINK(F6,"開く"))</f>
+        <v/>
+      </c>
+      <c r="H6" s="6" t="inlineStr">
         <is>
           <t>加盟店が学ぶ画面そのもの</t>
         </is>
@@ -1675,21 +1741,25 @@
           <t>LMP事業 · Web・ツール・システム</t>
         </is>
       </c>
-      <c r="C7" s="22" t="inlineStr">
+      <c r="C7" s="24" t="inlineStr">
         <is>
           <t>未定</t>
         </is>
       </c>
-      <c r="D7" s="19" t="n">
+      <c r="D7" s="21" t="n">
         <v>0.2</v>
       </c>
-      <c r="E7" s="20" t="inlineStr">
+      <c r="E7" s="22" t="inlineStr">
         <is>
           <t>進行中</t>
         </is>
       </c>
-      <c r="F7" s="21" t="n"/>
-      <c r="G7" s="6" t="inlineStr">
+      <c r="F7" s="23" t="n"/>
+      <c r="G7" s="10">
+        <f>IF(F7="","",HYPERLINK(F7,"開く"))</f>
+        <v/>
+      </c>
+      <c r="H7" s="6" t="inlineStr">
         <is>
           <t>教材の中で流す動画。担当が決まっていない</t>
         </is>
@@ -1706,21 +1776,25 @@
           <t>RC事業 · Web・ツール・システム</t>
         </is>
       </c>
-      <c r="C8" s="18" t="inlineStr">
+      <c r="C8" s="20" t="inlineStr">
         <is>
           <t>白石</t>
         </is>
       </c>
-      <c r="D8" s="19" t="n">
+      <c r="D8" s="21" t="n">
         <v>0.8</v>
       </c>
-      <c r="E8" s="20" t="inlineStr">
+      <c r="E8" s="22" t="inlineStr">
         <is>
           <t>進行中</t>
         </is>
       </c>
-      <c r="F8" s="21" t="n"/>
-      <c r="G8" s="6" t="inlineStr">
+      <c r="F8" s="23" t="n"/>
+      <c r="G8" s="10">
+        <f>IF(F8="","",HYPERLINK(F8,"開く"))</f>
+        <v/>
+      </c>
+      <c r="H8" s="6" t="inlineStr">
         <is>
           <t>学ぶ前に現在地をはかる</t>
         </is>
@@ -1737,21 +1811,25 @@
           <t>RC事業 · 動画・コンテンツ</t>
         </is>
       </c>
-      <c r="C9" s="18" t="inlineStr">
+      <c r="C9" s="20" t="inlineStr">
         <is>
           <t>白石</t>
         </is>
       </c>
-      <c r="D9" s="19" t="n">
+      <c r="D9" s="21" t="n">
         <v>0.6</v>
       </c>
-      <c r="E9" s="20" t="inlineStr">
+      <c r="E9" s="22" t="inlineStr">
         <is>
           <t>進行中</t>
         </is>
       </c>
-      <c r="F9" s="21" t="n"/>
-      <c r="G9" s="6" t="inlineStr">
+      <c r="F9" s="23" t="n"/>
+      <c r="G9" s="10">
+        <f>IF(F9="","",HYPERLINK(F9,"開く"))</f>
+        <v/>
+      </c>
+      <c r="H9" s="6" t="inlineStr">
         <is>
           <t>教材のもとになる原稿</t>
         </is>
@@ -1768,21 +1846,25 @@
           <t>LMP事業 · 営業・資料</t>
         </is>
       </c>
-      <c r="C10" s="22" t="inlineStr">
+      <c r="C10" s="24" t="inlineStr">
         <is>
           <t>未定</t>
         </is>
       </c>
-      <c r="D10" s="19" t="n">
+      <c r="D10" s="21" t="n">
         <v>0</v>
       </c>
-      <c r="E10" s="23" t="inlineStr">
+      <c r="E10" s="25" t="inlineStr">
         <is>
           <t>未着手</t>
         </is>
       </c>
-      <c r="F10" s="21" t="n"/>
-      <c r="G10" s="6" t="inlineStr">
+      <c r="F10" s="23" t="n"/>
+      <c r="G10" s="10">
+        <f>IF(F10="","",HYPERLINK(F10,"開く"))</f>
+        <v/>
+      </c>
+      <c r="H10" s="6" t="inlineStr">
         <is>
           <t>担当が決まっていない</t>
         </is>
@@ -1799,21 +1881,25 @@
           <t>LMP事業 · 加盟開発</t>
         </is>
       </c>
-      <c r="C11" s="18" t="inlineStr">
+      <c r="C11" s="20" t="inlineStr">
         <is>
           <t>白石・池之上・大熊</t>
         </is>
       </c>
-      <c r="D11" s="19" t="n">
+      <c r="D11" s="21" t="n">
         <v>0</v>
       </c>
-      <c r="E11" s="23" t="inlineStr">
+      <c r="E11" s="25" t="inlineStr">
         <is>
           <t>未着手</t>
         </is>
       </c>
-      <c r="F11" s="21" t="n"/>
-      <c r="G11" s="6" t="inlineStr"/>
+      <c r="F11" s="23" t="n"/>
+      <c r="G11" s="10">
+        <f>IF(F11="","",HYPERLINK(F11,"開く"))</f>
+        <v/>
+      </c>
+      <c r="H11" s="6" t="inlineStr"/>
     </row>
     <row r="12" ht="32" customHeight="1">
       <c r="A12" s="6" t="inlineStr">
@@ -1826,21 +1912,25 @@
           <t>RCP事業 · Web・ツール・システム</t>
         </is>
       </c>
-      <c r="C12" s="18" t="inlineStr">
+      <c r="C12" s="20" t="inlineStr">
         <is>
           <t>白石</t>
         </is>
       </c>
-      <c r="D12" s="19" t="n">
+      <c r="D12" s="21" t="n">
         <v>0</v>
       </c>
-      <c r="E12" s="23" t="inlineStr">
+      <c r="E12" s="25" t="inlineStr">
         <is>
           <t>未着手</t>
         </is>
       </c>
-      <c r="F12" s="21" t="n"/>
-      <c r="G12" s="6" t="inlineStr"/>
+      <c r="F12" s="23" t="n"/>
+      <c r="G12" s="10">
+        <f>IF(F12="","",HYPERLINK(F12,"開く"))</f>
+        <v/>
+      </c>
+      <c r="H12" s="6" t="inlineStr"/>
     </row>
     <row r="13" ht="32" customHeight="1">
       <c r="A13" s="6" t="inlineStr">
@@ -1853,21 +1943,25 @@
           <t>AIアオ先生 · 営業コーチ</t>
         </is>
       </c>
-      <c r="C13" s="18" t="inlineStr">
+      <c r="C13" s="20" t="inlineStr">
         <is>
           <t>池之上</t>
         </is>
       </c>
-      <c r="D13" s="19" t="n">
+      <c r="D13" s="21" t="n">
         <v>0.9</v>
       </c>
-      <c r="E13" s="24" t="inlineStr">
+      <c r="E13" s="26" t="inlineStr">
         <is>
           <t>確認待ち</t>
         </is>
       </c>
-      <c r="F13" s="21" t="n"/>
-      <c r="G13" s="6" t="inlineStr">
+      <c r="F13" s="23" t="n"/>
+      <c r="G13" s="10">
+        <f>IF(F13="","",HYPERLINK(F13,"開く"))</f>
+        <v/>
+      </c>
+      <c r="H13" s="6" t="inlineStr">
         <is>
           <t>制作MASTERのみに記載</t>
         </is>
@@ -1884,21 +1978,25 @@
           <t>RC事業 · 動画・コンテンツ</t>
         </is>
       </c>
-      <c r="C14" s="18" t="inlineStr">
+      <c r="C14" s="20" t="inlineStr">
         <is>
           <t>白石</t>
         </is>
       </c>
-      <c r="D14" s="19" t="n">
+      <c r="D14" s="21" t="n">
         <v>0.7</v>
       </c>
-      <c r="E14" s="20" t="inlineStr">
+      <c r="E14" s="22" t="inlineStr">
         <is>
           <t>進行中</t>
         </is>
       </c>
-      <c r="F14" s="21" t="n"/>
-      <c r="G14" s="6" t="inlineStr">
+      <c r="F14" s="23" t="n"/>
+      <c r="G14" s="10">
+        <f>IF(F14="","",HYPERLINK(F14,"開く"))</f>
+        <v/>
+      </c>
+      <c r="H14" s="6" t="inlineStr">
         <is>
           <t>動画で唯一動いている1本</t>
         </is>
@@ -1915,21 +2013,25 @@
           <t>RC事業 · 動画・コンテンツ</t>
         </is>
       </c>
-      <c r="C15" s="18" t="inlineStr">
+      <c r="C15" s="20" t="inlineStr">
         <is>
           <t>白石</t>
         </is>
       </c>
-      <c r="D15" s="19" t="n">
+      <c r="D15" s="21" t="n">
         <v>0</v>
       </c>
-      <c r="E15" s="23" t="inlineStr">
+      <c r="E15" s="25" t="inlineStr">
         <is>
           <t>未着手</t>
         </is>
       </c>
-      <c r="F15" s="21" t="n"/>
-      <c r="G15" s="6" t="inlineStr"/>
+      <c r="F15" s="23" t="n"/>
+      <c r="G15" s="10">
+        <f>IF(F15="","",HYPERLINK(F15,"開く"))</f>
+        <v/>
+      </c>
+      <c r="H15" s="6" t="inlineStr"/>
     </row>
     <row r="16" ht="32" customHeight="1">
       <c r="A16" s="6" t="inlineStr">
@@ -1942,21 +2044,25 @@
           <t>RC事業 · 動画・コンテンツ</t>
         </is>
       </c>
-      <c r="C16" s="18" t="inlineStr">
+      <c r="C16" s="20" t="inlineStr">
         <is>
           <t>白石</t>
         </is>
       </c>
-      <c r="D16" s="19" t="n">
+      <c r="D16" s="21" t="n">
         <v>0</v>
       </c>
-      <c r="E16" s="23" t="inlineStr">
+      <c r="E16" s="25" t="inlineStr">
         <is>
           <t>未着手</t>
         </is>
       </c>
-      <c r="F16" s="21" t="n"/>
-      <c r="G16" s="6" t="inlineStr"/>
+      <c r="F16" s="23" t="n"/>
+      <c r="G16" s="10">
+        <f>IF(F16="","",HYPERLINK(F16,"開く"))</f>
+        <v/>
+      </c>
+      <c r="H16" s="6" t="inlineStr"/>
     </row>
     <row r="17" ht="32" customHeight="1">
       <c r="A17" s="6" t="inlineStr">
@@ -1969,21 +2075,25 @@
           <t>RCP事業 · 動画・コンテンツ</t>
         </is>
       </c>
-      <c r="C17" s="18" t="inlineStr">
+      <c r="C17" s="20" t="inlineStr">
         <is>
           <t>白石</t>
         </is>
       </c>
-      <c r="D17" s="19" t="n">
+      <c r="D17" s="21" t="n">
         <v>0</v>
       </c>
-      <c r="E17" s="23" t="inlineStr">
+      <c r="E17" s="25" t="inlineStr">
         <is>
           <t>未着手</t>
         </is>
       </c>
-      <c r="F17" s="21" t="n"/>
-      <c r="G17" s="6" t="inlineStr"/>
+      <c r="F17" s="23" t="n"/>
+      <c r="G17" s="10">
+        <f>IF(F17="","",HYPERLINK(F17,"開く"))</f>
+        <v/>
+      </c>
+      <c r="H17" s="6" t="inlineStr"/>
     </row>
     <row r="18" ht="32" customHeight="1">
       <c r="A18" s="6" t="inlineStr">
@@ -1996,21 +2106,25 @@
           <t>RCP事業 · 動画・コンテンツ</t>
         </is>
       </c>
-      <c r="C18" s="18" t="inlineStr">
+      <c r="C18" s="20" t="inlineStr">
         <is>
           <t>白石</t>
         </is>
       </c>
-      <c r="D18" s="19" t="n">
+      <c r="D18" s="21" t="n">
         <v>0</v>
       </c>
-      <c r="E18" s="23" t="inlineStr">
+      <c r="E18" s="25" t="inlineStr">
         <is>
           <t>未着手</t>
         </is>
       </c>
-      <c r="F18" s="21" t="n"/>
-      <c r="G18" s="6" t="inlineStr"/>
+      <c r="F18" s="23" t="n"/>
+      <c r="G18" s="10">
+        <f>IF(F18="","",HYPERLINK(F18,"開く"))</f>
+        <v/>
+      </c>
+      <c r="H18" s="6" t="inlineStr"/>
     </row>
     <row r="19" ht="32" customHeight="1">
       <c r="A19" s="6" t="inlineStr">
@@ -2023,21 +2137,25 @@
           <t>RCP PPモデル · OEM</t>
         </is>
       </c>
-      <c r="C19" s="18" t="inlineStr">
+      <c r="C19" s="20" t="inlineStr">
         <is>
           <t>白石</t>
         </is>
       </c>
-      <c r="D19" s="19" t="n">
+      <c r="D19" s="21" t="n">
         <v>0</v>
       </c>
-      <c r="E19" s="23" t="inlineStr">
+      <c r="E19" s="25" t="inlineStr">
         <is>
           <t>未着手</t>
         </is>
       </c>
-      <c r="F19" s="21" t="n"/>
-      <c r="G19" s="6" t="inlineStr">
+      <c r="F19" s="23" t="n"/>
+      <c r="G19" s="10">
+        <f>IF(F19="","",HYPERLINK(F19,"開く"))</f>
+        <v/>
+      </c>
+      <c r="H19" s="6" t="inlineStr">
         <is>
           <t>AKさん・大橋会長・木原さん・水谷先生・藤田先生</t>
         </is>
@@ -2054,21 +2172,25 @@
           <t>RC／RCP／HI／PP · REALIZE QUEST</t>
         </is>
       </c>
-      <c r="C20" s="18" t="inlineStr">
+      <c r="C20" s="20" t="inlineStr">
         <is>
           <t>白石・片山</t>
         </is>
       </c>
-      <c r="D20" s="19" t="n">
+      <c r="D20" s="21" t="n">
         <v>0</v>
       </c>
-      <c r="E20" s="23" t="inlineStr">
+      <c r="E20" s="25" t="inlineStr">
         <is>
           <t>未着手</t>
         </is>
       </c>
-      <c r="F20" s="21" t="n"/>
-      <c r="G20" s="6" t="inlineStr"/>
+      <c r="F20" s="23" t="n"/>
+      <c r="G20" s="10">
+        <f>IF(F20="","",HYPERLINK(F20,"開く"))</f>
+        <v/>
+      </c>
+      <c r="H20" s="6" t="inlineStr"/>
     </row>
     <row r="21" ht="32" customHeight="1">
       <c r="A21" s="6" t="inlineStr">
@@ -2081,54 +2203,58 @@
           <t>採用 · 学生募集</t>
         </is>
       </c>
-      <c r="C21" s="18" t="inlineStr">
+      <c r="C21" s="20" t="inlineStr">
         <is>
           <t>白石・片山</t>
         </is>
       </c>
-      <c r="D21" s="19" t="n">
+      <c r="D21" s="21" t="n">
         <v>0</v>
       </c>
-      <c r="E21" s="23" t="inlineStr">
+      <c r="E21" s="25" t="inlineStr">
         <is>
           <t>未着手</t>
         </is>
       </c>
-      <c r="F21" s="21" t="n"/>
-      <c r="G21" s="6" t="inlineStr">
+      <c r="F21" s="23" t="n"/>
+      <c r="G21" s="10">
+        <f>IF(F21="","",HYPERLINK(F21,"開く"))</f>
+        <v/>
+      </c>
+      <c r="H21" s="6" t="inlineStr">
         <is>
           <t>PR動画・SNS採用募集動画</t>
         </is>
       </c>
     </row>
     <row r="22">
-      <c r="C22" s="12" t="inlineStr">
+      <c r="C22" s="14" t="inlineStr">
         <is>
           <t>平均</t>
         </is>
       </c>
-      <c r="D22" s="25">
+      <c r="D22" s="27">
         <f>AVERAGE(D6:D21)</f>
         <v/>
       </c>
-      <c r="E22" s="14">
+      <c r="E22" s="16">
         <f>COUNTIF(E6:E21,"未着手")&amp;" 件未着手"</f>
         <v/>
       </c>
-      <c r="F22" s="14">
+      <c r="F22" s="16">
         <f>COUNTA(F6:F21)&amp;" 件 登録ずみ"</f>
         <v/>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="26" t="inlineStr">
+      <c r="A24" s="28" t="inlineStr">
         <is>
           <t>できている設計書・ガイド</t>
         </is>
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="27" t="inlineStr">
+      <c r="A25" s="29" t="inlineStr">
         <is>
           <t>LIFE CHECK42 Eラーニング画面設計書</t>
         </is>
@@ -2143,14 +2269,14 @@
           <t>2026-08-31</t>
         </is>
       </c>
-      <c r="G25" s="28" t="inlineStr">
+      <c r="G25" s="30" t="inlineStr">
         <is>
           <t>開く</t>
         </is>
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="27" t="inlineStr">
+      <c r="A26" s="29" t="inlineStr">
         <is>
           <t>RCP ノーマル版 eラーニング｜UI提案 v1</t>
         </is>
@@ -2165,14 +2291,14 @@
           <t>2026-08-05</t>
         </is>
       </c>
-      <c r="G26" s="28" t="inlineStr">
+      <c r="G26" s="30" t="inlineStr">
         <is>
           <t>開く</t>
         </is>
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="27" t="inlineStr">
+      <c r="A27" s="29" t="inlineStr">
         <is>
           <t>AIロープレ 操作ガイド</t>
         </is>
@@ -2187,14 +2313,14 @@
           <t>2026-08-31</t>
         </is>
       </c>
-      <c r="G27" s="28" t="inlineStr">
+      <c r="G27" s="30" t="inlineStr">
         <is>
           <t>開く</t>
         </is>
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="27" t="inlineStr">
+      <c r="A28" s="29" t="inlineStr">
         <is>
           <t>生成AI動画講座 比較検討</t>
         </is>
@@ -2209,14 +2335,14 @@
           <t>2026-08-21</t>
         </is>
       </c>
-      <c r="G28" s="28" t="inlineStr">
+      <c r="G28" s="30" t="inlineStr">
         <is>
           <t>開く</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A5:G21"/>
+  <autoFilter ref="A5:H21"/>
   <conditionalFormatting sqref="D6:D21">
     <cfRule type="dataBar" priority="1">
       <dataBar showValue="1">
@@ -2254,7 +2380,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G11"/>
+  <dimension ref="A1:H11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -2263,7 +2389,8 @@
     <col width="10" customWidth="1" min="4" max="4"/>
     <col width="11" customWidth="1" min="5" max="5"/>
     <col width="34" customWidth="1" min="6" max="6"/>
-    <col width="44" customWidth="1" min="7" max="7"/>
+    <col width="8" customWidth="1" min="7" max="7"/>
+    <col width="42" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -2283,7 +2410,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>広告を出すには、飛ばす先のLPが公開され、問い合わせが届く状態である必要があります。着手日はLP公開日で決まります。</t>
+          <t>広告を出すには、飛ばす先のLPが公開され、問い合わせが届く状態である必要があります。着手日はLP公開日で決まります。黄色のF列にURLを貼ると、G列の「開く」から飛べます。</t>
         </is>
       </c>
     </row>
@@ -2320,6 +2447,11 @@
       </c>
       <c r="G5" s="4" t="inlineStr">
         <is>
+          <t>開く</t>
+        </is>
+      </c>
+      <c r="H5" s="4" t="inlineStr">
+        <is>
           <t>メモ</t>
         </is>
       </c>
@@ -2335,21 +2467,25 @@
           <t>RC法人開拓 · 地域企業への入口</t>
         </is>
       </c>
-      <c r="C6" s="18" t="inlineStr">
+      <c r="C6" s="20" t="inlineStr">
         <is>
           <t>大熊・片山</t>
         </is>
       </c>
-      <c r="D6" s="19" t="n">
+      <c r="D6" s="21" t="n">
         <v>0</v>
       </c>
-      <c r="E6" s="23" t="inlineStr">
+      <c r="E6" s="25" t="inlineStr">
         <is>
           <t>未着手</t>
         </is>
       </c>
-      <c r="F6" s="21" t="n"/>
-      <c r="G6" s="6" t="inlineStr">
+      <c r="F6" s="23" t="n"/>
+      <c r="G6" s="10">
+        <f>IF(F6="","",HYPERLINK(F6,"開く"))</f>
+        <v/>
+      </c>
+      <c r="H6" s="6" t="inlineStr">
         <is>
           <t>バナー・原稿などのクリエイティブ</t>
         </is>
@@ -2366,21 +2502,25 @@
           <t>RC法人開拓／LMP加盟開発</t>
         </is>
       </c>
-      <c r="C7" s="18" t="inlineStr">
+      <c r="C7" s="20" t="inlineStr">
         <is>
           <t>池之上・片山</t>
         </is>
       </c>
-      <c r="D7" s="19" t="n">
+      <c r="D7" s="21" t="n">
         <v>0</v>
       </c>
-      <c r="E7" s="23" t="inlineStr">
+      <c r="E7" s="25" t="inlineStr">
         <is>
           <t>未着手</t>
         </is>
       </c>
-      <c r="F7" s="21" t="n"/>
-      <c r="G7" s="6" t="inlineStr">
+      <c r="F7" s="23" t="n"/>
+      <c r="G7" s="10">
+        <f>IF(F7="","",HYPERLINK(F7,"開く"))</f>
+        <v/>
+      </c>
+      <c r="H7" s="6" t="inlineStr">
         <is>
           <t>出稿・予算・改善</t>
         </is>
@@ -2397,21 +2537,25 @@
           <t>LMP事業 · 全体品質確認</t>
         </is>
       </c>
-      <c r="C8" s="18" t="inlineStr">
+      <c r="C8" s="20" t="inlineStr">
         <is>
           <t>白石</t>
         </is>
       </c>
-      <c r="D8" s="19" t="n">
+      <c r="D8" s="21" t="n">
         <v>0</v>
       </c>
-      <c r="E8" s="23" t="inlineStr">
+      <c r="E8" s="25" t="inlineStr">
         <is>
           <t>未着手</t>
         </is>
       </c>
-      <c r="F8" s="21" t="n"/>
-      <c r="G8" s="6" t="inlineStr">
+      <c r="F8" s="23" t="n"/>
+      <c r="G8" s="10">
+        <f>IF(F8="","",HYPERLINK(F8,"開く"))</f>
+        <v/>
+      </c>
+      <c r="H8" s="6" t="inlineStr">
         <is>
           <t>出す前の品質確認</t>
         </is>
@@ -2428,21 +2572,25 @@
           <t>社内業務 · 法務・業法</t>
         </is>
       </c>
-      <c r="C9" s="18" t="inlineStr">
+      <c r="C9" s="20" t="inlineStr">
         <is>
           <t>社長・寺井・池之上・弁護士</t>
         </is>
       </c>
-      <c r="D9" s="19" t="n">
+      <c r="D9" s="21" t="n">
         <v>0</v>
       </c>
-      <c r="E9" s="23" t="inlineStr">
+      <c r="E9" s="25" t="inlineStr">
         <is>
           <t>未着手</t>
         </is>
       </c>
-      <c r="F9" s="21" t="n"/>
-      <c r="G9" s="6" t="inlineStr">
+      <c r="F9" s="23" t="n"/>
+      <c r="G9" s="10">
+        <f>IF(F9="","",HYPERLINK(F9,"開く"))</f>
+        <v/>
+      </c>
+      <c r="H9" s="6" t="inlineStr">
         <is>
           <t>言い切り表現・実績表示の法務確認</t>
         </is>
@@ -2459,43 +2607,47 @@
           <t>RC／RCP／HI／PP · REALIZE QUEST</t>
         </is>
       </c>
-      <c r="C10" s="18" t="inlineStr">
+      <c r="C10" s="20" t="inlineStr">
         <is>
           <t>白石</t>
         </is>
       </c>
-      <c r="D10" s="19" t="n">
+      <c r="D10" s="21" t="n">
         <v>0</v>
       </c>
-      <c r="E10" s="23" t="inlineStr">
+      <c r="E10" s="25" t="inlineStr">
         <is>
           <t>未着手</t>
         </is>
       </c>
-      <c r="F10" s="21" t="n"/>
-      <c r="G10" s="6" t="inlineStr"/>
+      <c r="F10" s="23" t="n"/>
+      <c r="G10" s="10">
+        <f>IF(F10="","",HYPERLINK(F10,"開く"))</f>
+        <v/>
+      </c>
+      <c r="H10" s="6" t="inlineStr"/>
     </row>
     <row r="11">
-      <c r="C11" s="12" t="inlineStr">
+      <c r="C11" s="14" t="inlineStr">
         <is>
           <t>平均</t>
         </is>
       </c>
-      <c r="D11" s="25">
+      <c r="D11" s="27">
         <f>AVERAGE(D6:D10)</f>
         <v/>
       </c>
-      <c r="E11" s="14">
+      <c r="E11" s="16">
         <f>COUNTIF(E6:E10,"未着手")&amp;" 件未着手"</f>
         <v/>
       </c>
-      <c r="F11" s="14">
+      <c r="F11" s="16">
         <f>COUNTA(F6:F10)&amp;" 件 登録ずみ"</f>
         <v/>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A5:G10"/>
+  <autoFilter ref="A5:H10"/>
   <conditionalFormatting sqref="D6:D10">
     <cfRule type="dataBar" priority="1">
       <dataBar showValue="1">
@@ -2535,318 +2687,318 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="29" t="inlineStr">
+      <c r="A1" s="31" t="inlineStr">
         <is>
           <t>凡例と出典</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="30" t="inlineStr">
+      <c r="A3" s="32" t="inlineStr">
         <is>
           <t>LPの3段</t>
         </is>
       </c>
     </row>
     <row r="4" ht="36" customHeight="1">
-      <c r="A4" s="31" t="inlineStr">
+      <c r="A4" s="33" t="inlineStr">
         <is>
           <t>原稿・デザイン</t>
         </is>
       </c>
-      <c r="B4" s="32" t="inlineStr">
+      <c r="B4" s="34" t="inlineStr">
         <is>
           <t>本編の文章とデザインが最後まで通っている</t>
         </is>
       </c>
     </row>
     <row r="5" ht="36" customHeight="1">
-      <c r="A5" s="31" t="inlineStr">
+      <c r="A5" s="33" t="inlineStr">
         <is>
           <t>問い合わせ導線</t>
         </is>
       </c>
-      <c r="B5" s="32" t="inlineStr">
+      <c r="B5" s="34" t="inlineStr">
         <is>
           <t>ボタンの行き先が実在し、問い合わせが届く先につながっている</t>
         </is>
       </c>
     </row>
     <row r="6" ht="36" customHeight="1">
-      <c r="A6" s="31" t="inlineStr">
+      <c r="A6" s="33" t="inlineStr">
         <is>
           <t>本番公開</t>
         </is>
       </c>
-      <c r="B6" s="32" t="inlineStr">
+      <c r="B6" s="34" t="inlineStr">
         <is>
           <t>独自ドメインで公開され、G列に本番URLが入っている（自動判定）。</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="30" t="inlineStr">
+      <c r="A8" s="32" t="inlineStr">
         <is>
           <t>記号</t>
         </is>
       </c>
     </row>
     <row r="9" ht="36" customHeight="1">
-      <c r="A9" s="31" t="inlineStr">
+      <c r="A9" s="33" t="inlineStr">
         <is>
           <t>○</t>
         </is>
       </c>
-      <c r="B9" s="32" t="inlineStr">
+      <c r="B9" s="34" t="inlineStr">
         <is>
           <t>できている</t>
         </is>
       </c>
     </row>
     <row r="10" ht="36" customHeight="1">
-      <c r="A10" s="31" t="inlineStr">
+      <c r="A10" s="33" t="inlineStr">
         <is>
           <t>△</t>
         </is>
       </c>
-      <c r="B10" s="32" t="inlineStr">
+      <c r="B10" s="34" t="inlineStr">
         <is>
           <t>仮づけ。メーラーを開くだけ、または行き先が「#」のまま</t>
         </is>
       </c>
     </row>
     <row r="11" ht="36" customHeight="1">
-      <c r="A11" s="31" t="inlineStr">
+      <c r="A11" s="33" t="inlineStr">
         <is>
           <t>×</t>
         </is>
       </c>
-      <c r="B11" s="32" t="inlineStr">
+      <c r="B11" s="34" t="inlineStr">
         <is>
           <t>手つかず／ページが存在しない</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="30" t="inlineStr">
+      <c r="A13" s="32" t="inlineStr">
         <is>
           <t>状態</t>
         </is>
       </c>
     </row>
     <row r="14" ht="36" customHeight="1">
-      <c r="A14" s="31" t="inlineStr">
+      <c r="A14" s="33" t="inlineStr">
         <is>
           <t>確認待ち</t>
         </is>
       </c>
-      <c r="B14" s="32" t="inlineStr">
+      <c r="B14" s="34" t="inlineStr">
         <is>
           <t>作業は終わり、誰かの確認を待っている</t>
         </is>
       </c>
     </row>
     <row r="15" ht="36" customHeight="1">
-      <c r="A15" s="31" t="inlineStr">
+      <c r="A15" s="33" t="inlineStr">
         <is>
           <t>進行中</t>
         </is>
       </c>
-      <c r="B15" s="32" t="inlineStr">
+      <c r="B15" s="34" t="inlineStr">
         <is>
           <t>いま手が動いている</t>
         </is>
       </c>
     </row>
     <row r="16" ht="36" customHeight="1">
-      <c r="A16" s="31" t="inlineStr">
+      <c r="A16" s="33" t="inlineStr">
         <is>
           <t>未着手</t>
         </is>
       </c>
-      <c r="B16" s="32" t="inlineStr">
+      <c r="B16" s="34" t="inlineStr">
         <is>
           <t>まだ始まっていない</t>
         </is>
       </c>
     </row>
     <row r="17" ht="36" customHeight="1">
-      <c r="A17" s="31" t="inlineStr">
+      <c r="A17" s="33" t="inlineStr">
         <is>
           <t>赤い担当名</t>
         </is>
       </c>
-      <c r="B17" s="32" t="inlineStr">
+      <c r="B17" s="34" t="inlineStr">
         <is>
           <t>担当が「未定」の仕事。誰かを決めないと進みません</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="30" t="inlineStr">
+      <c r="A19" s="32" t="inlineStr">
         <is>
           <t>クリックして選べるところ（水色のセル）</t>
         </is>
       </c>
     </row>
     <row r="20" ht="36" customHeight="1">
-      <c r="A20" s="31" t="inlineStr">
+      <c r="A20" s="33" t="inlineStr">
         <is>
           <t>案件</t>
         </is>
       </c>
-      <c r="B20" s="32" t="inlineStr">
+      <c r="B20" s="34" t="inlineStr">
         <is>
           <t>LPシートのA列。どの案件のLPかを選びます。</t>
         </is>
       </c>
     </row>
     <row r="21" ht="36" customHeight="1">
-      <c r="A21" s="31" t="inlineStr">
+      <c r="A21" s="33" t="inlineStr">
         <is>
           <t>担当</t>
         </is>
       </c>
-      <c r="B21" s="32" t="inlineStr">
+      <c r="B21" s="34" t="inlineStr">
         <is>
           <t>タスクシートのC列。一覧から選ぶか、直接書き換えます。</t>
         </is>
       </c>
     </row>
     <row r="22" ht="36" customHeight="1">
-      <c r="A22" s="31" t="inlineStr">
+      <c r="A22" s="33" t="inlineStr">
         <is>
           <t>進捗</t>
         </is>
       </c>
-      <c r="B22" s="32" t="inlineStr">
+      <c r="B22" s="34" t="inlineStr">
         <is>
           <t>タスクシートのD列。0%〜100%を5%きざみで選べます。選ぶとセルの中のバーが伸び縮みします。</t>
         </is>
       </c>
     </row>
     <row r="23" ht="36" customHeight="1">
-      <c r="A23" s="31" t="inlineStr">
+      <c r="A23" s="33" t="inlineStr">
         <is>
           <t>状態</t>
         </is>
       </c>
-      <c r="B23" s="32" t="inlineStr">
+      <c r="B23" s="34" t="inlineStr">
         <is>
           <t>タスクシートのE列。未着手／進行中／確認待ち。</t>
         </is>
       </c>
     </row>
     <row r="24" ht="36" customHeight="1">
-      <c r="A24" s="31" t="inlineStr">
+      <c r="A24" s="33" t="inlineStr">
         <is>
           <t>LPの○△×</t>
         </is>
       </c>
-      <c r="B24" s="32" t="inlineStr">
+      <c r="B24" s="34" t="inlineStr">
         <is>
           <t>LPシートのD・E列。本番公開（F列）はG列のURL有無から自動で決まります。</t>
         </is>
       </c>
     </row>
     <row r="25" ht="36" customHeight="1">
-      <c r="A25" s="31" t="inlineStr">
-        <is>
-          <t>黄色の記入欄（本番URL）</t>
-        </is>
-      </c>
-      <c r="B25" s="32" t="inlineStr">
-        <is>
-          <t>公開したURL・動画URL・広告の入稿先を貼ります。貼ってEnterを押すと、そのセルがそのページへのリンクになり、クリックで開きます。リンクにならないときは、そのセルを右クリック→「リンク」で設定できます。</t>
+      <c r="A25" s="33" t="inlineStr">
+        <is>
+          <t>黄色の記入欄と「開く」</t>
+        </is>
+      </c>
+      <c r="B25" s="34" t="inlineStr">
+        <is>
+          <t>公開したURL・動画URL・広告の入稿先を、黄色のセルに貼ります。貼ると右隣の「開く」がそのページへのリンクになり、クリックで開きます。全シート同じ作りです。</t>
         </is>
       </c>
     </row>
     <row r="26" ht="36" customHeight="1">
-      <c r="A26" s="31" t="inlineStr">
+      <c r="A26" s="33" t="inlineStr">
         <is>
           <t>列見出しの▼</t>
         </is>
       </c>
-      <c r="B26" s="32" t="inlineStr">
+      <c r="B26" s="34" t="inlineStr">
         <is>
           <t>オートフィルタです。値を選ぶとその行だけ表示されます。複数の列を組み合わせられます。</t>
         </is>
       </c>
     </row>
     <row r="27" ht="36" customHeight="1">
-      <c r="A27" s="31" t="inlineStr">
+      <c r="A27" s="33" t="inlineStr">
         <is>
           <t>選択肢を増やしたいとき</t>
         </is>
       </c>
-      <c r="B27" s="32" t="inlineStr">
+      <c r="B27" s="34" t="inlineStr">
         <is>
           <t>非表示シート「選択肢」に一覧があります。値を足し、入力規則の参照範囲を広げれば選べるようになります。</t>
         </is>
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="30" t="inlineStr">
+      <c r="A29" s="32" t="inlineStr">
         <is>
           <t>出典</t>
         </is>
       </c>
     </row>
     <row r="30" ht="36" customHeight="1">
-      <c r="A30" s="31" t="inlineStr">
+      <c r="A30" s="33" t="inlineStr">
         <is>
           <t>LPシート</t>
         </is>
       </c>
-      <c r="B30" s="32" t="inlineStr">
+      <c r="B30" s="34" t="inlineStr">
         <is>
           <t>公開済みアーティファクト43件のうちLPに該当する22ページ（本編11＋付随11）を、1ページずつHTMLを読んで確認。ボタンの行き先・フォームの送信方法・付随ページの有無は実物ベースです。</t>
         </is>
       </c>
     </row>
     <row r="31" ht="36" customHeight="1">
-      <c r="A31" s="31" t="inlineStr">
+      <c r="A31" s="33" t="inlineStr">
         <is>
           <t>進捗％と担当</t>
         </is>
       </c>
-      <c r="B31" s="32" t="inlineStr">
+      <c r="B31" s="34" t="inlineStr">
         <is>
           <t>社内の「REALIZE OS 制作MASTER」(2026-09-03) と「仕事の棚卸し」(2026-09-02) の数値をそのまま引いています。</t>
         </is>
       </c>
     </row>
     <row r="32" ht="36" customHeight="1">
-      <c r="A32" s="31" t="inlineStr">
+      <c r="A32" s="33" t="inlineStr">
         <is>
           <t>担当の食い違い</t>
         </is>
       </c>
-      <c r="B32" s="32" t="inlineStr">
+      <c r="B32" s="34" t="inlineStr">
         <is>
           <t>広告運用の担当は2資料で記載が違います（制作MASTER＝大熊・片山／棚卸し＝池之上・片山）。広告制作は大熊・片山、広告運用は池之上・片山としています。</t>
         </is>
       </c>
     </row>
     <row r="33" ht="36" customHeight="1">
-      <c r="A33" s="31" t="inlineStr">
+      <c r="A33" s="33" t="inlineStr">
         <is>
           <t>未確認</t>
         </is>
       </c>
-      <c r="B33" s="32" t="inlineStr">
+      <c r="B33" s="34" t="inlineStr">
         <is>
           <t>LP付随ページ4本（RC星空案の会社概要、RCアイス案の資料請求、LMP星空案の資料請求と会社概要）は、親LPからのリンクで存在を確認しただけで中身は開いていません。</t>
         </is>
       </c>
     </row>
     <row r="34" ht="36" customHeight="1">
-      <c r="A34" s="31" t="inlineStr">
+      <c r="A34" s="33" t="inlineStr">
         <is>
           <t>調査日</t>
         </is>
       </c>
-      <c r="B34" s="32" t="inlineStr">
+      <c r="B34" s="34" t="inlineStr">
         <is>
           <t>2026-09-03</t>
         </is>
